--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458C598F-D0E9-41DC-A334-3E40E002F393}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDBFCF7-637E-4C39-8FAE-BFCD691CC092}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="12" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="02-12-2026" sheetId="20" r:id="rId11"/>
     <sheet name="02-13-2026" sheetId="11" r:id="rId12"/>
     <sheet name="02-14-2026" sheetId="21" r:id="rId13"/>
+    <sheet name="02-16-2026" sheetId="22" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -39,6 +40,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'02-12-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'02-13-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'02-14-2026'!$A$1:$W$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'02-16-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
   </definedNames>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="93">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -1414,7 +1416,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1816,6 +1818,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3131,34 +3136,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="133" t="s">
+      <c r="A21" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="130" t="s">
+      <c r="B21" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="131"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="130" t="s">
+      <c r="C21" s="132"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="131"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="130" t="s">
+      <c r="F21" s="132"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="131"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="130" t="s">
+      <c r="I21" s="132"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="131"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="130" t="s">
+      <c r="L21" s="132"/>
+      <c r="M21" s="133"/>
+      <c r="N21" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="131"/>
-      <c r="P21" s="132"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="133"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3181,7 +3186,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="134"/>
+      <c r="A22" s="135"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3405,21 +3410,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3431,17 +3436,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3461,13 +3466,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3507,10 +3512,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3518,9 +3523,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6103,17 +6108,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6422,21 +6427,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6448,17 +6453,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6478,13 +6483,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6524,10 +6529,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6535,9 +6540,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9116,17 +9121,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9435,21 +9440,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9461,17 +9466,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9491,13 +9496,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9537,10 +9542,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9548,9 +9553,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12120,17 +12125,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12439,21 +12444,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12465,17 +12470,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12495,13 +12500,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12541,10 +12546,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12552,9 +12557,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -14540,7 +14545,7 @@
       <c r="F42" s="97"/>
       <c r="G42" s="97"/>
       <c r="H42" s="97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" s="97">
         <v>6</v>
@@ -14571,15 +14576,15 @@
       <c r="S42" s="102"/>
       <c r="T42" s="104">
         <f t="shared" ref="T42" si="6">H42+I42+J42+K42+N42+P42+R42</f>
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="U42" s="104">
         <f>C42*6+M42*6+O42*6+Q42*6+T42</f>
-        <v>155123</v>
+        <v>155124</v>
       </c>
       <c r="V42" s="104">
         <f>U42/6</f>
-        <v>25853.833333333332</v>
+        <v>25854</v>
       </c>
     </row>
     <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -15081,7 +15086,7 @@
       </c>
       <c r="H57" s="49">
         <f t="shared" si="12"/>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I57" s="54">
         <f t="shared" si="12"/>
@@ -15122,15 +15127,15 @@
       <c r="S57" s="57"/>
       <c r="T57" s="51">
         <f>SUM(T7:T56)</f>
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="U57" s="51">
         <f>SUM(U7:U56)</f>
-        <v>335993</v>
+        <v>335994</v>
       </c>
       <c r="V57" s="51">
         <f>SUM(V7:V56)</f>
-        <v>39489.458333333336</v>
+        <v>39489.625</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -15138,17 +15143,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15407,6 +15412,2854 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854A82F5-4846-4B63-B1FC-CBAEA8F57277}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB80"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="136" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="147" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="149" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="142" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="144" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="145"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="130"/>
+      <c r="Q6" s="130"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="69"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="69"/>
+      <c r="T7" s="91">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="91">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="91">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="126">
+        <f t="shared" ref="T8:T40" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="124">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A56" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="46"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="46"/>
+      <c r="T9" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="125">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="125">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="46"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="46"/>
+      <c r="T10" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="46"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="46"/>
+      <c r="T11" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="124">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="124">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="46"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="46"/>
+      <c r="T13" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="125">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="125">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="46"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="46"/>
+      <c r="T14" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="46"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="46"/>
+      <c r="T15" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="46"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="46"/>
+      <c r="T16" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="46"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="46"/>
+      <c r="T17" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="46"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="46"/>
+      <c r="T18" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="46"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="46"/>
+      <c r="T19" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="46"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="46"/>
+      <c r="T20" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="46"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="46"/>
+      <c r="T21" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="57"/>
+      <c r="X24" s="57"/>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="57"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="57"/>
+      <c r="AE24" s="57"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="46"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="46"/>
+      <c r="T25" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="60"/>
+      <c r="AG25" s="60"/>
+      <c r="AH25" s="60"/>
+      <c r="AI25" s="60"/>
+      <c r="AJ25" s="60"/>
+      <c r="AK25" s="60"/>
+      <c r="AL25" s="60"/>
+      <c r="AM25" s="60"/>
+      <c r="AN25" s="60"/>
+      <c r="AO25" s="60"/>
+      <c r="AP25" s="60"/>
+      <c r="AQ25" s="60"/>
+      <c r="AR25" s="60"/>
+      <c r="AS25" s="60"/>
+      <c r="AT25" s="60"/>
+      <c r="AU25" s="60"/>
+      <c r="AV25" s="60"/>
+      <c r="AW25" s="60"/>
+      <c r="AX25" s="60"/>
+      <c r="AY25" s="60"/>
+      <c r="AZ25" s="60"/>
+      <c r="BA25" s="60"/>
+      <c r="BB25" s="60"/>
+    </row>
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="46"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="46"/>
+      <c r="T26" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY26" s="62" t="e">
+        <f>#REF!-AY25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="46"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="46"/>
+      <c r="T29" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="46"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="46"/>
+      <c r="T30" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="46"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="46"/>
+      <c r="T31" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="46"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="46"/>
+      <c r="T32" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="46"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="46"/>
+      <c r="T33" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="46"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="46"/>
+      <c r="T34" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="46"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="46"/>
+      <c r="T35" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="46"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="46"/>
+      <c r="T36" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="97"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="98"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="104">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="104">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="46"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="46"/>
+      <c r="T38" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="50">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="50">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="110"/>
+      <c r="K39" s="96"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="103"/>
+      <c r="N39" s="120"/>
+      <c r="O39" s="97"/>
+      <c r="P39" s="113"/>
+      <c r="Q39" s="113"/>
+      <c r="R39" s="98"/>
+      <c r="S39" s="102"/>
+      <c r="T39" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U39" s="104">
+        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="104">
+        <f>U39/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="100"/>
+      <c r="D40" s="100"/>
+      <c r="E40" s="100"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="100"/>
+      <c r="J40" s="112"/>
+      <c r="K40" s="101"/>
+      <c r="L40" s="105"/>
+      <c r="M40" s="106"/>
+      <c r="N40" s="122"/>
+      <c r="O40" s="100"/>
+      <c r="P40" s="112"/>
+      <c r="Q40" s="112"/>
+      <c r="R40" s="101"/>
+      <c r="S40" s="105"/>
+      <c r="T40" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="107">
+        <f>C40*12+M40*12+O40*12+Q40*12+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="107">
+        <f>U40/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="111"/>
+      <c r="K41" s="46"/>
+      <c r="M41" s="52"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="47"/>
+      <c r="P41" s="111"/>
+      <c r="Q41" s="111"/>
+      <c r="R41" s="46"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="50"/>
+      <c r="V41" s="50"/>
+    </row>
+    <row r="42" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="97"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="97"/>
+      <c r="F42" s="97"/>
+      <c r="G42" s="97"/>
+      <c r="H42" s="97"/>
+      <c r="I42" s="97"/>
+      <c r="J42" s="113"/>
+      <c r="K42" s="98"/>
+      <c r="L42" s="102"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="120"/>
+      <c r="O42" s="97"/>
+      <c r="P42" s="113"/>
+      <c r="Q42" s="113"/>
+      <c r="R42" s="98"/>
+      <c r="S42" s="102"/>
+      <c r="T42" s="104">
+        <f t="shared" ref="T42" si="6">H42+I42+J42+K42+N42+P42+R42</f>
+        <v>0</v>
+      </c>
+      <c r="U42" s="104">
+        <f>C42*6+M42*6+O42*6+Q42*6+T42</f>
+        <v>0</v>
+      </c>
+      <c r="V42" s="104">
+        <f>U42/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="111"/>
+      <c r="K43" s="46"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="47"/>
+      <c r="P43" s="111"/>
+      <c r="Q43" s="111"/>
+      <c r="R43" s="46"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="50"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="46"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111"/>
+      <c r="R44" s="46"/>
+      <c r="T44" s="50">
+        <f t="shared" ref="T44:T53" si="7">H44+I44+J44+K44+N44+P44+R44</f>
+        <v>0</v>
+      </c>
+      <c r="U44" s="50">
+        <f>C44*24+M44*24+O44*24+Q44*24+T44</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="50">
+        <f>U44/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="46"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="46"/>
+      <c r="T45" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U45" s="50">
+        <f t="shared" ref="U45:U47" si="8">C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="50">
+        <f t="shared" ref="V45:V53" si="9">U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="46"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="46"/>
+      <c r="T46" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="46"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="111"/>
+      <c r="Q47" s="111"/>
+      <c r="R47" s="46"/>
+      <c r="T47" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="46"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="111"/>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="46"/>
+      <c r="T48" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="50">
+        <f>C48*6+M48*6+O48*6+Q48*6+T48</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="50">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="46"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="46"/>
+      <c r="T49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="50">
+        <f t="shared" ref="U49:U51" si="10">C49*24+M49*24+O49*24+Q49*24+T49</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="46"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="111"/>
+      <c r="Q50" s="111"/>
+      <c r="R50" s="46"/>
+      <c r="T50" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="46"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="46"/>
+      <c r="T51" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="46"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="111"/>
+      <c r="R52" s="46"/>
+      <c r="T52" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="50">
+        <f>C52*6+M52*6+O52*6+Q52*6+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="50">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="46"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="111"/>
+      <c r="Q53" s="111"/>
+      <c r="R53" s="46"/>
+      <c r="T53" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="50">
+        <f t="shared" ref="U53" si="11">C53*24+M53*24+O53*24+Q53*24+T53</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="46"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="46"/>
+      <c r="T54" s="50"/>
+      <c r="U54" s="50"/>
+      <c r="V54" s="50"/>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="46"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="46"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="46"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="46"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="50"/>
+      <c r="V56" s="50"/>
+    </row>
+    <row r="57" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="49">
+        <f>SUM(C7:C56)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49">
+        <f t="shared" ref="F57:K57" si="12">SUM(F7:F56)</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="53">
+        <f t="shared" ref="M57:R57" si="13">SUM(M7:M56)</f>
+        <v>0</v>
+      </c>
+      <c r="N57" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O57" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R57" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="57"/>
+      <c r="T57" s="51">
+        <f>SUM(T7:T56)</f>
+        <v>0</v>
+      </c>
+      <c r="U57" s="51">
+        <f>SUM(U7:U56)</f>
+        <v>0</v>
+      </c>
+      <c r="V57" s="51">
+        <f>SUM(V7:V56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" s="138" t="s">
+        <v>49</v>
+      </c>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
+      <c r="U59" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B60" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="114"/>
+      <c r="K60" s="68"/>
+      <c r="U60" s="55"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="109"/>
+      <c r="K61" s="69"/>
+      <c r="U61" s="50"/>
+    </row>
+    <row r="62" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" s="70"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="70"/>
+      <c r="F62" s="70"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="70"/>
+      <c r="I62" s="70"/>
+      <c r="J62" s="115"/>
+      <c r="K62" s="71"/>
+      <c r="U62" s="56"/>
+    </row>
+    <row r="63" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="67"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="67"/>
+      <c r="I64" s="67"/>
+      <c r="J64" s="114"/>
+      <c r="K64" s="68"/>
+      <c r="U64" s="55"/>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C65" s="48"/>
+      <c r="D65" s="48"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="109"/>
+      <c r="K65" s="69"/>
+      <c r="U65" s="50"/>
+    </row>
+    <row r="66" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C66" s="70"/>
+      <c r="D66" s="70"/>
+      <c r="E66" s="70"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="70"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="70"/>
+      <c r="J66" s="115"/>
+      <c r="K66" s="71"/>
+      <c r="U66" s="56"/>
+    </row>
+    <row r="67" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B68" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="67"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="67"/>
+      <c r="I68" s="67"/>
+      <c r="J68" s="114"/>
+      <c r="K68" s="68"/>
+      <c r="U68" s="55"/>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69" s="48"/>
+      <c r="D69" s="48"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="109"/>
+      <c r="K69" s="69"/>
+      <c r="U69" s="50"/>
+    </row>
+    <row r="70" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="70"/>
+      <c r="J70" s="115"/>
+      <c r="K70" s="71"/>
+      <c r="U70" s="56"/>
+    </row>
+    <row r="71" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B72" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="67"/>
+      <c r="D72" s="67"/>
+      <c r="E72" s="67"/>
+      <c r="F72" s="67"/>
+      <c r="G72" s="67"/>
+      <c r="H72" s="67"/>
+      <c r="I72" s="67"/>
+      <c r="J72" s="114"/>
+      <c r="K72" s="68"/>
+      <c r="U72" s="55"/>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="48"/>
+      <c r="D73" s="48"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="109"/>
+      <c r="K73" s="69"/>
+      <c r="U73" s="50"/>
+    </row>
+    <row r="74" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C74" s="70"/>
+      <c r="D74" s="70"/>
+      <c r="E74" s="70"/>
+      <c r="F74" s="70"/>
+      <c r="G74" s="70"/>
+      <c r="H74" s="70"/>
+      <c r="I74" s="70"/>
+      <c r="J74" s="115"/>
+      <c r="K74" s="71"/>
+      <c r="U74" s="56"/>
+    </row>
+    <row r="75" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B76" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="67"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="67"/>
+      <c r="G76" s="67"/>
+      <c r="H76" s="67"/>
+      <c r="I76" s="67"/>
+      <c r="J76" s="114"/>
+      <c r="K76" s="68"/>
+      <c r="U76" s="55"/>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77" s="48"/>
+      <c r="D77" s="48"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="109"/>
+      <c r="K77" s="69"/>
+      <c r="U77" s="50"/>
+    </row>
+    <row r="78" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" s="70"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
+      <c r="F78" s="70"/>
+      <c r="G78" s="70"/>
+      <c r="H78" s="70"/>
+      <c r="I78" s="70"/>
+      <c r="J78" s="115"/>
+      <c r="K78" s="71"/>
+      <c r="U78" s="56"/>
+    </row>
+    <row r="79" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="65"/>
+      <c r="F80" s="65"/>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
+      <c r="J80" s="116"/>
+      <c r="K80" s="66"/>
+      <c r="U80" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -15448,16 +18301,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="140" t="s">
+      <c r="H1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15469,15 +18322,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="137"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -17126,15 +19979,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="140"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -17407,21 +20260,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -17433,17 +20286,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -17463,13 +20316,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -17509,10 +20362,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -17520,9 +20373,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -20127,17 +22980,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -20446,21 +23299,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -20472,17 +23325,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -20502,13 +23355,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -20548,10 +23401,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -20559,9 +23412,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -23159,17 +26012,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -23478,21 +26331,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -23504,17 +26357,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -23534,13 +26387,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -23580,10 +26433,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -23591,9 +26444,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -26200,17 +29053,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -26519,21 +29372,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -26545,17 +29398,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -26575,13 +29428,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -26621,10 +29474,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -26632,9 +29485,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -29234,17 +32087,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -29553,21 +32406,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -29579,17 +32432,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -29609,13 +32462,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -29655,10 +32508,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -29666,9 +32519,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -32250,17 +35103,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -32569,21 +35422,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -32595,17 +35448,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -32625,13 +35478,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -32671,10 +35524,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -32682,9 +35535,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -35264,17 +38117,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35583,21 +38436,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="140" t="s">
+      <c r="I1" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35609,17 +38462,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="136" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="135"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="136"/>
+      <c r="D4" s="136"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+      <c r="H4" s="136"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="137"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35639,13 +38492,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="146" t="s">
+      <c r="T4" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="148" t="s">
+      <c r="U4" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="141" t="s">
+      <c r="V4" s="142" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35685,10 +38538,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="143" t="s">
+      <c r="J5" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="144"/>
+      <c r="K5" s="145"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35696,9 +38549,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="149"/>
-      <c r="V5" s="142"/>
+      <c r="T5" s="148"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="143"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38285,17 +41138,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="137" t="s">
+      <c r="C59" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="138"/>
-      <c r="E59" s="138"/>
-      <c r="F59" s="138"/>
-      <c r="G59" s="138"/>
-      <c r="H59" s="138"/>
-      <c r="I59" s="138"/>
-      <c r="J59" s="138"/>
-      <c r="K59" s="139"/>
+      <c r="D59" s="139"/>
+      <c r="E59" s="139"/>
+      <c r="F59" s="139"/>
+      <c r="G59" s="139"/>
+      <c r="H59" s="139"/>
+      <c r="I59" s="139"/>
+      <c r="J59" s="139"/>
+      <c r="K59" s="140"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDBFCF7-637E-4C39-8FAE-BFCD691CC092}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5092D4B5-3648-4E67-877E-B7F353DBECCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="13" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="15" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -27,6 +27,8 @@
     <sheet name="02-13-2026" sheetId="11" r:id="rId12"/>
     <sheet name="02-14-2026" sheetId="21" r:id="rId13"/>
     <sheet name="02-16-2026" sheetId="22" r:id="rId14"/>
+    <sheet name="EXAMPLE" sheetId="23" r:id="rId15"/>
+    <sheet name="02-17-2026" sheetId="24" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -40,9 +42,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="10">'02-12-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'02-13-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'02-14-2026'!$A$1:$W$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'02-16-2026'!$A$1:$W$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'02-16-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'02-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="96">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -341,6 +345,15 @@
   <si>
     <t>DATE: 02/14/2026</t>
   </si>
+  <si>
+    <t xml:space="preserve">DATE: </t>
+  </si>
+  <si>
+    <t>DATE: 02/16/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/17/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -497,7 +510,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="74">
     <border>
       <left/>
       <right/>
@@ -1409,6 +1422,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1416,7 +1480,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1821,6 +1885,33 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="69" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="70" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="71" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="72" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="69" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="73" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3136,34 +3227,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="131" t="s">
+      <c r="B21" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="132"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="131" t="s">
+      <c r="C21" s="141"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="132"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="131" t="s">
+      <c r="F21" s="141"/>
+      <c r="G21" s="142"/>
+      <c r="H21" s="140" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="132"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="131" t="s">
+      <c r="I21" s="141"/>
+      <c r="J21" s="142"/>
+      <c r="K21" s="140" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="132"/>
-      <c r="M21" s="133"/>
-      <c r="N21" s="131" t="s">
+      <c r="L21" s="141"/>
+      <c r="M21" s="142"/>
+      <c r="N21" s="140" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="132"/>
-      <c r="P21" s="133"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="142"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3186,7 +3277,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="135"/>
+      <c r="A22" s="144"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3410,21 +3501,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3436,17 +3527,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3466,13 +3557,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3512,10 +3603,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3523,9 +3614,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6108,17 +6199,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6427,21 +6518,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6453,17 +6544,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6483,13 +6574,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6529,10 +6620,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6540,9 +6631,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9121,17 +9212,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9440,21 +9531,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9466,17 +9557,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9496,13 +9587,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9542,10 +9633,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9553,9 +9644,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12125,17 +12216,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12444,21 +12535,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12470,17 +12561,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12500,13 +12591,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12546,10 +12637,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12557,9 +12648,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15143,17 +15234,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15427,7 +15518,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BB80"/>
+  <dimension ref="A1:BB81"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
@@ -15462,25 +15553,25 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -15488,17 +15579,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15518,13 +15609,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15564,10 +15655,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15575,9 +15666,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15654,32 +15745,44 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="48"/>
+      <c r="C7" s="48">
+        <v>28</v>
+      </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
+      <c r="H7" s="48">
+        <v>17</v>
+      </c>
+      <c r="I7" s="48">
+        <v>1</v>
+      </c>
       <c r="J7" s="109"/>
-      <c r="K7" s="69"/>
+      <c r="K7" s="69">
+        <v>6</v>
+      </c>
       <c r="M7" s="88"/>
       <c r="N7" s="119"/>
-      <c r="O7" s="48"/>
+      <c r="O7" s="48">
+        <v>2</v>
+      </c>
       <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
+      <c r="Q7" s="109">
+        <v>2</v>
+      </c>
       <c r="R7" s="69"/>
       <c r="T7" s="91">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="91">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V7" s="91">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -15714,7 +15817,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="95"/>
+      <c r="C8" s="95">
+        <f>63+31</f>
+        <v>94</v>
+      </c>
       <c r="D8" s="95"/>
       <c r="E8" s="95"/>
       <c r="F8" s="95"/>
@@ -15724,7 +15830,9 @@
       <c r="J8" s="110"/>
       <c r="K8" s="96"/>
       <c r="L8" s="102"/>
-      <c r="M8" s="103"/>
+      <c r="M8" s="103">
+        <v>1</v>
+      </c>
       <c r="N8" s="120"/>
       <c r="O8" s="97"/>
       <c r="P8" s="113"/>
@@ -15732,16 +15840,16 @@
       <c r="R8" s="98"/>
       <c r="S8" s="102"/>
       <c r="T8" s="126">
-        <f t="shared" ref="T8:T40" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
         <v>0</v>
       </c>
       <c r="U8" s="124">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="V8" s="124">
         <f>U8/24</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -15770,7 +15878,7 @@
     </row>
     <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="75">
-        <f t="shared" ref="A9:A56" si="1">A8+1</f>
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
         <v>3</v>
       </c>
       <c r="B9" s="73" t="s">
@@ -15836,7 +15944,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="47">
+        <v>61</v>
+      </c>
       <c r="D10" s="47"/>
       <c r="E10" s="47"/>
       <c r="F10" s="47"/>
@@ -15849,7 +15959,9 @@
       <c r="N10" s="121"/>
       <c r="O10" s="47"/>
       <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
+      <c r="Q10" s="111">
+        <v>3</v>
+      </c>
       <c r="R10" s="46"/>
       <c r="T10" s="91">
         <f t="shared" si="0"/>
@@ -15857,11 +15969,11 @@
       </c>
       <c r="U10" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="V10" s="91">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -15901,10 +16013,14 @@
       <c r="E11" s="47"/>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
+      <c r="H11" s="47">
+        <v>22</v>
+      </c>
       <c r="I11" s="47"/>
       <c r="J11" s="111"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="46">
+        <v>2</v>
+      </c>
       <c r="M11" s="52"/>
       <c r="N11" s="121"/>
       <c r="O11" s="47"/>
@@ -15913,15 +16029,15 @@
       <c r="R11" s="46"/>
       <c r="T11" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="91">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -15954,7 +16070,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="95"/>
+      <c r="C12" s="95">
+        <f>72+1368+53+1440+576</f>
+        <v>3509</v>
+      </c>
       <c r="D12" s="95"/>
       <c r="E12" s="95"/>
       <c r="F12" s="95"/>
@@ -15964,24 +16083,34 @@
       <c r="J12" s="110"/>
       <c r="K12" s="96"/>
       <c r="L12" s="102"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="97"/>
+      <c r="M12" s="103">
+        <v>13</v>
+      </c>
+      <c r="N12" s="120">
+        <v>11</v>
+      </c>
+      <c r="O12" s="97">
+        <v>16</v>
+      </c>
       <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="98"/>
+      <c r="Q12" s="113">
+        <v>13</v>
+      </c>
+      <c r="R12" s="98">
+        <v>16</v>
+      </c>
       <c r="S12" s="102"/>
       <c r="T12" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U12" s="124">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>85251</v>
       </c>
       <c r="V12" s="124">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3552.125</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -16023,7 +16152,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="47"/>
+      <c r="C13" s="47">
+        <v>5</v>
+      </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
@@ -16044,11 +16175,11 @@
       </c>
       <c r="U13" s="125">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="125">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -16259,7 +16390,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="47"/>
+      <c r="C17" s="47">
+        <v>4</v>
+      </c>
       <c r="D17" s="47"/>
       <c r="E17" s="47"/>
       <c r="F17" s="47"/>
@@ -16280,11 +16413,11 @@
       </c>
       <c r="U17" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -16376,7 +16509,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="47">
+        <v>4</v>
+      </c>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="47"/>
@@ -16397,11 +16532,11 @@
       </c>
       <c r="U19" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -16435,7 +16570,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="47"/>
+      <c r="C20" s="47">
+        <v>6</v>
+      </c>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="47"/>
@@ -16456,11 +16593,11 @@
       </c>
       <c r="U20" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -16494,7 +16631,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="47"/>
+      <c r="C21" s="47">
+        <v>4</v>
+      </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="47"/>
@@ -16515,11 +16654,11 @@
       </c>
       <c r="U21" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -16553,7 +16692,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="47"/>
+      <c r="C22" s="47">
+        <v>2</v>
+      </c>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="47"/>
@@ -16576,11 +16717,11 @@
       </c>
       <c r="U22" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -16623,7 +16764,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="47"/>
+      <c r="C23" s="47">
+        <v>48</v>
+      </c>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
       <c r="F23" s="47"/>
@@ -16646,11 +16789,11 @@
       </c>
       <c r="U23" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -16685,15 +16828,17 @@
       <c r="BA23" s="60"/>
       <c r="BB23" s="60"/>
     </row>
-    <row r="24" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="75">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B24" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="47"/>
+        <v>67</v>
+      </c>
+      <c r="C24" s="47">
+        <v>7</v>
+      </c>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
       <c r="F24" s="47"/>
@@ -16702,35 +16847,24 @@
       <c r="I24" s="47"/>
       <c r="J24" s="111"/>
       <c r="K24" s="46"/>
-      <c r="L24" s="57"/>
       <c r="M24" s="52"/>
       <c r="N24" s="121"/>
       <c r="O24" s="47"/>
       <c r="P24" s="111"/>
       <c r="Q24" s="111"/>
       <c r="R24" s="46"/>
-      <c r="S24" s="57"/>
       <c r="T24" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U24" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W24" s="57"/>
-      <c r="X24" s="57"/>
-      <c r="Y24" s="57"/>
-      <c r="Z24" s="57"/>
-      <c r="AA24" s="57"/>
-      <c r="AB24" s="57"/>
-      <c r="AC24" s="57"/>
-      <c r="AD24" s="57"/>
-      <c r="AE24" s="57"/>
+        <v>7</v>
+      </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
       <c r="AH24" s="60"/>
@@ -16761,66 +16895,60 @@
         <v>22</v>
       </c>
       <c r="B25" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="47"/>
+        <v>9</v>
+      </c>
+      <c r="C25" s="47">
+        <f>63+21</f>
+        <v>84</v>
+      </c>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
       <c r="F25" s="47"/>
       <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
+      <c r="H25" s="47">
+        <v>22</v>
+      </c>
+      <c r="I25" s="47">
+        <v>1</v>
+      </c>
       <c r="J25" s="111"/>
       <c r="K25" s="46"/>
-      <c r="M25" s="52"/>
+      <c r="M25" s="52">
+        <v>1</v>
+      </c>
       <c r="N25" s="121"/>
-      <c r="O25" s="47"/>
+      <c r="O25" s="47">
+        <v>2</v>
+      </c>
       <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
+      <c r="Q25" s="111">
+        <v>2</v>
+      </c>
       <c r="R25" s="46"/>
       <c r="T25" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U25" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2159</v>
       </c>
       <c r="V25" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="60"/>
-      <c r="AG25" s="60"/>
-      <c r="AH25" s="60"/>
-      <c r="AI25" s="60"/>
-      <c r="AJ25" s="60"/>
-      <c r="AK25" s="60"/>
-      <c r="AL25" s="60"/>
-      <c r="AM25" s="60"/>
-      <c r="AN25" s="60"/>
-      <c r="AO25" s="60"/>
-      <c r="AP25" s="60"/>
-      <c r="AQ25" s="60"/>
-      <c r="AR25" s="60"/>
-      <c r="AS25" s="60"/>
-      <c r="AT25" s="60"/>
-      <c r="AU25" s="60"/>
-      <c r="AV25" s="60"/>
-      <c r="AW25" s="60"/>
-      <c r="AX25" s="60"/>
-      <c r="AY25" s="60"/>
-      <c r="AZ25" s="60"/>
-      <c r="BA25" s="60"/>
-      <c r="BB25" s="60"/>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
+        <v>89.958333333333329</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="75">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B26" s="74" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -16831,12 +16959,14 @@
       <c r="I26" s="47"/>
       <c r="J26" s="111"/>
       <c r="K26" s="46"/>
+      <c r="L26" s="57"/>
       <c r="M26" s="52"/>
       <c r="N26" s="121"/>
       <c r="O26" s="47"/>
       <c r="P26" s="111"/>
       <c r="Q26" s="111"/>
       <c r="R26" s="46"/>
+      <c r="S26" s="57"/>
       <c r="T26" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -16849,10 +16979,15 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY26" s="62" t="e">
-        <f>#REF!-AY25</f>
-        <v>#REF!</v>
-      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
     </row>
     <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="75">
@@ -16860,7 +16995,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="74" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -16879,18 +17014,9 @@
       <c r="Q27" s="111"/>
       <c r="R27" s="46"/>
       <c r="S27" s="57"/>
-      <c r="T27" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="50">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V27" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="T27" s="91"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
       <c r="W27" s="57"/>
       <c r="X27" s="57"/>
       <c r="Y27" s="57"/>
@@ -16909,7 +17035,9 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="47"/>
+      <c r="C28" s="47">
+        <v>33</v>
+      </c>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
       <c r="F28" s="47"/>
@@ -16919,11 +17047,17 @@
       <c r="J28" s="111"/>
       <c r="K28" s="46"/>
       <c r="L28" s="57"/>
-      <c r="M28" s="52"/>
+      <c r="M28" s="52">
+        <v>10</v>
+      </c>
       <c r="N28" s="121"/>
-      <c r="O28" s="47"/>
+      <c r="O28" s="47">
+        <v>4</v>
+      </c>
       <c r="P28" s="111"/>
-      <c r="Q28" s="111"/>
+      <c r="Q28" s="111">
+        <v>3</v>
+      </c>
       <c r="R28" s="46"/>
       <c r="S28" s="57"/>
       <c r="T28" s="91">
@@ -16932,11 +17066,11 @@
       </c>
       <c r="U28" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="V28" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -16992,7 +17126,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="47"/>
+      <c r="C30" s="47">
+        <v>62</v>
+      </c>
       <c r="D30" s="47"/>
       <c r="E30" s="47"/>
       <c r="F30" s="47"/>
@@ -17003,9 +17139,13 @@
       <c r="K30" s="46"/>
       <c r="M30" s="52"/>
       <c r="N30" s="121"/>
-      <c r="O30" s="47"/>
+      <c r="O30" s="47">
+        <v>1</v>
+      </c>
       <c r="P30" s="111"/>
-      <c r="Q30" s="111"/>
+      <c r="Q30" s="111">
+        <v>1</v>
+      </c>
       <c r="R30" s="46"/>
       <c r="T30" s="91">
         <f t="shared" si="0"/>
@@ -17013,11 +17153,11 @@
       </c>
       <c r="U30" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="V30" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -17136,32 +17276,45 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="47"/>
+      <c r="C34" s="47">
+        <f>19+8+72</f>
+        <v>99</v>
+      </c>
       <c r="D34" s="47"/>
       <c r="E34" s="47"/>
       <c r="F34" s="47"/>
       <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
+      <c r="H34" s="47">
+        <v>16</v>
+      </c>
       <c r="I34" s="47"/>
       <c r="J34" s="111"/>
-      <c r="K34" s="46"/>
-      <c r="M34" s="52"/>
+      <c r="K34" s="46">
+        <v>1</v>
+      </c>
+      <c r="M34" s="52">
+        <v>5</v>
+      </c>
       <c r="N34" s="121"/>
-      <c r="O34" s="47"/>
+      <c r="O34" s="47">
+        <v>2</v>
+      </c>
       <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
+      <c r="Q34" s="111">
+        <v>3</v>
+      </c>
       <c r="R34" s="46"/>
       <c r="T34" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U34" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2633</v>
       </c>
       <c r="V34" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>109.70833333333333</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -17244,34 +17397,49 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="95"/>
+      <c r="C37" s="95">
+        <f>2376+1944</f>
+        <v>4320</v>
+      </c>
       <c r="D37" s="95"/>
       <c r="E37" s="95"/>
       <c r="F37" s="95"/>
       <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
+      <c r="H37" s="95">
+        <v>2</v>
+      </c>
       <c r="I37" s="95"/>
-      <c r="J37" s="110"/>
-      <c r="K37" s="96"/>
+      <c r="J37" s="110">
+        <v>4</v>
+      </c>
+      <c r="K37" s="96">
+        <v>2</v>
+      </c>
       <c r="L37" s="102"/>
-      <c r="M37" s="103"/>
+      <c r="M37" s="103">
+        <v>108</v>
+      </c>
       <c r="N37" s="120"/>
-      <c r="O37" s="97"/>
+      <c r="O37" s="97">
+        <v>34</v>
+      </c>
       <c r="P37" s="113"/>
-      <c r="Q37" s="113"/>
+      <c r="Q37" s="113">
+        <v>72</v>
+      </c>
       <c r="R37" s="98"/>
       <c r="S37" s="102"/>
       <c r="T37" s="104">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="104">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>27212</v>
       </c>
       <c r="V37" s="104">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4535.333333333333</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -17283,7 +17451,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="47"/>
+      <c r="C38" s="47">
+        <f>1+3</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="47"/>
       <c r="E38" s="47"/>
       <c r="F38" s="47"/>
@@ -17304,188 +17475,223 @@
       </c>
       <c r="U38" s="50">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="50">
         <f>U38/24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="75">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B39" s="94" t="s">
-        <v>22</v>
-      </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
-      <c r="I39" s="95"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="102"/>
-      <c r="M39" s="103"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="97"/>
-      <c r="P39" s="113"/>
-      <c r="Q39" s="113"/>
-      <c r="R39" s="98"/>
-      <c r="S39" s="102"/>
-      <c r="T39" s="104">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U39" s="104">
-        <f>C39*24+M39*24+O39*24+Q39*24+T39</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="104">
-        <f>U39/24</f>
-        <v>0</v>
-      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="75">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B40" s="99" t="s">
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="95">
+        <f>2+693</f>
+        <v>695</v>
+      </c>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95">
+        <v>9</v>
+      </c>
+      <c r="I40" s="95"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="96">
+        <v>15</v>
+      </c>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113">
+        <v>2</v>
+      </c>
+      <c r="R40" s="98"/>
+      <c r="S40" s="102"/>
+      <c r="T40" s="104">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="104">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>16752</v>
+      </c>
+      <c r="V40" s="104">
+        <f>U40/24</f>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="100"/>
-      <c r="D40" s="100"/>
-      <c r="E40" s="100"/>
-      <c r="F40" s="100"/>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="100"/>
-      <c r="J40" s="112"/>
-      <c r="K40" s="101"/>
-      <c r="L40" s="105"/>
-      <c r="M40" s="106"/>
-      <c r="N40" s="122"/>
-      <c r="O40" s="100"/>
-      <c r="P40" s="112"/>
-      <c r="Q40" s="112"/>
-      <c r="R40" s="101"/>
-      <c r="S40" s="105"/>
-      <c r="T40" s="107">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="107">
-        <f>C40*12+M40*12+O40*12+Q40*12+T40</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="107">
-        <f>U40/12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="75">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B41" s="73" t="s">
+      <c r="C41" s="100">
+        <f>1632+25</f>
+        <v>1657</v>
+      </c>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="112"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="100">
+        <v>6</v>
+      </c>
+      <c r="P41" s="112"/>
+      <c r="Q41" s="112">
+        <v>15</v>
+      </c>
+      <c r="R41" s="101"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="107">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>20136</v>
+      </c>
+      <c r="V41" s="107">
+        <f>U41/12</f>
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="111"/>
-      <c r="K41" s="46"/>
-      <c r="M41" s="52"/>
-      <c r="N41" s="121"/>
-      <c r="O41" s="47"/>
-      <c r="P41" s="111"/>
-      <c r="Q41" s="111"/>
-      <c r="R41" s="46"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="50"/>
-      <c r="V41" s="50"/>
-    </row>
-    <row r="42" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="75">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B42" s="94" t="s">
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="46"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="46"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="97"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="97"/>
-      <c r="F42" s="97"/>
-      <c r="G42" s="97"/>
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="98"/>
-      <c r="L42" s="102"/>
-      <c r="M42" s="103"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="97"/>
-      <c r="P42" s="113"/>
-      <c r="Q42" s="113"/>
-      <c r="R42" s="98"/>
-      <c r="S42" s="102"/>
-      <c r="T42" s="104">
-        <f t="shared" ref="T42" si="6">H42+I42+J42+K42+N42+P42+R42</f>
-        <v>0</v>
-      </c>
-      <c r="U42" s="104">
-        <f>C42*6+M42*6+O42*6+Q42*6+T42</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="104">
-        <f>U42/6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="75">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B43" s="73" t="s">
+      <c r="C43" s="97">
+        <f>6048+6048+864+5400+7128+46+1836</f>
+        <v>27370</v>
+      </c>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97">
+        <v>1</v>
+      </c>
+      <c r="I43" s="97">
+        <v>6</v>
+      </c>
+      <c r="J43" s="113">
+        <f>9*6+5</f>
+        <v>59</v>
+      </c>
+      <c r="K43" s="98">
+        <f>75*6+4</f>
+        <v>454</v>
+      </c>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103">
+        <v>224</v>
+      </c>
+      <c r="N43" s="120"/>
+      <c r="O43" s="97">
+        <v>474</v>
+      </c>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113">
+        <v>411</v>
+      </c>
+      <c r="R43" s="98"/>
+      <c r="S43" s="102"/>
+      <c r="T43" s="104">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>520</v>
+      </c>
+      <c r="U43" s="104">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>171394</v>
+      </c>
+      <c r="V43" s="104">
+        <f>U43/6</f>
+        <v>28565.666666666668</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
         <v>33</v>
-      </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="111"/>
-      <c r="K43" s="46"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="121"/>
-      <c r="O43" s="47"/>
-      <c r="P43" s="111"/>
-      <c r="Q43" s="111"/>
-      <c r="R43" s="46"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="75">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B44" s="74" t="s">
-        <v>25</v>
       </c>
       <c r="C44" s="47"/>
       <c r="D44" s="47"/>
@@ -17502,18 +17708,9 @@
       <c r="P44" s="111"/>
       <c r="Q44" s="111"/>
       <c r="R44" s="46"/>
-      <c r="T44" s="50">
-        <f t="shared" ref="T44:T53" si="7">H44+I44+J44+K44+N44+P44+R44</f>
-        <v>0</v>
-      </c>
-      <c r="U44" s="50">
-        <f>C44*24+M44*24+O44*24+Q44*24+T44</f>
-        <v>0</v>
-      </c>
-      <c r="V44" s="50">
-        <f>U44/24</f>
-        <v>0</v>
-      </c>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="75">
@@ -17521,7 +17718,7 @@
         <v>42</v>
       </c>
       <c r="B45" s="74" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
@@ -17539,15 +17736,15 @@
       <c r="Q45" s="111"/>
       <c r="R45" s="46"/>
       <c r="T45" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
         <v>0</v>
       </c>
       <c r="U45" s="50">
-        <f t="shared" ref="U45:U47" si="8">C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
         <v>0</v>
       </c>
       <c r="V45" s="50">
-        <f t="shared" ref="V45:V53" si="9">U45/24</f>
+        <f>U45/24</f>
         <v>0</v>
       </c>
     </row>
@@ -17557,7 +17754,7 @@
         <v>43</v>
       </c>
       <c r="B46" s="74" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C46" s="47"/>
       <c r="D46" s="47"/>
@@ -17579,11 +17776,11 @@
         <v>0</v>
       </c>
       <c r="U46" s="50">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="U46:U48" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
         <v>0</v>
       </c>
       <c r="V46" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
         <v>0</v>
       </c>
     </row>
@@ -17593,34 +17790,50 @@
         <v>44</v>
       </c>
       <c r="B47" s="74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="47"/>
+        <v>26</v>
+      </c>
+      <c r="C47" s="47">
+        <f>24+44+2268</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="47"/>
       <c r="E47" s="47"/>
       <c r="F47" s="47"/>
       <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
+      <c r="H47" s="47">
+        <v>3</v>
+      </c>
       <c r="I47" s="47"/>
       <c r="J47" s="111"/>
-      <c r="K47" s="46"/>
-      <c r="M47" s="52"/>
+      <c r="K47" s="46">
+        <f>1*6</f>
+        <v>6</v>
+      </c>
+      <c r="M47" s="52">
+        <v>10</v>
+      </c>
       <c r="N47" s="121"/>
-      <c r="O47" s="47"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
+      <c r="O47" s="47">
+        <v>8</v>
+      </c>
+      <c r="P47" s="111">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="111">
+        <v>10</v>
+      </c>
       <c r="R47" s="46"/>
       <c r="T47" s="50">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U47" s="50">
-        <f t="shared" si="8"/>
-        <v>0</v>
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>14195</v>
       </c>
       <c r="V47" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>U47/6</f>
+        <v>2365.8333333333335</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -17629,7 +17842,7 @@
         <v>45</v>
       </c>
       <c r="B48" s="74" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C48" s="47"/>
       <c r="D48" s="47"/>
@@ -17651,11 +17864,11 @@
         <v>0</v>
       </c>
       <c r="U48" s="50">
-        <f>C48*6+M48*6+O48*6+Q48*6+T48</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V48" s="50">
-        <f>U48/6</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -17665,7 +17878,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="74" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="C49" s="47"/>
       <c r="D49" s="47"/>
@@ -17683,15 +17896,15 @@
       <c r="Q49" s="111"/>
       <c r="R49" s="46"/>
       <c r="T49" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="T49:T50" si="10">H49+I49+J49+K49+N49+P49+R49</f>
         <v>0</v>
       </c>
       <c r="U49" s="50">
-        <f t="shared" ref="U49:U51" si="10">C49*24+M49*24+O49*24+Q49*24+T49</f>
+        <f t="shared" ref="U49:U50" si="11">C49*24+M49*24+O49*24+Q49*24+T49</f>
         <v>0</v>
       </c>
       <c r="V49" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="V49:V50" si="12">U49/24</f>
         <v>0</v>
       </c>
     </row>
@@ -17701,7 +17914,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="74" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="C50" s="47"/>
       <c r="D50" s="47"/>
@@ -17719,15 +17932,15 @@
       <c r="Q50" s="111"/>
       <c r="R50" s="46"/>
       <c r="T50" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U50" s="50">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V50" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -17737,9 +17950,11 @@
         <v>48</v>
       </c>
       <c r="B51" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="47"/>
+        <v>29</v>
+      </c>
+      <c r="C51" s="47">
+        <v>34</v>
+      </c>
       <c r="D51" s="47"/>
       <c r="E51" s="47"/>
       <c r="F51" s="47"/>
@@ -17755,16 +17970,16 @@
       <c r="Q51" s="111"/>
       <c r="R51" s="46"/>
       <c r="T51" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="T51" si="13">H51+I51+J51+K51+N51+P51+R51</f>
         <v>0</v>
       </c>
       <c r="U51" s="50">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
       </c>
       <c r="V51" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>U51/6</f>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -17773,7 +17988,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
@@ -17795,11 +18010,11 @@
         <v>0</v>
       </c>
       <c r="U52" s="50">
-        <f>C52*6+M52*6+O52*6+Q52*6+T52</f>
+        <f t="shared" ref="U50:U52" si="14">C52*24+M52*24+O52*24+Q52*24+T52</f>
         <v>0</v>
       </c>
       <c r="V52" s="50">
-        <f>U52/6</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -17809,9 +18024,11 @@
         <v>50</v>
       </c>
       <c r="B53" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53" s="47"/>
+        <v>75</v>
+      </c>
+      <c r="C53" s="47">
+        <v>2</v>
+      </c>
       <c r="D53" s="47"/>
       <c r="E53" s="47"/>
       <c r="F53" s="47"/>
@@ -17827,16 +18044,16 @@
       <c r="Q53" s="111"/>
       <c r="R53" s="46"/>
       <c r="T53" s="50">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="T53" si="15">H53+I53+J53+K53+N53+P53+R53</f>
         <v>0</v>
       </c>
       <c r="U53" s="50">
-        <f t="shared" ref="U53" si="11">C53*24+M53*24+O53*24+Q53*24+T53</f>
-        <v>0</v>
+        <f t="shared" ref="U53" si="16">C53*24+M53*24+O53*24+Q53*24+T53</f>
+        <v>48</v>
       </c>
       <c r="V53" s="50">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" ref="V53" si="17">U53/24</f>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -17860,9 +18077,18 @@
       <c r="P54" s="111"/>
       <c r="Q54" s="111"/>
       <c r="R54" s="46"/>
-      <c r="T54" s="50"/>
-      <c r="U54" s="50"/>
-      <c r="V54" s="50"/>
+      <c r="T54" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="50">
+        <f t="shared" ref="U54" si="18">C54*24+M54*24+O54*24+Q54*24+T54</f>
+        <v>0</v>
+      </c>
+      <c r="V54" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="75">
@@ -17914,346 +18140,6053 @@
       <c r="U56" s="50"/>
       <c r="V56" s="50"/>
     </row>
-    <row r="57" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="77" t="s">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="46"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="46"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="49">
-        <f>SUM(C7:C56)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
-      <c r="F57" s="49">
-        <f t="shared" ref="F57:K57" si="12">SUM(F7:F56)</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="49">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="49">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I57" s="54">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="54">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="54">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="53">
-        <f t="shared" ref="M57:R57" si="13">SUM(M7:M56)</f>
-        <v>0</v>
-      </c>
-      <c r="N57" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="O57" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="R57" s="53">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="57"/>
-      <c r="T57" s="51">
-        <f>SUM(T7:T56)</f>
-        <v>0</v>
-      </c>
-      <c r="U57" s="51">
-        <f>SUM(U7:U56)</f>
-        <v>0</v>
-      </c>
-      <c r="V57" s="51">
-        <f>SUM(V7:V56)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="78" t="s">
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>40468</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="19">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="19"/>
+        <v>92</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="19"/>
+        <v>8</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="19"/>
+        <v>63</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="19"/>
+        <v>486</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="20">SUM(M7:M57)</f>
+        <v>372</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="20"/>
+        <v>11</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="20"/>
+        <v>549</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="20"/>
+        <v>2</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="20"/>
+        <v>537</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="20"/>
+        <v>16</v>
+      </c>
+      <c r="S58" s="57"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>678</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>349368</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>42021.625000000007</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C60" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
-      <c r="U59" s="72" t="s">
+      <c r="D60" s="148"/>
+      <c r="E60" s="148"/>
+      <c r="F60" s="148"/>
+      <c r="G60" s="148"/>
+      <c r="H60" s="148"/>
+      <c r="I60" s="148"/>
+      <c r="J60" s="148"/>
+      <c r="K60" s="149"/>
+      <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B60" s="79" t="s">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="114"/>
-      <c r="K60" s="68"/>
-      <c r="U60" s="55"/>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B61" s="80" t="s">
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="48"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="109"/>
-      <c r="K61" s="69"/>
-      <c r="U61" s="50"/>
-    </row>
-    <row r="62" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="81" t="s">
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="70"/>
-      <c r="D62" s="70"/>
-      <c r="E62" s="70"/>
-      <c r="F62" s="70"/>
-      <c r="G62" s="70"/>
-      <c r="H62" s="70"/>
-      <c r="I62" s="70"/>
-      <c r="J62" s="115"/>
-      <c r="K62" s="71"/>
-      <c r="U62" s="56"/>
-    </row>
-    <row r="63" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="79" t="s">
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="67"/>
-      <c r="I64" s="67"/>
-      <c r="J64" s="114"/>
-      <c r="K64" s="68"/>
-      <c r="U64" s="55"/>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B65" s="80" t="s">
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="48"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="109"/>
-      <c r="K65" s="69"/>
-      <c r="U65" s="50"/>
-    </row>
-    <row r="66" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="81" t="s">
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C66" s="70"/>
-      <c r="D66" s="70"/>
-      <c r="E66" s="70"/>
-      <c r="F66" s="70"/>
-      <c r="G66" s="70"/>
-      <c r="H66" s="70"/>
-      <c r="I66" s="70"/>
-      <c r="J66" s="115"/>
-      <c r="K66" s="71"/>
-      <c r="U66" s="56"/>
-    </row>
-    <row r="67" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B68" s="79" t="s">
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="114"/>
-      <c r="K68" s="68"/>
-      <c r="U68" s="55"/>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B69" s="80" t="s">
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="48"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="109"/>
-      <c r="K69" s="69"/>
-      <c r="U69" s="50"/>
-    </row>
-    <row r="70" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="81" t="s">
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C70" s="70"/>
-      <c r="D70" s="70"/>
-      <c r="E70" s="70"/>
-      <c r="F70" s="70"/>
-      <c r="G70" s="70"/>
-      <c r="H70" s="70"/>
-      <c r="I70" s="70"/>
-      <c r="J70" s="115"/>
-      <c r="K70" s="71"/>
-      <c r="U70" s="56"/>
-    </row>
-    <row r="71" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B72" s="79" t="s">
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
-      <c r="E72" s="67"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="114"/>
-      <c r="K72" s="68"/>
-      <c r="U72" s="55"/>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B73" s="80" t="s">
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="109"/>
-      <c r="K73" s="69"/>
-      <c r="U73" s="50"/>
-    </row>
-    <row r="74" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="81" t="s">
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C74" s="70"/>
-      <c r="D74" s="70"/>
-      <c r="E74" s="70"/>
-      <c r="F74" s="70"/>
-      <c r="G74" s="70"/>
-      <c r="H74" s="70"/>
-      <c r="I74" s="70"/>
-      <c r="J74" s="115"/>
-      <c r="K74" s="71"/>
-      <c r="U74" s="56"/>
-    </row>
-    <row r="75" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B76" s="79" t="s">
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C76" s="67"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="114"/>
-      <c r="K76" s="68"/>
-      <c r="U76" s="55"/>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B77" s="80" t="s">
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C77" s="48"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="109"/>
-      <c r="K77" s="69"/>
-      <c r="U77" s="50"/>
-    </row>
-    <row r="78" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="81" t="s">
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C78" s="70"/>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
-      <c r="F78" s="70"/>
-      <c r="G78" s="70"/>
-      <c r="H78" s="70"/>
-      <c r="I78" s="70"/>
-      <c r="J78" s="115"/>
-      <c r="K78" s="71"/>
-      <c r="U78" s="56"/>
-    </row>
-    <row r="79" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="78" t="s">
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="C80" s="65"/>
-      <c r="D80" s="65"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-      <c r="J80" s="116"/>
-      <c r="K80" s="66"/>
-      <c r="U80" s="64"/>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B979239-8777-43F5-9407-4159B48ED3EF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="150" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="145" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="156" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="158" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="151" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="153" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="154"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="131"/>
+      <c r="Q5" s="131"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="131"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="131"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="69"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="69"/>
+      <c r="T7" s="91">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="91">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="91">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="126">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="124">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="46"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="46"/>
+      <c r="T9" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="125">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="125">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="46"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="46"/>
+      <c r="T10" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="46"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="46"/>
+      <c r="T11" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="124">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="124">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="46"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="46"/>
+      <c r="T13" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="125">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="125">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="46"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="46"/>
+      <c r="T14" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="46"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="46"/>
+      <c r="T15" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="46"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="46"/>
+      <c r="T16" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="46"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="46"/>
+      <c r="T17" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="46"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="46"/>
+      <c r="T18" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="46"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="46"/>
+      <c r="T19" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="46"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="46"/>
+      <c r="T20" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="46"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="46"/>
+      <c r="T21" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="46"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="46"/>
+      <c r="T24" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="46"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="46"/>
+      <c r="T25" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="46"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="46"/>
+      <c r="T29" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="46"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="46"/>
+      <c r="T30" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="46"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="46"/>
+      <c r="T31" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="46"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="46"/>
+      <c r="T32" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="46"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="46"/>
+      <c r="T33" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="46"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="46"/>
+      <c r="T34" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="46"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="46"/>
+      <c r="T35" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="46"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="46"/>
+      <c r="T36" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="97"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="98"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="104">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="104">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="46"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="46"/>
+      <c r="T38" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="50">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="50">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="98"/>
+      <c r="S40" s="102"/>
+      <c r="T40" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="104">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="104">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="100"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="112"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="112"/>
+      <c r="Q41" s="112"/>
+      <c r="R41" s="101"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="107">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="107">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="46"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="46"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="97"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97"/>
+      <c r="I43" s="97"/>
+      <c r="J43" s="113"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="97"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113"/>
+      <c r="R43" s="98"/>
+      <c r="S43" s="102"/>
+      <c r="T43" s="104">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="104">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="104">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="46"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111"/>
+      <c r="R44" s="46"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="46"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="46"/>
+      <c r="T45" s="50">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="50">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="50">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="46"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="46"/>
+      <c r="T46" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="50">
+        <f t="shared" ref="U46:U48" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="50">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="46"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="111"/>
+      <c r="Q47" s="111"/>
+      <c r="R47" s="46"/>
+      <c r="T47" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="46"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="111"/>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="46"/>
+      <c r="T48" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="46"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="46"/>
+      <c r="T49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="50">
+        <f>C49*6+M49*6+O49*6+Q49*6+T49</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="50">
+        <f>U49/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="46"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="111"/>
+      <c r="Q50" s="111"/>
+      <c r="R50" s="46"/>
+      <c r="T50" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="50">
+        <f t="shared" ref="U50:U52" si="10">C50*24+M50*24+O50*24+Q50*24+T50</f>
+        <v>0</v>
+      </c>
+      <c r="V50" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="46"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="46"/>
+      <c r="T51" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="46"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="111"/>
+      <c r="R52" s="46"/>
+      <c r="T52" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V52" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="46"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="111"/>
+      <c r="Q53" s="111"/>
+      <c r="R53" s="46"/>
+      <c r="T53" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="50">
+        <f>C53*6+M53*6+O53*6+Q53*6+T53</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="50">
+        <f>U53/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="46"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="46"/>
+      <c r="T54" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="50">
+        <f t="shared" ref="U54" si="11">C54*24+M54*24+O54*24+Q54*24+T54</f>
+        <v>0</v>
+      </c>
+      <c r="V54" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="46"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="46"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="46"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="46"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="50"/>
+      <c r="V56" s="50"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="46"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="46"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="12">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="13">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="57"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="147" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="148"/>
+      <c r="E60" s="148"/>
+      <c r="F60" s="148"/>
+      <c r="G60" s="148"/>
+      <c r="H60" s="148"/>
+      <c r="I60" s="148"/>
+      <c r="J60" s="148"/>
+      <c r="K60" s="149"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="14" scale="55" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1E6D21-8432-42F5-A0EA-128BF8928235}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="150" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="145" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="156" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="158" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="151" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="153" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="154"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="139"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="139"/>
+      <c r="Q6" s="139"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="69"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="69"/>
+      <c r="T7" s="91">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="91">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="91">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="126">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="124">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="46"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="46"/>
+      <c r="T9" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="125">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="125">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="46"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="46"/>
+      <c r="T10" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="46"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="46"/>
+      <c r="T11" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="124">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="124">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="46"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="46"/>
+      <c r="T13" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="125">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="125">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="46"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="46"/>
+      <c r="T14" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="46"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="46"/>
+      <c r="T15" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="46"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="46"/>
+      <c r="T16" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="46"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="46"/>
+      <c r="T17" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="46"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="46"/>
+      <c r="T18" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="46"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="46"/>
+      <c r="T19" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="46"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="46"/>
+      <c r="T20" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="46"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="46"/>
+      <c r="T21" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="46"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="46"/>
+      <c r="T24" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="46"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="46"/>
+      <c r="T25" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="47"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="46"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="46"/>
+      <c r="T29" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="46"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="46"/>
+      <c r="T30" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="46"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="46"/>
+      <c r="T31" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="46"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="46"/>
+      <c r="T32" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="46"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="46"/>
+      <c r="T33" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="47"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="46"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="121"/>
+      <c r="O34" s="47"/>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="46"/>
+      <c r="T34" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="46"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="46"/>
+      <c r="T35" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="46"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="46"/>
+      <c r="T36" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="120"/>
+      <c r="O37" s="97"/>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="98"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="104">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="104">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="46"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="46"/>
+      <c r="T38" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="50">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="50">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="98"/>
+      <c r="S40" s="102"/>
+      <c r="T40" s="104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="104">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="104">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="100"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="112"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106"/>
+      <c r="N41" s="122"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="112"/>
+      <c r="Q41" s="112"/>
+      <c r="R41" s="101"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="107">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="107">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="46"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="46"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="97"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97"/>
+      <c r="I43" s="97"/>
+      <c r="J43" s="113"/>
+      <c r="K43" s="98"/>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="120"/>
+      <c r="O43" s="97"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113"/>
+      <c r="R43" s="98"/>
+      <c r="S43" s="102"/>
+      <c r="T43" s="104">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="104">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="104">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="46"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111"/>
+      <c r="R44" s="46"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="46"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="46"/>
+      <c r="T45" s="50">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="50">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="50">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="46"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="46"/>
+      <c r="T46" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="50">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="50">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="46"/>
+      <c r="M47" s="52"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="47"/>
+      <c r="P47" s="111"/>
+      <c r="Q47" s="111"/>
+      <c r="R47" s="46"/>
+      <c r="T47" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="50">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="50">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="46"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="111"/>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="46"/>
+      <c r="T48" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="46"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="46"/>
+      <c r="T49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="46"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="111"/>
+      <c r="Q50" s="111"/>
+      <c r="R50" s="46"/>
+      <c r="T50" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="46"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="46"/>
+      <c r="T51" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="50">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="50">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="46"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="111"/>
+      <c r="R52" s="46"/>
+      <c r="T52" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="50">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="46"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="111"/>
+      <c r="Q53" s="111"/>
+      <c r="R53" s="46"/>
+      <c r="T53" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="46"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="46"/>
+      <c r="T54" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="46"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="46"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="46"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="46"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="50"/>
+      <c r="V56" s="50"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="46"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="46"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="57"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="147" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="148"/>
+      <c r="E60" s="148"/>
+      <c r="F60" s="148"/>
+      <c r="G60" s="148"/>
+      <c r="H60" s="148"/>
+      <c r="I60" s="148"/>
+      <c r="J60" s="148"/>
+      <c r="K60" s="149"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
@@ -18301,16 +24234,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="141" t="s">
+      <c r="H1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="141"/>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18322,15 +24255,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="146"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -19979,15 +25912,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="149"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -20260,21 +26193,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -20286,17 +26219,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -20316,13 +26249,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -20362,10 +26295,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -20373,9 +26306,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -22980,17 +28913,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -23299,21 +29232,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -23325,17 +29258,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -23355,13 +29288,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -23401,10 +29334,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -23412,9 +29345,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -26012,17 +31945,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -26331,21 +32264,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -26357,17 +32290,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -26387,13 +32320,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -26433,10 +32366,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -26444,9 +32377,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -29053,17 +34986,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -29372,21 +35305,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -29398,17 +35331,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -29428,13 +35361,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -29474,10 +35407,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -29485,9 +35418,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -32087,17 +38020,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -32406,21 +38339,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -32432,17 +38365,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -32462,13 +38395,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -32508,10 +38441,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -32519,9 +38452,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -35103,17 +41036,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35422,21 +41355,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35448,17 +41381,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35478,13 +41411,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35524,10 +41457,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35535,9 +41468,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38117,17 +44050,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -38436,21 +44369,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="141" t="s">
+      <c r="I1" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="141"/>
-      <c r="K1" s="141"/>
-      <c r="L1" s="141"/>
-      <c r="M1" s="141"/>
-      <c r="N1" s="141"/>
-      <c r="O1" s="141"/>
-      <c r="P1" s="141"/>
-      <c r="Q1" s="141"/>
-      <c r="R1" s="141"/>
-      <c r="S1" s="141"/>
-      <c r="T1" s="141"/>
-      <c r="U1" s="141"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38462,17 +44395,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="C4" s="145" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="137"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="155"/>
+      <c r="K4" s="146"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38492,13 +44425,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="147" t="s">
+      <c r="T4" s="156" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="149" t="s">
+      <c r="U4" s="158" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="142" t="s">
+      <c r="V4" s="151" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38538,10 +44471,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="144" t="s">
+      <c r="J5" s="153" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="145"/>
+      <c r="K5" s="154"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38549,9 +44482,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="148"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="143"/>
+      <c r="T5" s="157"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="152"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41138,17 +47071,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="138" t="s">
+      <c r="C59" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="139"/>
-      <c r="E59" s="139"/>
-      <c r="F59" s="139"/>
-      <c r="G59" s="139"/>
-      <c r="H59" s="139"/>
-      <c r="I59" s="139"/>
-      <c r="J59" s="139"/>
-      <c r="K59" s="140"/>
+      <c r="D59" s="148"/>
+      <c r="E59" s="148"/>
+      <c r="F59" s="148"/>
+      <c r="G59" s="148"/>
+      <c r="H59" s="148"/>
+      <c r="I59" s="148"/>
+      <c r="J59" s="148"/>
+      <c r="K59" s="149"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5092D4B5-3648-4E67-877E-B7F353DBECCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC97E699-789D-44A1-A7E5-16AA9AF86CF5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="6" activeTab="15" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -28,7 +28,8 @@
     <sheet name="02-14-2026" sheetId="21" r:id="rId13"/>
     <sheet name="02-16-2026" sheetId="22" r:id="rId14"/>
     <sheet name="EXAMPLE" sheetId="23" r:id="rId15"/>
-    <sheet name="02-17-2026" sheetId="24" r:id="rId16"/>
+    <sheet name="02-17-2026" sheetId="25" r:id="rId16"/>
+    <sheet name="02-18-2026" sheetId="24" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -44,6 +45,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'02-14-2026'!$A$1:$W$58</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'02-16-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'02-17-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'02-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="97">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -353,6 +355,9 @@
   </si>
   <si>
     <t>DATE: 02/17/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/18/2026</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1485,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1912,6 +1917,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3227,34 +3235,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="143" t="s">
+      <c r="A21" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="140" t="s">
+      <c r="B21" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="140" t="s">
+      <c r="C21" s="142"/>
+      <c r="D21" s="143"/>
+      <c r="E21" s="141" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="141"/>
-      <c r="G21" s="142"/>
-      <c r="H21" s="140" t="s">
+      <c r="F21" s="142"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="141"/>
-      <c r="J21" s="142"/>
-      <c r="K21" s="140" t="s">
+      <c r="I21" s="142"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="141" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="141"/>
-      <c r="M21" s="142"/>
-      <c r="N21" s="140" t="s">
+      <c r="L21" s="142"/>
+      <c r="M21" s="143"/>
+      <c r="N21" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="141"/>
-      <c r="P21" s="142"/>
+      <c r="O21" s="142"/>
+      <c r="P21" s="143"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3277,7 +3285,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="144"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3501,21 +3509,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3527,17 +3535,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3557,13 +3565,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3603,10 +3611,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3614,9 +3622,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6199,17 +6207,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6518,21 +6526,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6544,17 +6552,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6574,13 +6582,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6620,10 +6628,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6631,9 +6639,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9212,17 +9220,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9531,21 +9539,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9557,17 +9565,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9587,13 +9595,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9633,10 +9641,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9644,9 +9652,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12216,17 +12224,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12535,21 +12543,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12561,17 +12569,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12591,13 +12599,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12637,10 +12645,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12648,9 +12656,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15234,17 +15242,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15553,21 +15561,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15579,17 +15587,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15609,13 +15617,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15655,10 +15663,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15666,9 +15674,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18010,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="50">
-        <f t="shared" ref="U50:U52" si="14">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <f t="shared" ref="U52" si="14">C52*24+M52*24+O52*24+Q52*24+T52</f>
         <v>0</v>
       </c>
       <c r="V52" s="50">
@@ -18242,17 +18250,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="148"/>
-      <c r="E60" s="148"/>
-      <c r="F60" s="148"/>
-      <c r="G60" s="148"/>
-      <c r="H60" s="148"/>
-      <c r="I60" s="148"/>
-      <c r="J60" s="148"/>
-      <c r="K60" s="149"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
+      <c r="G60" s="149"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="150"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18561,21 +18569,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18587,17 +18595,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18617,13 +18625,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18663,10 +18671,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18674,9 +18682,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21083,17 +21091,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="148"/>
-      <c r="E60" s="148"/>
-      <c r="F60" s="148"/>
-      <c r="G60" s="148"/>
-      <c r="H60" s="148"/>
-      <c r="I60" s="148"/>
-      <c r="J60" s="148"/>
-      <c r="K60" s="149"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
+      <c r="G60" s="149"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="150"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21363,6 +21371,3026 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7BD0FAF-93FD-4661-8F84-CB345153E478}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="151" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="146" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="157" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="159" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="152" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="154" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="155"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="48">
+        <v>26</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48">
+        <v>5</v>
+      </c>
+      <c r="I7" s="48">
+        <v>1</v>
+      </c>
+      <c r="J7" s="109"/>
+      <c r="K7" s="69">
+        <v>6</v>
+      </c>
+      <c r="M7" s="88">
+        <v>2</v>
+      </c>
+      <c r="N7" s="119">
+        <v>12</v>
+      </c>
+      <c r="O7" s="48">
+        <v>2</v>
+      </c>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109">
+        <v>2</v>
+      </c>
+      <c r="R7" s="69"/>
+      <c r="T7" s="91">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>24</v>
+      </c>
+      <c r="U7" s="91">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>792</v>
+      </c>
+      <c r="V7" s="91">
+        <f>U7/24</f>
+        <v>33</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95">
+        <f>63+31</f>
+        <v>94</v>
+      </c>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103">
+        <v>1</v>
+      </c>
+      <c r="N8" s="120"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="126">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>2280</v>
+      </c>
+      <c r="V8" s="124">
+        <f>U8/24</f>
+        <v>95</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="46"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="46"/>
+      <c r="T9" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="125">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="125">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="47">
+        <f>59</f>
+        <v>59</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="46"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="47">
+        <v>2</v>
+      </c>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="46"/>
+      <c r="T10" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="91">
+        <f t="shared" si="2"/>
+        <v>1464</v>
+      </c>
+      <c r="V10" s="91">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47">
+        <v>22</v>
+      </c>
+      <c r="I11" s="47"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="46">
+        <v>2</v>
+      </c>
+      <c r="M11" s="52"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="46"/>
+      <c r="T11" s="91">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="91">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="95">
+        <f>72+1368+16+1440+576</f>
+        <v>3472</v>
+      </c>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103">
+        <v>11</v>
+      </c>
+      <c r="N12" s="120">
+        <v>8</v>
+      </c>
+      <c r="O12" s="97">
+        <v>10</v>
+      </c>
+      <c r="P12" s="113">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="113">
+        <v>19</v>
+      </c>
+      <c r="R12" s="98">
+        <v>12</v>
+      </c>
+      <c r="S12" s="102"/>
+      <c r="T12" s="91">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="U12" s="124">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>84326</v>
+      </c>
+      <c r="V12" s="124">
+        <f>U12/24</f>
+        <v>3513.5833333333335</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47">
+        <v>5</v>
+      </c>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="46"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="46"/>
+      <c r="T13" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="125">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>120</v>
+      </c>
+      <c r="V13" s="125">
+        <f>U13/24</f>
+        <v>5</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="46"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="46"/>
+      <c r="T14" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="46"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="46"/>
+      <c r="T15" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="46"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="46"/>
+      <c r="T16" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="47">
+        <v>4</v>
+      </c>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="46"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="46"/>
+      <c r="T17" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="50">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V17" s="50">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="46"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="46"/>
+      <c r="T18" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="47">
+        <v>4</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="46"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="46"/>
+      <c r="T19" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="50">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V19" s="50">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="47">
+        <v>6</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="46"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="46"/>
+      <c r="T20" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="50">
+        <f t="shared" si="4"/>
+        <v>144</v>
+      </c>
+      <c r="V20" s="50">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47">
+        <v>4</v>
+      </c>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="46"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="46"/>
+      <c r="T21" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="50">
+        <f t="shared" si="4"/>
+        <v>96</v>
+      </c>
+      <c r="V21" s="50">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="47">
+        <v>2</v>
+      </c>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="50">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="V22" s="50">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="47">
+        <v>48</v>
+      </c>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="50">
+        <f t="shared" si="4"/>
+        <v>1152</v>
+      </c>
+      <c r="V23" s="50">
+        <f t="shared" si="5"/>
+        <v>48</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="47">
+        <v>7</v>
+      </c>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="46"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="46"/>
+      <c r="T24" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="50">
+        <f t="shared" si="4"/>
+        <v>168</v>
+      </c>
+      <c r="V24" s="50">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="47">
+        <f>63+19+1</f>
+        <v>83</v>
+      </c>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47">
+        <v>10</v>
+      </c>
+      <c r="I25" s="47">
+        <v>1</v>
+      </c>
+      <c r="J25" s="111"/>
+      <c r="K25" s="46"/>
+      <c r="M25" s="52">
+        <v>2</v>
+      </c>
+      <c r="N25" s="121">
+        <v>12</v>
+      </c>
+      <c r="O25" s="47">
+        <v>2</v>
+      </c>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111">
+        <v>2</v>
+      </c>
+      <c r="R25" s="46"/>
+      <c r="T25" s="91">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U25" s="50">
+        <f t="shared" si="4"/>
+        <v>2159</v>
+      </c>
+      <c r="V25" s="50">
+        <f t="shared" si="5"/>
+        <v>89.958333333333329</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="47">
+        <v>32</v>
+      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="52">
+        <v>2</v>
+      </c>
+      <c r="N28" s="121"/>
+      <c r="O28" s="47">
+        <v>1</v>
+      </c>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111">
+        <v>2</v>
+      </c>
+      <c r="R28" s="46"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="50">
+        <f t="shared" si="4"/>
+        <v>888</v>
+      </c>
+      <c r="V28" s="50">
+        <f t="shared" si="5"/>
+        <v>37</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="46"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="46"/>
+      <c r="T29" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="47">
+        <v>62</v>
+      </c>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="46"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="47">
+        <v>1</v>
+      </c>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111">
+        <v>1</v>
+      </c>
+      <c r="R30" s="46"/>
+      <c r="T30" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="50">
+        <f t="shared" si="4"/>
+        <v>1536</v>
+      </c>
+      <c r="V30" s="50">
+        <f t="shared" si="5"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="46"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="46"/>
+      <c r="T31" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="46"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="46"/>
+      <c r="T32" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="46"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="46"/>
+      <c r="T33" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="47">
+        <f>72+19+6</f>
+        <v>97</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47">
+        <v>4</v>
+      </c>
+      <c r="I34" s="47"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="46">
+        <v>1</v>
+      </c>
+      <c r="M34" s="52">
+        <v>2</v>
+      </c>
+      <c r="N34" s="121">
+        <v>12</v>
+      </c>
+      <c r="O34" s="47">
+        <v>2</v>
+      </c>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111">
+        <v>3</v>
+      </c>
+      <c r="R34" s="46"/>
+      <c r="T34" s="91">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U34" s="50">
+        <f t="shared" si="4"/>
+        <v>2513</v>
+      </c>
+      <c r="V34" s="50">
+        <f t="shared" si="5"/>
+        <v>104.70833333333333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="46"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="46"/>
+      <c r="T35" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="46"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="46"/>
+      <c r="T36" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="95">
+        <f>2376+1836+14</f>
+        <v>4226</v>
+      </c>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95">
+        <v>2</v>
+      </c>
+      <c r="I37" s="95"/>
+      <c r="J37" s="110">
+        <v>4</v>
+      </c>
+      <c r="K37" s="96">
+        <v>2</v>
+      </c>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103">
+        <v>30</v>
+      </c>
+      <c r="N37" s="120"/>
+      <c r="O37" s="97">
+        <v>34</v>
+      </c>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113">
+        <v>81</v>
+      </c>
+      <c r="R37" s="98"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="104">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="104">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>26234</v>
+      </c>
+      <c r="V37" s="104">
+        <f>U37/6</f>
+        <v>4372.333333333333</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="47">
+        <f>1+3</f>
+        <v>4</v>
+      </c>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="46"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="47"/>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="46"/>
+      <c r="T38" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="50">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>96</v>
+      </c>
+      <c r="V38" s="50">
+        <f>U38/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="95">
+        <f>2+693</f>
+        <v>695</v>
+      </c>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95">
+        <v>9</v>
+      </c>
+      <c r="I40" s="95"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="96">
+        <v>15</v>
+      </c>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="97"/>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113">
+        <v>2</v>
+      </c>
+      <c r="R40" s="98"/>
+      <c r="S40" s="102"/>
+      <c r="T40" s="104">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="104">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>16752</v>
+      </c>
+      <c r="V40" s="104">
+        <f>U40/24</f>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="100">
+        <f>1632+8</f>
+        <v>1640</v>
+      </c>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="112"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106">
+        <v>10</v>
+      </c>
+      <c r="N41" s="122"/>
+      <c r="O41" s="100">
+        <v>6</v>
+      </c>
+      <c r="P41" s="112"/>
+      <c r="Q41" s="112">
+        <v>20</v>
+      </c>
+      <c r="R41" s="101"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="107">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>20112</v>
+      </c>
+      <c r="V41" s="107">
+        <f>U41/12</f>
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="46"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="46"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="97">
+        <f>6048+5076+6372+5400+7128+1</f>
+        <v>30025</v>
+      </c>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97">
+        <v>1</v>
+      </c>
+      <c r="I43" s="97">
+        <v>6</v>
+      </c>
+      <c r="J43" s="113">
+        <f>11*6+4</f>
+        <v>70</v>
+      </c>
+      <c r="K43" s="98">
+        <f>75*6+4</f>
+        <v>454</v>
+      </c>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103">
+        <v>305</v>
+      </c>
+      <c r="N43" s="120"/>
+      <c r="O43" s="97">
+        <v>358</v>
+      </c>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113">
+        <v>432</v>
+      </c>
+      <c r="R43" s="98"/>
+      <c r="S43" s="102"/>
+      <c r="T43" s="104">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>531</v>
+      </c>
+      <c r="U43" s="104">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>187251</v>
+      </c>
+      <c r="V43" s="104">
+        <f>U43/6</f>
+        <v>31208.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="46"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111"/>
+      <c r="R44" s="46"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="46"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="46"/>
+      <c r="T45" s="50">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="50">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="50">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="46"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="46"/>
+      <c r="T46" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="50">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="50">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="47">
+        <f>24+44+2268</f>
+        <v>2336</v>
+      </c>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47">
+        <v>3</v>
+      </c>
+      <c r="I47" s="47"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="46">
+        <v>6</v>
+      </c>
+      <c r="M47" s="52">
+        <v>10</v>
+      </c>
+      <c r="N47" s="121"/>
+      <c r="O47" s="47">
+        <v>8</v>
+      </c>
+      <c r="P47" s="111">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="111">
+        <v>10</v>
+      </c>
+      <c r="R47" s="46"/>
+      <c r="T47" s="50">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="U47" s="50">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>14195</v>
+      </c>
+      <c r="V47" s="50">
+        <f>U47/6</f>
+        <v>2365.8333333333335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="46"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="111"/>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="46"/>
+      <c r="T48" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="46"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="46"/>
+      <c r="T49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="46"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="111"/>
+      <c r="Q50" s="111"/>
+      <c r="R50" s="46"/>
+      <c r="T50" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="47">
+        <v>34</v>
+      </c>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="46"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="46"/>
+      <c r="T51" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="50">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="50">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="46"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="111"/>
+      <c r="R52" s="46"/>
+      <c r="T52" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="50">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="47">
+        <v>2</v>
+      </c>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="46"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="111"/>
+      <c r="Q53" s="111"/>
+      <c r="R53" s="46"/>
+      <c r="T53" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="50">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="V53" s="50">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="46"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="46"/>
+      <c r="T54" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="46"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="46"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="46"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="46"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="50"/>
+      <c r="V56" s="50"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="46"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="46"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>42967</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>56</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>74</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>486</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>375</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>426</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>574</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="S58" s="57"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>700</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>362794</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>44439.916666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
+      <c r="G60" s="149"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="150"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D1E6D21-8432-42F5-A0EA-128BF8928235}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -21402,25 +24430,25 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -21428,17 +24456,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21458,13 +24486,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21504,10 +24532,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21515,9 +24543,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -23924,17 +26952,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="147" t="s">
+      <c r="C60" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="148"/>
-      <c r="E60" s="148"/>
-      <c r="F60" s="148"/>
-      <c r="G60" s="148"/>
-      <c r="H60" s="148"/>
-      <c r="I60" s="148"/>
-      <c r="J60" s="148"/>
-      <c r="K60" s="149"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
+      <c r="F60" s="149"/>
+      <c r="G60" s="149"/>
+      <c r="H60" s="149"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="150"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24186,13 +27214,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -24234,16 +27262,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="150" t="s">
+      <c r="H1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24255,15 +27283,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="147"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -25912,15 +28940,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="150"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -26193,21 +29221,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -26219,17 +29247,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -26249,13 +29277,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -26295,10 +29323,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -26306,9 +29334,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -28913,17 +31941,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -29232,21 +32260,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -29258,17 +32286,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -29288,13 +32316,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -29334,10 +32362,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -29345,9 +32373,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -31945,17 +34973,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -32264,21 +35292,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -32290,17 +35318,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -32320,13 +35348,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -32366,10 +35394,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -32377,9 +35405,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -34986,17 +38014,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35305,21 +38333,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35331,17 +38359,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35361,13 +38389,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35407,10 +38435,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35418,9 +38446,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38020,17 +41048,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -38339,21 +41367,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38365,17 +41393,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38395,13 +41423,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38441,10 +41469,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38452,9 +41480,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41036,17 +44064,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -41355,21 +44383,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41381,17 +44409,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41411,13 +44439,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41457,10 +44485,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41468,9 +44496,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44050,17 +47078,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -44369,21 +47397,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="150" t="s">
+      <c r="I1" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44395,17 +47423,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="145" t="s">
+      <c r="C4" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="145"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="155"/>
-      <c r="K4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="147"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44425,13 +47453,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="156" t="s">
+      <c r="T4" s="157" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="159" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="151" t="s">
+      <c r="V4" s="152" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44471,10 +47499,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="153" t="s">
+      <c r="J5" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="154"/>
+      <c r="K5" s="155"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44482,9 +47510,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="157"/>
-      <c r="U5" s="159"/>
-      <c r="V5" s="152"/>
+      <c r="T5" s="158"/>
+      <c r="U5" s="160"/>
+      <c r="V5" s="153"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47071,17 +50099,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="147" t="s">
+      <c r="C59" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="148"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="148"/>
-      <c r="I59" s="148"/>
-      <c r="J59" s="148"/>
-      <c r="K59" s="149"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
+      <c r="F59" s="149"/>
+      <c r="G59" s="149"/>
+      <c r="H59" s="149"/>
+      <c r="I59" s="149"/>
+      <c r="J59" s="149"/>
+      <c r="K59" s="150"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC97E699-789D-44A1-A7E5-16AA9AF86CF5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF902B25-41A1-43F9-9EA5-3608EF00773D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="EXAMPLE" sheetId="23" r:id="rId15"/>
     <sheet name="02-17-2026" sheetId="25" r:id="rId16"/>
     <sheet name="02-18-2026" sheetId="24" r:id="rId17"/>
+    <sheet name="02-19-2026" sheetId="26" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -46,6 +47,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="13">'02-16-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'02-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'02-18-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'02-19-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1403" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="98">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -358,6 +360,9 @@
   </si>
   <si>
     <t>DATE: 02/18/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/19/2026</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1490,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1920,6 +1925,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3235,34 +3243,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="144" t="s">
+      <c r="A21" s="145" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="141" t="s">
+      <c r="B21" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="142"/>
-      <c r="D21" s="143"/>
-      <c r="E21" s="141" t="s">
+      <c r="C21" s="143"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="142"/>
-      <c r="G21" s="143"/>
-      <c r="H21" s="141" t="s">
+      <c r="F21" s="143"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="142"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="141" t="s">
+      <c r="I21" s="143"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="142"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="141" t="s">
+      <c r="L21" s="143"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="142"/>
-      <c r="P21" s="143"/>
+      <c r="O21" s="143"/>
+      <c r="P21" s="144"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3285,7 +3293,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="145"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3509,21 +3517,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3535,17 +3543,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3565,13 +3573,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3611,10 +3619,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3622,9 +3630,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6207,17 +6215,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6526,21 +6534,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6552,17 +6560,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6582,13 +6590,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6628,10 +6636,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6639,9 +6647,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9220,17 +9228,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9539,21 +9547,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9565,17 +9573,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9595,13 +9603,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9641,10 +9649,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9652,9 +9660,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12224,17 +12232,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12543,21 +12551,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12569,17 +12577,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12599,13 +12607,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12645,10 +12653,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12656,9 +12664,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15242,17 +15250,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15561,21 +15569,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15587,17 +15595,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15617,13 +15625,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15663,10 +15671,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15674,9 +15682,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18250,17 +18258,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="148" t="s">
+      <c r="C60" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
-      <c r="G60" s="149"/>
-      <c r="H60" s="149"/>
-      <c r="I60" s="149"/>
-      <c r="J60" s="149"/>
-      <c r="K60" s="150"/>
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="151"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18569,21 +18577,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18595,17 +18603,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18625,13 +18633,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18671,10 +18679,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18682,9 +18690,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21091,17 +21099,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="148" t="s">
+      <c r="C60" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
-      <c r="G60" s="149"/>
-      <c r="H60" s="149"/>
-      <c r="I60" s="149"/>
-      <c r="J60" s="149"/>
-      <c r="K60" s="150"/>
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="151"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21410,21 +21418,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21436,17 +21444,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21466,13 +21474,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21512,10 +21520,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21523,9 +21531,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24111,17 +24119,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="148" t="s">
+      <c r="C60" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
-      <c r="G60" s="149"/>
-      <c r="H60" s="149"/>
-      <c r="I60" s="149"/>
-      <c r="J60" s="149"/>
-      <c r="K60" s="150"/>
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="151"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24373,13 +24381,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -24430,21 +24438,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24456,17 +24464,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24486,13 +24494,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24532,10 +24540,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24543,9 +24551,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24622,32 +24630,48 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="48"/>
+      <c r="C7" s="48">
+        <v>26</v>
+      </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
       <c r="F7" s="48"/>
       <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
+      <c r="H7" s="48">
+        <v>5</v>
+      </c>
+      <c r="I7" s="48">
+        <v>1</v>
+      </c>
       <c r="J7" s="109"/>
-      <c r="K7" s="69"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="48"/>
+      <c r="K7" s="69">
+        <v>6</v>
+      </c>
+      <c r="M7" s="88">
+        <v>2</v>
+      </c>
+      <c r="N7" s="119">
+        <v>12</v>
+      </c>
+      <c r="O7" s="48">
+        <v>2</v>
+      </c>
       <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
+      <c r="Q7" s="109">
+        <v>2</v>
+      </c>
       <c r="R7" s="69"/>
       <c r="T7" s="91">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="91">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="V7" s="91">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -24682,7 +24706,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="95"/>
+      <c r="C8" s="95">
+        <f>63+30</f>
+        <v>93</v>
+      </c>
       <c r="D8" s="95"/>
       <c r="E8" s="95"/>
       <c r="F8" s="95"/>
@@ -24692,9 +24719,13 @@
       <c r="J8" s="110"/>
       <c r="K8" s="96"/>
       <c r="L8" s="102"/>
-      <c r="M8" s="103"/>
+      <c r="M8" s="103">
+        <v>1</v>
+      </c>
       <c r="N8" s="120"/>
-      <c r="O8" s="97"/>
+      <c r="O8" s="97">
+        <v>1</v>
+      </c>
       <c r="P8" s="113"/>
       <c r="Q8" s="113"/>
       <c r="R8" s="98"/>
@@ -24705,11 +24736,11 @@
       </c>
       <c r="U8" s="124">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="V8" s="124">
         <f>U8/24</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -24804,7 +24835,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="47"/>
+      <c r="C10" s="47">
+        <v>58</v>
+      </c>
       <c r="D10" s="47"/>
       <c r="E10" s="47"/>
       <c r="F10" s="47"/>
@@ -24815,7 +24848,9 @@
       <c r="K10" s="46"/>
       <c r="M10" s="52"/>
       <c r="N10" s="121"/>
-      <c r="O10" s="47"/>
+      <c r="O10" s="47">
+        <v>1</v>
+      </c>
       <c r="P10" s="111"/>
       <c r="Q10" s="111"/>
       <c r="R10" s="46"/>
@@ -24825,11 +24860,11 @@
       </c>
       <c r="U10" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1416</v>
       </c>
       <c r="V10" s="91">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -24869,10 +24904,14 @@
       <c r="E11" s="47"/>
       <c r="F11" s="47"/>
       <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
+      <c r="H11" s="47">
+        <v>22</v>
+      </c>
       <c r="I11" s="47"/>
       <c r="J11" s="111"/>
-      <c r="K11" s="46"/>
+      <c r="K11" s="46">
+        <v>2</v>
+      </c>
       <c r="M11" s="52"/>
       <c r="N11" s="121"/>
       <c r="O11" s="47"/>
@@ -24881,15 +24920,15 @@
       <c r="R11" s="46"/>
       <c r="T11" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="91">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="91">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -24922,7 +24961,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="95"/>
+      <c r="C12" s="95">
+        <f>72+1368+6+1440+576</f>
+        <v>3462</v>
+      </c>
       <c r="D12" s="95"/>
       <c r="E12" s="95"/>
       <c r="F12" s="95"/>
@@ -24932,24 +24974,34 @@
       <c r="J12" s="110"/>
       <c r="K12" s="96"/>
       <c r="L12" s="102"/>
-      <c r="M12" s="103"/>
+      <c r="M12" s="103">
+        <v>9</v>
+      </c>
       <c r="N12" s="120"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="98"/>
+      <c r="O12" s="97">
+        <v>9</v>
+      </c>
+      <c r="P12" s="113">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="113">
+        <v>14</v>
+      </c>
+      <c r="R12" s="98">
+        <v>8</v>
+      </c>
       <c r="S12" s="102"/>
       <c r="T12" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="U12" s="124">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>83876</v>
       </c>
       <c r="V12" s="124">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3494.8333333333335</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -24991,7 +25043,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="47"/>
+      <c r="C13" s="47">
+        <v>5</v>
+      </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
       <c r="F13" s="47"/>
@@ -25012,11 +25066,11 @@
       </c>
       <c r="U13" s="125">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="125">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -25227,7 +25281,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="47"/>
+      <c r="C17" s="47">
+        <v>4</v>
+      </c>
       <c r="D17" s="47"/>
       <c r="E17" s="47"/>
       <c r="F17" s="47"/>
@@ -25248,11 +25304,11 @@
       </c>
       <c r="U17" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -25344,7 +25400,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="47">
+        <v>4</v>
+      </c>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="47"/>
@@ -25365,11 +25423,11 @@
       </c>
       <c r="U19" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -25403,7 +25461,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="47"/>
+      <c r="C20" s="47">
+        <v>6</v>
+      </c>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="47"/>
@@ -25424,11 +25484,11 @@
       </c>
       <c r="U20" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -25462,7 +25522,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="47"/>
+      <c r="C21" s="47">
+        <v>4</v>
+      </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="47"/>
@@ -25483,11 +25545,11 @@
       </c>
       <c r="U21" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -25521,7 +25583,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="47"/>
+      <c r="C22" s="47">
+        <v>2</v>
+      </c>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="47"/>
@@ -25544,11 +25608,11 @@
       </c>
       <c r="U22" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -25591,7 +25655,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="47"/>
+      <c r="C23" s="47">
+        <v>48</v>
+      </c>
       <c r="D23" s="47"/>
       <c r="E23" s="47"/>
       <c r="F23" s="47"/>
@@ -25614,11 +25680,11 @@
       </c>
       <c r="U23" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -25661,7 +25727,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="47"/>
+      <c r="C24" s="47">
+        <v>7</v>
+      </c>
       <c r="D24" s="47"/>
       <c r="E24" s="47"/>
       <c r="F24" s="47"/>
@@ -25682,11 +25750,11 @@
       </c>
       <c r="U24" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -25720,32 +25788,47 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="47"/>
+      <c r="C25" s="47">
+        <f>63+20</f>
+        <v>83</v>
+      </c>
       <c r="D25" s="47"/>
       <c r="E25" s="47"/>
       <c r="F25" s="47"/>
       <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
+      <c r="H25" s="47">
+        <v>10</v>
+      </c>
+      <c r="I25" s="47">
+        <v>1</v>
+      </c>
       <c r="J25" s="111"/>
       <c r="K25" s="46"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="47"/>
+      <c r="M25" s="52">
+        <v>2</v>
+      </c>
+      <c r="N25" s="121">
+        <v>12</v>
+      </c>
+      <c r="O25" s="47">
+        <v>2</v>
+      </c>
       <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
+      <c r="Q25" s="111">
+        <v>2</v>
+      </c>
       <c r="R25" s="46"/>
       <c r="T25" s="91">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U25" s="50">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2159</v>
       </c>
       <c r="V25" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>89.958333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -25845,6 +25928,2950 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
+      <c r="C28" s="47">
+        <v>30</v>
+      </c>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="52">
+        <v>2</v>
+      </c>
+      <c r="N28" s="121"/>
+      <c r="O28" s="47">
+        <v>2</v>
+      </c>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111">
+        <v>2</v>
+      </c>
+      <c r="R28" s="46"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="50">
+        <f t="shared" si="4"/>
+        <v>864</v>
+      </c>
+      <c r="V28" s="50">
+        <f t="shared" si="5"/>
+        <v>36</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="111"/>
+      <c r="K29" s="46"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="121"/>
+      <c r="O29" s="47"/>
+      <c r="P29" s="111"/>
+      <c r="Q29" s="111"/>
+      <c r="R29" s="46"/>
+      <c r="T29" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="47">
+        <v>62</v>
+      </c>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="47"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="46"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="47"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111">
+        <v>1</v>
+      </c>
+      <c r="R30" s="46"/>
+      <c r="T30" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="50">
+        <f t="shared" si="4"/>
+        <v>1512</v>
+      </c>
+      <c r="V30" s="50">
+        <f t="shared" si="5"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="111"/>
+      <c r="K31" s="46"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="47"/>
+      <c r="P31" s="111"/>
+      <c r="Q31" s="111"/>
+      <c r="R31" s="46"/>
+      <c r="T31" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="46"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="46"/>
+      <c r="T32" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="111"/>
+      <c r="K33" s="46"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="121"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="111"/>
+      <c r="Q33" s="111"/>
+      <c r="R33" s="46"/>
+      <c r="T33" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="47">
+        <f>72+19+6</f>
+        <v>97</v>
+      </c>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47">
+        <v>4</v>
+      </c>
+      <c r="I34" s="47"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="46">
+        <v>1</v>
+      </c>
+      <c r="M34" s="52">
+        <v>2</v>
+      </c>
+      <c r="N34" s="121">
+        <v>12</v>
+      </c>
+      <c r="O34" s="47">
+        <v>2</v>
+      </c>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111">
+        <v>3</v>
+      </c>
+      <c r="R34" s="46"/>
+      <c r="T34" s="91">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U34" s="50">
+        <f t="shared" si="4"/>
+        <v>2513</v>
+      </c>
+      <c r="V34" s="50">
+        <f t="shared" si="5"/>
+        <v>104.70833333333333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="47"/>
+      <c r="I35" s="47"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="46"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="47"/>
+      <c r="P35" s="111"/>
+      <c r="Q35" s="111"/>
+      <c r="R35" s="46"/>
+      <c r="T35" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="46"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="121"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="46"/>
+      <c r="T36" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="95">
+        <f>2376+1728+25</f>
+        <v>4129</v>
+      </c>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95">
+        <v>2</v>
+      </c>
+      <c r="I37" s="95"/>
+      <c r="J37" s="110">
+        <v>4</v>
+      </c>
+      <c r="K37" s="96">
+        <v>2</v>
+      </c>
+      <c r="L37" s="102"/>
+      <c r="M37" s="103">
+        <v>2</v>
+      </c>
+      <c r="N37" s="120"/>
+      <c r="O37" s="97">
+        <v>30</v>
+      </c>
+      <c r="P37" s="113"/>
+      <c r="Q37" s="113">
+        <v>107</v>
+      </c>
+      <c r="R37" s="98"/>
+      <c r="S37" s="102"/>
+      <c r="T37" s="104">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="104">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>25616</v>
+      </c>
+      <c r="V37" s="104">
+        <f>U37/6</f>
+        <v>4269.333333333333</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="47">
+        <v>3</v>
+      </c>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="111"/>
+      <c r="K38" s="46"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="121"/>
+      <c r="O38" s="47">
+        <v>1</v>
+      </c>
+      <c r="P38" s="111"/>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="46"/>
+      <c r="T38" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="50">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>96</v>
+      </c>
+      <c r="V38" s="50">
+        <f>U38/24</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="134"/>
+      <c r="K39" s="135"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="134"/>
+      <c r="Q39" s="134"/>
+      <c r="R39" s="135"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="95">
+        <f>1+693</f>
+        <v>694</v>
+      </c>
+      <c r="D40" s="95"/>
+      <c r="E40" s="95"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95">
+        <v>9</v>
+      </c>
+      <c r="I40" s="95"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="96">
+        <v>15</v>
+      </c>
+      <c r="L40" s="102"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="97">
+        <v>1</v>
+      </c>
+      <c r="P40" s="113"/>
+      <c r="Q40" s="113">
+        <v>2</v>
+      </c>
+      <c r="R40" s="98"/>
+      <c r="S40" s="102"/>
+      <c r="T40" s="104">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="104">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>16752</v>
+      </c>
+      <c r="V40" s="104">
+        <f>U40/24</f>
+        <v>698</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="100">
+        <f>1536+81</f>
+        <v>1617</v>
+      </c>
+      <c r="D41" s="100"/>
+      <c r="E41" s="100"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="100"/>
+      <c r="J41" s="112"/>
+      <c r="K41" s="101"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="106">
+        <v>4</v>
+      </c>
+      <c r="N41" s="122"/>
+      <c r="O41" s="100">
+        <v>12</v>
+      </c>
+      <c r="P41" s="112"/>
+      <c r="Q41" s="112">
+        <v>15</v>
+      </c>
+      <c r="R41" s="101"/>
+      <c r="S41" s="105"/>
+      <c r="T41" s="107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="107">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>19776</v>
+      </c>
+      <c r="V41" s="107">
+        <f>U41/12</f>
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="46"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="121"/>
+      <c r="O42" s="47"/>
+      <c r="P42" s="111"/>
+      <c r="Q42" s="111"/>
+      <c r="R42" s="46"/>
+      <c r="T42" s="50"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="50"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="97">
+        <f>6048+4536+6372+5400+7128</f>
+        <v>29484</v>
+      </c>
+      <c r="D43" s="97"/>
+      <c r="E43" s="97"/>
+      <c r="F43" s="97"/>
+      <c r="G43" s="97"/>
+      <c r="H43" s="97">
+        <v>2</v>
+      </c>
+      <c r="I43" s="97">
+        <v>6</v>
+      </c>
+      <c r="J43" s="113">
+        <f>12*6+3</f>
+        <v>75</v>
+      </c>
+      <c r="K43" s="98">
+        <f>75*6+4</f>
+        <v>454</v>
+      </c>
+      <c r="L43" s="102"/>
+      <c r="M43" s="103">
+        <v>2</v>
+      </c>
+      <c r="N43" s="120"/>
+      <c r="O43" s="97">
+        <v>282</v>
+      </c>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="113">
+        <v>384</v>
+      </c>
+      <c r="R43" s="98"/>
+      <c r="S43" s="102"/>
+      <c r="T43" s="104">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>537</v>
+      </c>
+      <c r="U43" s="104">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>181449</v>
+      </c>
+      <c r="V43" s="104">
+        <f>U43/6</f>
+        <v>30241.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="47"/>
+      <c r="I44" s="47"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="46"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="121"/>
+      <c r="O44" s="47"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111"/>
+      <c r="R44" s="46"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="50"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="46"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="46"/>
+      <c r="T45" s="50">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="50">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="50">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="47"/>
+      <c r="I46" s="47"/>
+      <c r="J46" s="111"/>
+      <c r="K46" s="46"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="121"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="111"/>
+      <c r="Q46" s="111"/>
+      <c r="R46" s="46"/>
+      <c r="T46" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="50">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="50">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="47">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="111"/>
+      <c r="K47" s="46">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="M47" s="52">
+        <v>10</v>
+      </c>
+      <c r="N47" s="121"/>
+      <c r="O47" s="47">
+        <v>8</v>
+      </c>
+      <c r="P47" s="111">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="111">
+        <v>10</v>
+      </c>
+      <c r="R47" s="46"/>
+      <c r="T47" s="50">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="U47" s="50">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>14195</v>
+      </c>
+      <c r="V47" s="50">
+        <f>U47/6</f>
+        <v>2365.8333333333335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="47"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="111"/>
+      <c r="K48" s="46"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="121"/>
+      <c r="O48" s="47"/>
+      <c r="P48" s="111"/>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="46"/>
+      <c r="T48" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="46"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="121"/>
+      <c r="O49" s="47"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="46"/>
+      <c r="T49" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="111"/>
+      <c r="K50" s="46"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="121"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="111"/>
+      <c r="Q50" s="111"/>
+      <c r="R50" s="46"/>
+      <c r="T50" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="47">
+        <v>34</v>
+      </c>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="46"/>
+      <c r="M51" s="52"/>
+      <c r="N51" s="121"/>
+      <c r="O51" s="47"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="46"/>
+      <c r="T51" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="50">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>204</v>
+      </c>
+      <c r="V51" s="50">
+        <f>U51/6</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="46"/>
+      <c r="M52" s="52"/>
+      <c r="N52" s="121"/>
+      <c r="O52" s="47"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="111"/>
+      <c r="R52" s="46"/>
+      <c r="T52" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="50">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="47">
+        <v>2</v>
+      </c>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
+      <c r="G53" s="47"/>
+      <c r="H53" s="47"/>
+      <c r="I53" s="47"/>
+      <c r="J53" s="111"/>
+      <c r="K53" s="46"/>
+      <c r="M53" s="52"/>
+      <c r="N53" s="121"/>
+      <c r="O53" s="47"/>
+      <c r="P53" s="111"/>
+      <c r="Q53" s="111"/>
+      <c r="R53" s="46"/>
+      <c r="T53" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="50">
+        <f t="shared" si="10"/>
+        <v>48</v>
+      </c>
+      <c r="V53" s="50">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
+      <c r="I54" s="47"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="46"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="121"/>
+      <c r="O54" s="47"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="46"/>
+      <c r="T54" s="50">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="50">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="50">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
+      <c r="G55" s="47"/>
+      <c r="H55" s="47"/>
+      <c r="I55" s="47"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="46"/>
+      <c r="M55" s="52"/>
+      <c r="N55" s="121"/>
+      <c r="O55" s="47"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="46"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="47"/>
+      <c r="I56" s="47"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="46"/>
+      <c r="M56" s="52"/>
+      <c r="N56" s="121"/>
+      <c r="O56" s="47"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="46"/>
+      <c r="T56" s="50"/>
+      <c r="U56" s="50"/>
+      <c r="V56" s="50"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="47"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="47"/>
+      <c r="I57" s="47"/>
+      <c r="J57" s="111"/>
+      <c r="K57" s="46"/>
+      <c r="M57" s="52"/>
+      <c r="N57" s="121"/>
+      <c r="O57" s="47"/>
+      <c r="P57" s="111"/>
+      <c r="Q57" s="111"/>
+      <c r="R57" s="46"/>
+      <c r="T57" s="50"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="50"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>42290</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>54</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>79</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>486</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>36</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>36</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>353</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>542</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="S58" s="57"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>688</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>355492</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>43319.166666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="149" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="151"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9408C4C9-0152-4EDD-8366-FCE42DBB1118}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="152" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="147" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="158" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="160" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="153" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="155" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="156"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="141"/>
+      <c r="Q5" s="141"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="141"/>
+      <c r="Q6" s="141"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="69"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="69"/>
+      <c r="T7" s="91">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="91">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="91">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="95"/>
+      <c r="I8" s="95"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="97"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="126">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="124">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="124">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="46"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="121"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="46"/>
+      <c r="T9" s="50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="125">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="125">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="46"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="46"/>
+      <c r="T10" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="111"/>
+      <c r="K11" s="46"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="46"/>
+      <c r="T11" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="91">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="113"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="102"/>
+      <c r="T12" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="124">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="124">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="46"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="46"/>
+      <c r="T13" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="125">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="125">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="46"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="46"/>
+      <c r="T14" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="50">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="50">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="46"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="121"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="46"/>
+      <c r="T15" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="46"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="46"/>
+      <c r="T16" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="111"/>
+      <c r="K17" s="46"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="47"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="46"/>
+      <c r="T17" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="46"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="121"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="46"/>
+      <c r="T18" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="46"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="121"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="46"/>
+      <c r="T19" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="46"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="47"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="46"/>
+      <c r="T20" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="46"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="47"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="46"/>
+      <c r="T21" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="47"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="47"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="121"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="46"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="121"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="46"/>
+      <c r="T24" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="46"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="121"/>
+      <c r="O25" s="47"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="46"/>
+      <c r="T25" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="50">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="50">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
       <c r="C28" s="47"/>
       <c r="D28" s="47"/>
       <c r="E28" s="47"/>
@@ -26952,17 +29979,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="148" t="s">
+      <c r="C60" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
-      <c r="F60" s="149"/>
-      <c r="G60" s="149"/>
-      <c r="H60" s="149"/>
-      <c r="I60" s="149"/>
-      <c r="J60" s="149"/>
-      <c r="K60" s="150"/>
+      <c r="D60" s="150"/>
+      <c r="E60" s="150"/>
+      <c r="F60" s="150"/>
+      <c r="G60" s="150"/>
+      <c r="H60" s="150"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="151"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27262,16 +30289,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="151" t="s">
+      <c r="H1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27283,15 +30310,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="148"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -28940,15 +31967,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="151"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -29221,21 +32248,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -29247,17 +32274,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -29277,13 +32304,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -29323,10 +32350,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -29334,9 +32361,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -31941,17 +34968,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -32260,21 +35287,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -32286,17 +35313,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -32316,13 +35343,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -32362,10 +35389,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -32373,9 +35400,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -34973,17 +38000,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35292,21 +38319,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35318,17 +38345,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35348,13 +38375,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35394,10 +38421,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35405,9 +38432,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38014,17 +41041,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -38333,21 +41360,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38359,17 +41386,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38389,13 +41416,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38435,10 +41462,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38446,9 +41473,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41048,17 +44075,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -41367,21 +44394,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41393,17 +44420,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41423,13 +44450,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41469,10 +44496,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41480,9 +44507,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44064,17 +47091,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -44383,21 +47410,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44409,17 +47436,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44439,13 +47466,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44485,10 +47512,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44496,9 +47523,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47078,17 +50105,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -47397,21 +50424,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="151" t="s">
+      <c r="I1" s="152" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
+      <c r="J1" s="152"/>
+      <c r="K1" s="152"/>
+      <c r="L1" s="152"/>
+      <c r="M1" s="152"/>
+      <c r="N1" s="152"/>
+      <c r="O1" s="152"/>
+      <c r="P1" s="152"/>
+      <c r="Q1" s="152"/>
+      <c r="R1" s="152"/>
+      <c r="S1" s="152"/>
+      <c r="T1" s="152"/>
+      <c r="U1" s="152"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47423,17 +50450,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="146" t="s">
+      <c r="C4" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="156"/>
-      <c r="K4" s="147"/>
+      <c r="D4" s="147"/>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="148"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -47453,13 +50480,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="157" t="s">
+      <c r="T4" s="158" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="159" t="s">
+      <c r="U4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="152" t="s">
+      <c r="V4" s="153" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -47499,10 +50526,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="154" t="s">
+      <c r="J5" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="155"/>
+      <c r="K5" s="156"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -47510,9 +50537,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="158"/>
-      <c r="U5" s="160"/>
-      <c r="V5" s="153"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="161"/>
+      <c r="V5" s="154"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -50099,17 +53126,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="148" t="s">
+      <c r="C59" s="149" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
-      <c r="F59" s="149"/>
-      <c r="G59" s="149"/>
-      <c r="H59" s="149"/>
-      <c r="I59" s="149"/>
-      <c r="J59" s="149"/>
-      <c r="K59" s="150"/>
+      <c r="D59" s="150"/>
+      <c r="E59" s="150"/>
+      <c r="F59" s="150"/>
+      <c r="G59" s="150"/>
+      <c r="H59" s="150"/>
+      <c r="I59" s="150"/>
+      <c r="J59" s="150"/>
+      <c r="K59" s="151"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF902B25-41A1-43F9-9EA5-3608EF00773D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA49809-3B8C-4D66-991B-92650C19D9AA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="16" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="18" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="02-17-2026" sheetId="25" r:id="rId16"/>
     <sheet name="02-18-2026" sheetId="24" r:id="rId17"/>
     <sheet name="02-19-2026" sheetId="26" r:id="rId18"/>
+    <sheet name="02-20-2026" sheetId="28" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -48,6 +49,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'02-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'02-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'02-19-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'02-20-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -68,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="99">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -364,6 +366,9 @@
   <si>
     <t>DATE: 02/19/2026</t>
   </si>
+  <si>
+    <t>DATE: 02/20/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -375,7 +380,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +506,12 @@
     </font>
     <font>
       <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1490,7 +1501,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1928,6 +1939,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,6 +2001,123 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="55" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="61" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="56" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="48" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="49" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="62" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="43" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="59" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="44" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="68" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="67" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="57" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="63" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="66" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="50" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="70" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="71" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="72" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="69" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="73" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="47" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="45" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="64" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3243,34 +3374,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="145" t="s">
+      <c r="A21" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="142" t="s">
+      <c r="B21" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="143"/>
-      <c r="D21" s="144"/>
-      <c r="E21" s="142" t="s">
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="143"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="142" t="s">
+      <c r="F21" s="144"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="143"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="142" t="s">
+      <c r="I21" s="144"/>
+      <c r="J21" s="145"/>
+      <c r="K21" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="143"/>
-      <c r="M21" s="144"/>
-      <c r="N21" s="142" t="s">
+      <c r="L21" s="144"/>
+      <c r="M21" s="145"/>
+      <c r="N21" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="143"/>
-      <c r="P21" s="144"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="145"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3293,7 +3424,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="146"/>
+      <c r="A22" s="147"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3517,21 +3648,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3543,17 +3674,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3573,13 +3704,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3619,10 +3750,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3630,9 +3761,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6215,17 +6346,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6534,21 +6665,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6560,17 +6691,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6590,13 +6721,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6636,10 +6767,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6647,9 +6778,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9228,17 +9359,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9547,21 +9678,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9573,17 +9704,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9603,13 +9734,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9649,10 +9780,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9660,9 +9791,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12232,17 +12363,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12551,21 +12682,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12577,17 +12708,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12607,13 +12738,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12653,10 +12784,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12664,9 +12795,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15250,17 +15381,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15569,21 +15700,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15595,17 +15726,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15625,13 +15756,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15671,10 +15802,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15682,9 +15813,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18258,17 +18389,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18577,21 +18708,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18603,17 +18734,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18633,13 +18764,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18679,10 +18810,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18690,9 +18821,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21099,17 +21230,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21418,21 +21549,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21444,17 +21575,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21474,13 +21605,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21520,10 +21651,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21531,9 +21662,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24119,17 +24250,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24438,21 +24569,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24464,17 +24595,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24494,13 +24625,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24540,10 +24671,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24551,9 +24682,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27138,17 +27269,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27430,20 +27561,20 @@
     <col min="3" max="6" width="10" style="57" customWidth="1"/>
     <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
     <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
     <col min="13" max="13" width="10" style="57" customWidth="1"/>
-    <col min="14" max="14" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="57" customWidth="1"/>
     <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
     <col min="17" max="17" width="10" style="57" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
-    <col min="22" max="22" width="19.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
     <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
     <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
     <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
@@ -27457,21 +27588,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27483,17 +27614,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -27513,13 +27644,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -27559,10 +27690,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -27570,9 +27701,9 @@
       <c r="Q5" s="141"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27649,32 +27780,50 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="69"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="119"/>
-      <c r="O7" s="48"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="69"/>
-      <c r="T7" s="91">
+      <c r="C7" s="163">
+        <v>25</v>
+      </c>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163">
+        <v>5</v>
+      </c>
+      <c r="I7" s="163">
+        <v>1</v>
+      </c>
+      <c r="J7" s="164"/>
+      <c r="K7" s="165">
+        <v>6</v>
+      </c>
+      <c r="L7" s="166"/>
+      <c r="M7" s="167">
+        <v>2</v>
+      </c>
+      <c r="N7" s="168">
+        <v>12</v>
+      </c>
+      <c r="O7" s="163">
+        <v>3</v>
+      </c>
+      <c r="P7" s="164"/>
+      <c r="Q7" s="164">
+        <v>2</v>
+      </c>
+      <c r="R7" s="165"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="169">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="91">
+        <v>24</v>
+      </c>
+      <c r="U7" s="169">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="91">
+        <v>792</v>
+      </c>
+      <c r="V7" s="169">
         <f>U7/24</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -27709,34 +27858,39 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="103"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="97"/>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="126">
+      <c r="C8" s="170">
+        <f>63+30</f>
+        <v>93</v>
+      </c>
+      <c r="D8" s="170"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="170"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="171"/>
+      <c r="K8" s="172"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="174">
+        <v>1</v>
+      </c>
+      <c r="N8" s="175"/>
+      <c r="O8" s="176"/>
+      <c r="P8" s="177"/>
+      <c r="Q8" s="177"/>
+      <c r="R8" s="178"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="179">
         <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
         <v>0</v>
       </c>
-      <c r="U8" s="124">
+      <c r="U8" s="180">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="124">
+        <v>2256</v>
+      </c>
+      <c r="V8" s="180">
         <f>U8/24</f>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -27771,30 +27925,32 @@
       <c r="B9" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="46"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="121"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="46"/>
-      <c r="T9" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="125">
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="183"/>
+      <c r="L9" s="166"/>
+      <c r="M9" s="184"/>
+      <c r="N9" s="185"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="182"/>
+      <c r="Q9" s="182"/>
+      <c r="R9" s="183"/>
+      <c r="S9" s="166"/>
+      <c r="T9" s="186">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="187">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
         <v>0</v>
       </c>
-      <c r="V9" s="125">
+      <c r="V9" s="187">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
         <v>0</v>
       </c>
@@ -27831,32 +27987,38 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="46"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="46"/>
-      <c r="T10" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U10" s="91">
+      <c r="C10" s="181">
+        <v>54</v>
+      </c>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="181"/>
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="183"/>
+      <c r="L10" s="166"/>
+      <c r="M10" s="184">
+        <v>4</v>
+      </c>
+      <c r="N10" s="185"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="182"/>
+      <c r="Q10" s="182"/>
+      <c r="R10" s="183"/>
+      <c r="S10" s="166"/>
+      <c r="T10" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="169">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="91">
+        <v>1392</v>
+      </c>
+      <c r="V10" s="169">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -27891,32 +28053,38 @@
       <c r="B11" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47"/>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="111"/>
-      <c r="K11" s="46"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="121"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="46"/>
-      <c r="T11" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="91">
+      <c r="C11" s="181"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181">
+        <v>22</v>
+      </c>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183">
+        <v>2</v>
+      </c>
+      <c r="L11" s="166"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="185"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="182"/>
+      <c r="Q11" s="182"/>
+      <c r="R11" s="183"/>
+      <c r="S11" s="166"/>
+      <c r="T11" s="169">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U11" s="169">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="91">
+        <v>24</v>
+      </c>
+      <c r="V11" s="169">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -27949,34 +28117,47 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="113"/>
-      <c r="Q12" s="113"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="102"/>
-      <c r="T12" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="124">
+      <c r="C12" s="170">
+        <f>72+1296+53+1440+576</f>
+        <v>3437</v>
+      </c>
+      <c r="D12" s="170"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="173"/>
+      <c r="M12" s="174">
+        <v>14</v>
+      </c>
+      <c r="N12" s="175"/>
+      <c r="O12" s="176">
+        <v>8</v>
+      </c>
+      <c r="P12" s="177">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="177">
+        <v>16</v>
+      </c>
+      <c r="R12" s="178">
+        <v>8</v>
+      </c>
+      <c r="S12" s="173"/>
+      <c r="T12" s="169">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="U12" s="180">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="124">
+        <v>83410</v>
+      </c>
+      <c r="V12" s="180">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3475.4166666666665</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -28018,32 +28199,36 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="46"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="46"/>
-      <c r="T13" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U13" s="125">
+      <c r="C13" s="181">
+        <v>5</v>
+      </c>
+      <c r="D13" s="181"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="182"/>
+      <c r="K13" s="183"/>
+      <c r="L13" s="166"/>
+      <c r="M13" s="184"/>
+      <c r="N13" s="185"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="182"/>
+      <c r="Q13" s="182"/>
+      <c r="R13" s="183"/>
+      <c r="S13" s="166"/>
+      <c r="T13" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="187">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
-      </c>
-      <c r="V13" s="125">
+        <v>120</v>
+      </c>
+      <c r="V13" s="187">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -28077,30 +28262,32 @@
       <c r="B14" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="46"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="46"/>
-      <c r="T14" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="50">
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="182"/>
+      <c r="K14" s="183"/>
+      <c r="L14" s="166"/>
+      <c r="M14" s="184"/>
+      <c r="N14" s="185"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="182"/>
+      <c r="Q14" s="182"/>
+      <c r="R14" s="183"/>
+      <c r="S14" s="166"/>
+      <c r="T14" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="186">
         <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
         <v>0</v>
       </c>
-      <c r="V14" s="50">
+      <c r="V14" s="186">
         <f t="shared" ref="V14:V36" si="5">U14/24</f>
         <v>0</v>
       </c>
@@ -28136,30 +28323,32 @@
       <c r="B15" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="46"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="46"/>
-      <c r="T15" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="50">
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="181"/>
+      <c r="I15" s="181"/>
+      <c r="J15" s="182"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="166"/>
+      <c r="M15" s="184"/>
+      <c r="N15" s="185"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="182"/>
+      <c r="Q15" s="182"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="166"/>
+      <c r="T15" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V15" s="50">
+      <c r="V15" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -28195,30 +28384,32 @@
       <c r="B16" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="46"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="46"/>
-      <c r="T16" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="50">
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="181"/>
+      <c r="H16" s="181"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="182"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="166"/>
+      <c r="M16" s="184"/>
+      <c r="N16" s="185"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="182"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="183"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V16" s="50">
+      <c r="V16" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -28254,32 +28445,36 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="46"/>
-      <c r="M17" s="52"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="46"/>
-      <c r="T17" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U17" s="50">
+      <c r="C17" s="181">
+        <v>4</v>
+      </c>
+      <c r="D17" s="181"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="181"/>
+      <c r="H17" s="181"/>
+      <c r="I17" s="181"/>
+      <c r="J17" s="182"/>
+      <c r="K17" s="183"/>
+      <c r="L17" s="166"/>
+      <c r="M17" s="184"/>
+      <c r="N17" s="185"/>
+      <c r="O17" s="181"/>
+      <c r="P17" s="182"/>
+      <c r="Q17" s="182"/>
+      <c r="R17" s="183"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V17" s="50">
+        <v>96</v>
+      </c>
+      <c r="V17" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -28313,30 +28508,32 @@
       <c r="B18" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="111"/>
-      <c r="K18" s="46"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="46"/>
-      <c r="T18" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="50">
+      <c r="C18" s="181"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="181"/>
+      <c r="F18" s="181"/>
+      <c r="G18" s="181"/>
+      <c r="H18" s="181"/>
+      <c r="I18" s="181"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="183"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="184"/>
+      <c r="N18" s="185"/>
+      <c r="O18" s="181"/>
+      <c r="P18" s="182"/>
+      <c r="Q18" s="182"/>
+      <c r="R18" s="183"/>
+      <c r="S18" s="166"/>
+      <c r="T18" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V18" s="50">
+      <c r="V18" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -28371,32 +28568,36 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="46"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="121"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="46"/>
-      <c r="T19" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U19" s="50">
+      <c r="C19" s="181">
+        <v>4</v>
+      </c>
+      <c r="D19" s="181"/>
+      <c r="E19" s="181"/>
+      <c r="F19" s="181"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="181"/>
+      <c r="I19" s="181"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="184"/>
+      <c r="N19" s="185"/>
+      <c r="O19" s="181"/>
+      <c r="P19" s="182"/>
+      <c r="Q19" s="182"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="166"/>
+      <c r="T19" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V19" s="50">
+        <v>96</v>
+      </c>
+      <c r="V19" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -28430,32 +28631,36 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="111"/>
-      <c r="K20" s="46"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="46"/>
-      <c r="T20" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="50">
+      <c r="C20" s="181">
+        <v>6</v>
+      </c>
+      <c r="D20" s="181"/>
+      <c r="E20" s="181"/>
+      <c r="F20" s="181"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="181"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="183"/>
+      <c r="L20" s="166"/>
+      <c r="M20" s="184"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="181"/>
+      <c r="P20" s="182"/>
+      <c r="Q20" s="182"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="50">
+        <v>144</v>
+      </c>
+      <c r="V20" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -28489,32 +28694,36 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="46"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="121"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="46"/>
-      <c r="T21" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="50">
+      <c r="C21" s="181">
+        <v>4</v>
+      </c>
+      <c r="D21" s="181"/>
+      <c r="E21" s="181"/>
+      <c r="F21" s="181"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="184"/>
+      <c r="N21" s="185"/>
+      <c r="O21" s="181"/>
+      <c r="P21" s="182"/>
+      <c r="Q21" s="182"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="166"/>
+      <c r="T21" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V21" s="50">
+        <v>96</v>
+      </c>
+      <c r="V21" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -28548,34 +28757,36 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="46"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="46"/>
-      <c r="S22" s="57"/>
-      <c r="T22" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="50">
+      <c r="C22" s="181">
+        <v>2</v>
+      </c>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="181"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="183"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="184"/>
+      <c r="N22" s="185"/>
+      <c r="O22" s="181"/>
+      <c r="P22" s="182"/>
+      <c r="Q22" s="182"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="166"/>
+      <c r="T22" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V22" s="50">
+        <v>48</v>
+      </c>
+      <c r="V22" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -28618,34 +28829,36 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="46"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="121"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="57"/>
-      <c r="T23" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U23" s="50">
+      <c r="C23" s="181">
+        <v>48</v>
+      </c>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="181"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="184"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="181"/>
+      <c r="P23" s="182"/>
+      <c r="Q23" s="182"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="166"/>
+      <c r="T23" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V23" s="50">
+        <v>1152</v>
+      </c>
+      <c r="V23" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -28688,32 +28901,36 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="46"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="46"/>
-      <c r="T24" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U24" s="50">
+      <c r="C24" s="181">
+        <v>7</v>
+      </c>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="183"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="184"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="181"/>
+      <c r="P24" s="182"/>
+      <c r="Q24" s="182"/>
+      <c r="R24" s="183"/>
+      <c r="S24" s="166"/>
+      <c r="T24" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V24" s="50">
+        <v>168</v>
+      </c>
+      <c r="V24" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -28747,32 +28964,47 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="46"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="121"/>
-      <c r="O25" s="47"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="46"/>
-      <c r="T25" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="50">
+      <c r="C25" s="181">
+        <f>63+19+1</f>
+        <v>83</v>
+      </c>
+      <c r="D25" s="181"/>
+      <c r="E25" s="181"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181">
+        <v>10</v>
+      </c>
+      <c r="I25" s="181">
+        <v>1</v>
+      </c>
+      <c r="J25" s="182"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="184">
+        <v>2</v>
+      </c>
+      <c r="N25" s="185">
+        <v>12</v>
+      </c>
+      <c r="O25" s="181"/>
+      <c r="P25" s="182"/>
+      <c r="Q25" s="182">
+        <v>2</v>
+      </c>
+      <c r="R25" s="183"/>
+      <c r="S25" s="166"/>
+      <c r="T25" s="169">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="U25" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V25" s="50">
+        <v>2111</v>
+      </c>
+      <c r="V25" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>87.958333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -28787,32 +29019,32 @@
       <c r="B26" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="57"/>
-      <c r="T26" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="50">
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="184"/>
+      <c r="N26" s="185"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="182"/>
+      <c r="Q26" s="182"/>
+      <c r="R26" s="183"/>
+      <c r="S26" s="166"/>
+      <c r="T26" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V26" s="50">
+      <c r="V26" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -28834,26 +29066,26 @@
       <c r="B27" s="74" t="s">
         <v>83</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="121"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="57"/>
-      <c r="T27" s="91"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
+      <c r="C27" s="181"/>
+      <c r="D27" s="181"/>
+      <c r="E27" s="181"/>
+      <c r="F27" s="181"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="184"/>
+      <c r="N27" s="185"/>
+      <c r="O27" s="181"/>
+      <c r="P27" s="182"/>
+      <c r="Q27" s="182"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="166"/>
+      <c r="T27" s="169"/>
+      <c r="U27" s="186"/>
+      <c r="V27" s="186"/>
       <c r="W27" s="57"/>
       <c r="X27" s="57"/>
       <c r="Y27" s="57"/>
@@ -28872,34 +29104,42 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="111"/>
-      <c r="Q28" s="111"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="57"/>
-      <c r="T28" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="50">
+      <c r="C28" s="181">
+        <v>28</v>
+      </c>
+      <c r="D28" s="181"/>
+      <c r="E28" s="181"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="183"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="184">
+        <v>2</v>
+      </c>
+      <c r="N28" s="185"/>
+      <c r="O28" s="181">
+        <v>1</v>
+      </c>
+      <c r="P28" s="182"/>
+      <c r="Q28" s="182">
+        <v>2</v>
+      </c>
+      <c r="R28" s="183"/>
+      <c r="S28" s="166"/>
+      <c r="T28" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V28" s="50">
+        <v>792</v>
+      </c>
+      <c r="V28" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -28919,30 +29159,32 @@
       <c r="B29" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="46"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="121"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="111"/>
-      <c r="Q29" s="111"/>
-      <c r="R29" s="46"/>
-      <c r="T29" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="50">
+      <c r="C29" s="181"/>
+      <c r="D29" s="181"/>
+      <c r="E29" s="181"/>
+      <c r="F29" s="181"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="181"/>
+      <c r="I29" s="181"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="184"/>
+      <c r="N29" s="185"/>
+      <c r="O29" s="181"/>
+      <c r="P29" s="182"/>
+      <c r="Q29" s="182"/>
+      <c r="R29" s="183"/>
+      <c r="S29" s="166"/>
+      <c r="T29" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V29" s="50">
+      <c r="V29" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -28955,32 +29197,38 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="46"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="111"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="46"/>
-      <c r="T30" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="50">
+      <c r="C30" s="181">
+        <v>62</v>
+      </c>
+      <c r="D30" s="181"/>
+      <c r="E30" s="181"/>
+      <c r="F30" s="181"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="181"/>
+      <c r="I30" s="181"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="183"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="185"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="182"/>
+      <c r="Q30" s="182">
+        <v>1</v>
+      </c>
+      <c r="R30" s="183"/>
+      <c r="S30" s="166"/>
+      <c r="T30" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V30" s="50">
+        <v>1512</v>
+      </c>
+      <c r="V30" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -28991,30 +29239,32 @@
       <c r="B31" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="46"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="121"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="111"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="46"/>
-      <c r="T31" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="50">
+      <c r="C31" s="181"/>
+      <c r="D31" s="181"/>
+      <c r="E31" s="181"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="181"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="182"/>
+      <c r="K31" s="183"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="184"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="181"/>
+      <c r="P31" s="182"/>
+      <c r="Q31" s="182"/>
+      <c r="R31" s="183"/>
+      <c r="S31" s="166"/>
+      <c r="T31" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V31" s="50">
+      <c r="V31" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -29027,30 +29277,32 @@
       <c r="B32" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="111"/>
-      <c r="K32" s="46"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="47"/>
-      <c r="P32" s="111"/>
-      <c r="Q32" s="111"/>
-      <c r="R32" s="46"/>
-      <c r="T32" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="50">
+      <c r="C32" s="181"/>
+      <c r="D32" s="181"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="183"/>
+      <c r="L32" s="166"/>
+      <c r="M32" s="184"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="182"/>
+      <c r="Q32" s="182"/>
+      <c r="R32" s="183"/>
+      <c r="S32" s="166"/>
+      <c r="T32" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V32" s="50">
+      <c r="V32" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -29063,30 +29315,32 @@
       <c r="B33" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="111"/>
-      <c r="K33" s="46"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="121"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="111"/>
-      <c r="Q33" s="111"/>
-      <c r="R33" s="46"/>
-      <c r="T33" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U33" s="50">
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="166"/>
+      <c r="M33" s="184"/>
+      <c r="N33" s="185"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="182"/>
+      <c r="Q33" s="182"/>
+      <c r="R33" s="183"/>
+      <c r="S33" s="166"/>
+      <c r="T33" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V33" s="50">
+      <c r="V33" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -29099,32 +29353,49 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="47"/>
-      <c r="J34" s="111"/>
-      <c r="K34" s="46"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="121"/>
-      <c r="O34" s="47"/>
-      <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="46"/>
-      <c r="T34" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="50">
+      <c r="C34" s="181">
+        <f>72+19+6</f>
+        <v>97</v>
+      </c>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181">
+        <v>4</v>
+      </c>
+      <c r="I34" s="181"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="183">
+        <v>1</v>
+      </c>
+      <c r="L34" s="166"/>
+      <c r="M34" s="184">
+        <v>2</v>
+      </c>
+      <c r="N34" s="185">
+        <v>12</v>
+      </c>
+      <c r="O34" s="181">
+        <v>2</v>
+      </c>
+      <c r="P34" s="182"/>
+      <c r="Q34" s="182">
+        <v>3</v>
+      </c>
+      <c r="R34" s="183"/>
+      <c r="S34" s="166"/>
+      <c r="T34" s="169">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="U34" s="186">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V34" s="50">
+        <v>2513</v>
+      </c>
+      <c r="V34" s="186">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>104.70833333333333</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -29135,30 +29406,32 @@
       <c r="B35" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="46"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="46"/>
-      <c r="T35" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U35" s="50">
+      <c r="C35" s="181"/>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="181"/>
+      <c r="H35" s="181"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="185"/>
+      <c r="O35" s="181"/>
+      <c r="P35" s="182"/>
+      <c r="Q35" s="182"/>
+      <c r="R35" s="183"/>
+      <c r="S35" s="166"/>
+      <c r="T35" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V35" s="50">
+      <c r="V35" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -29171,30 +29444,32 @@
       <c r="B36" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47"/>
-      <c r="I36" s="47"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="46"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="121"/>
-      <c r="O36" s="47"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="46"/>
-      <c r="T36" s="91">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="50">
+      <c r="C36" s="181"/>
+      <c r="D36" s="181"/>
+      <c r="E36" s="181"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="181"/>
+      <c r="H36" s="181"/>
+      <c r="I36" s="181"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="166"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="185"/>
+      <c r="O36" s="181"/>
+      <c r="P36" s="182"/>
+      <c r="Q36" s="182"/>
+      <c r="R36" s="183"/>
+      <c r="S36" s="166"/>
+      <c r="T36" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="186">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V36" s="50">
+      <c r="V36" s="186">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -29207,34 +29482,49 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="95"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="95"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
-      <c r="I37" s="95"/>
-      <c r="J37" s="110"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="102"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="97"/>
-      <c r="P37" s="113"/>
-      <c r="Q37" s="113"/>
-      <c r="R37" s="98"/>
-      <c r="S37" s="102"/>
-      <c r="T37" s="104">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="104">
+      <c r="C37" s="170">
+        <f>2376+1512+80</f>
+        <v>3968</v>
+      </c>
+      <c r="D37" s="170"/>
+      <c r="E37" s="170"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="170">
+        <v>2</v>
+      </c>
+      <c r="I37" s="170"/>
+      <c r="J37" s="171">
+        <v>4</v>
+      </c>
+      <c r="K37" s="172">
+        <v>2</v>
+      </c>
+      <c r="L37" s="173"/>
+      <c r="M37" s="174">
+        <v>30</v>
+      </c>
+      <c r="N37" s="175"/>
+      <c r="O37" s="176">
+        <v>37</v>
+      </c>
+      <c r="P37" s="177"/>
+      <c r="Q37" s="177">
+        <v>121</v>
+      </c>
+      <c r="R37" s="178"/>
+      <c r="S37" s="173"/>
+      <c r="T37" s="188">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U37" s="188">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="104">
+        <v>24944</v>
+      </c>
+      <c r="V37" s="188">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4157.333333333333</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -29246,32 +29536,38 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="46"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="121"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="111"/>
-      <c r="Q38" s="111"/>
-      <c r="R38" s="46"/>
-      <c r="T38" s="50">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U38" s="50">
+      <c r="C38" s="181">
+        <v>3</v>
+      </c>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="181"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="181"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="183"/>
+      <c r="L38" s="166"/>
+      <c r="M38" s="184"/>
+      <c r="N38" s="185"/>
+      <c r="O38" s="181">
+        <v>1</v>
+      </c>
+      <c r="P38" s="182"/>
+      <c r="Q38" s="182"/>
+      <c r="R38" s="183"/>
+      <c r="S38" s="166"/>
+      <c r="T38" s="186">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="186">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="50">
+        <v>96</v>
+      </c>
+      <c r="V38" s="186">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -29282,24 +29578,26 @@
       <c r="B39" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="133"/>
-      <c r="D39" s="133"/>
-      <c r="E39" s="133"/>
-      <c r="F39" s="133"/>
-      <c r="G39" s="133"/>
-      <c r="H39" s="133"/>
-      <c r="I39" s="133"/>
-      <c r="J39" s="134"/>
-      <c r="K39" s="135"/>
-      <c r="M39" s="136"/>
-      <c r="N39" s="137"/>
-      <c r="O39" s="133"/>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="134"/>
-      <c r="R39" s="135"/>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
+      <c r="C39" s="189"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="166"/>
+      <c r="M39" s="192"/>
+      <c r="N39" s="193"/>
+      <c r="O39" s="189"/>
+      <c r="P39" s="190"/>
+      <c r="Q39" s="190"/>
+      <c r="R39" s="191"/>
+      <c r="S39" s="166"/>
+      <c r="T39" s="194"/>
+      <c r="U39" s="194"/>
+      <c r="V39" s="194"/>
     </row>
     <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="75">
@@ -29309,34 +29607,43 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="95"/>
-      <c r="E40" s="95"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="95"/>
-      <c r="I40" s="95"/>
-      <c r="J40" s="110"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="102"/>
-      <c r="M40" s="103"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="97"/>
-      <c r="P40" s="113"/>
-      <c r="Q40" s="113"/>
-      <c r="R40" s="98"/>
-      <c r="S40" s="102"/>
-      <c r="T40" s="104">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U40" s="104">
+      <c r="C40" s="170">
+        <f>693+1</f>
+        <v>694</v>
+      </c>
+      <c r="D40" s="170"/>
+      <c r="E40" s="170"/>
+      <c r="F40" s="170"/>
+      <c r="G40" s="170"/>
+      <c r="H40" s="170">
+        <v>9</v>
+      </c>
+      <c r="I40" s="170"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="172">
+        <v>15</v>
+      </c>
+      <c r="L40" s="173"/>
+      <c r="M40" s="174"/>
+      <c r="N40" s="175"/>
+      <c r="O40" s="176">
+        <v>1</v>
+      </c>
+      <c r="P40" s="177"/>
+      <c r="Q40" s="177"/>
+      <c r="R40" s="178"/>
+      <c r="S40" s="173"/>
+      <c r="T40" s="188">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="U40" s="188">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="104">
+        <v>16704</v>
+      </c>
+      <c r="V40" s="188">
         <f>U40/24</f>
-        <v>0</v>
+        <v>696</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -29347,34 +29654,43 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="100"/>
-      <c r="D41" s="100"/>
-      <c r="E41" s="100"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="100"/>
-      <c r="J41" s="112"/>
-      <c r="K41" s="101"/>
-      <c r="L41" s="105"/>
-      <c r="M41" s="106"/>
-      <c r="N41" s="122"/>
-      <c r="O41" s="100"/>
-      <c r="P41" s="112"/>
-      <c r="Q41" s="112"/>
-      <c r="R41" s="101"/>
-      <c r="S41" s="105"/>
-      <c r="T41" s="107">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U41" s="107">
+      <c r="C41" s="195">
+        <f>1536+76</f>
+        <v>1612</v>
+      </c>
+      <c r="D41" s="195"/>
+      <c r="E41" s="195"/>
+      <c r="F41" s="195"/>
+      <c r="G41" s="195"/>
+      <c r="H41" s="195"/>
+      <c r="I41" s="195"/>
+      <c r="J41" s="196"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="199">
+        <v>4</v>
+      </c>
+      <c r="N41" s="200"/>
+      <c r="O41" s="195">
+        <v>8</v>
+      </c>
+      <c r="P41" s="196"/>
+      <c r="Q41" s="196">
+        <v>15</v>
+      </c>
+      <c r="R41" s="197"/>
+      <c r="S41" s="198"/>
+      <c r="T41" s="201">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="201">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="107">
+        <v>19668</v>
+      </c>
+      <c r="V41" s="201">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -29385,24 +29701,26 @@
       <c r="B42" s="73" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="111"/>
-      <c r="K42" s="46"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="121"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="111"/>
-      <c r="Q42" s="111"/>
-      <c r="R42" s="46"/>
-      <c r="T42" s="50"/>
-      <c r="U42" s="50"/>
-      <c r="V42" s="50"/>
+      <c r="C42" s="181"/>
+      <c r="D42" s="181"/>
+      <c r="E42" s="181"/>
+      <c r="F42" s="181"/>
+      <c r="G42" s="181"/>
+      <c r="H42" s="181"/>
+      <c r="I42" s="181"/>
+      <c r="J42" s="182"/>
+      <c r="K42" s="183"/>
+      <c r="L42" s="166"/>
+      <c r="M42" s="184"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="181"/>
+      <c r="P42" s="182"/>
+      <c r="Q42" s="182"/>
+      <c r="R42" s="183"/>
+      <c r="S42" s="166"/>
+      <c r="T42" s="186"/>
+      <c r="U42" s="186"/>
+      <c r="V42" s="186"/>
     </row>
     <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="75">
@@ -29412,34 +29730,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="97"/>
-      <c r="D43" s="97"/>
-      <c r="E43" s="97"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="97"/>
-      <c r="H43" s="97"/>
-      <c r="I43" s="97"/>
-      <c r="J43" s="113"/>
-      <c r="K43" s="98"/>
-      <c r="L43" s="102"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="120"/>
-      <c r="O43" s="97"/>
-      <c r="P43" s="113"/>
-      <c r="Q43" s="113"/>
-      <c r="R43" s="98"/>
-      <c r="S43" s="102"/>
-      <c r="T43" s="104">
+      <c r="C43" s="176">
+        <f>6048+3780+6372+5400+7128</f>
+        <v>28728</v>
+      </c>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176">
+        <v>2</v>
+      </c>
+      <c r="I43" s="176">
+        <v>6</v>
+      </c>
+      <c r="J43" s="177">
+        <f>13*6+2</f>
+        <v>80</v>
+      </c>
+      <c r="K43" s="178">
+        <f>75*6+4</f>
+        <v>454</v>
+      </c>
+      <c r="L43" s="173"/>
+      <c r="M43" s="174">
+        <v>325</v>
+      </c>
+      <c r="N43" s="175"/>
+      <c r="O43" s="176">
+        <v>218</v>
+      </c>
+      <c r="P43" s="177"/>
+      <c r="Q43" s="177">
+        <v>350</v>
+      </c>
+      <c r="R43" s="178"/>
+      <c r="S43" s="173"/>
+      <c r="T43" s="188">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="104">
+        <v>542</v>
+      </c>
+      <c r="U43" s="188">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="104">
+        <v>178268</v>
+      </c>
+      <c r="V43" s="188">
         <f>U43/6</f>
-        <v>0</v>
+        <v>29711.333333333332</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -29450,24 +29787,26 @@
       <c r="B44" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="47"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="46"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="121"/>
-      <c r="O44" s="47"/>
-      <c r="P44" s="111"/>
-      <c r="Q44" s="111"/>
-      <c r="R44" s="46"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="181"/>
+      <c r="F44" s="181"/>
+      <c r="G44" s="181"/>
+      <c r="H44" s="181"/>
+      <c r="I44" s="181"/>
+      <c r="J44" s="182"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="166"/>
+      <c r="M44" s="184"/>
+      <c r="N44" s="185"/>
+      <c r="O44" s="181"/>
+      <c r="P44" s="182"/>
+      <c r="Q44" s="182"/>
+      <c r="R44" s="183"/>
+      <c r="S44" s="166"/>
+      <c r="T44" s="186"/>
+      <c r="U44" s="186"/>
+      <c r="V44" s="186"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="75">
@@ -29477,30 +29816,32 @@
       <c r="B45" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="111"/>
-      <c r="K45" s="46"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="121"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="111"/>
-      <c r="Q45" s="111"/>
-      <c r="R45" s="46"/>
-      <c r="T45" s="50">
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="181"/>
+      <c r="F45" s="181"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="183"/>
+      <c r="L45" s="166"/>
+      <c r="M45" s="184"/>
+      <c r="N45" s="185"/>
+      <c r="O45" s="181"/>
+      <c r="P45" s="182"/>
+      <c r="Q45" s="182"/>
+      <c r="R45" s="183"/>
+      <c r="S45" s="166"/>
+      <c r="T45" s="186">
         <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
         <v>0</v>
       </c>
-      <c r="U45" s="50">
+      <c r="U45" s="186">
         <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
         <v>0</v>
       </c>
-      <c r="V45" s="50">
+      <c r="V45" s="186">
         <f>U45/24</f>
         <v>0</v>
       </c>
@@ -29513,30 +29854,32 @@
       <c r="B46" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="111"/>
-      <c r="K46" s="46"/>
-      <c r="M46" s="52"/>
-      <c r="N46" s="121"/>
-      <c r="O46" s="47"/>
-      <c r="P46" s="111"/>
-      <c r="Q46" s="111"/>
-      <c r="R46" s="46"/>
-      <c r="T46" s="50">
+      <c r="C46" s="181"/>
+      <c r="D46" s="181"/>
+      <c r="E46" s="181"/>
+      <c r="F46" s="181"/>
+      <c r="G46" s="181"/>
+      <c r="H46" s="181"/>
+      <c r="I46" s="181"/>
+      <c r="J46" s="182"/>
+      <c r="K46" s="183"/>
+      <c r="L46" s="166"/>
+      <c r="M46" s="184"/>
+      <c r="N46" s="185"/>
+      <c r="O46" s="181"/>
+      <c r="P46" s="182"/>
+      <c r="Q46" s="182"/>
+      <c r="R46" s="183"/>
+      <c r="S46" s="166"/>
+      <c r="T46" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U46" s="50">
+      <c r="U46" s="186">
         <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
         <v>0</v>
       </c>
-      <c r="V46" s="50">
+      <c r="V46" s="186">
         <f t="shared" ref="V46:V54" si="9">U46/24</f>
         <v>0</v>
       </c>
@@ -29549,32 +29892,47 @@
       <c r="B47" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
-      <c r="I47" s="47"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="46"/>
-      <c r="M47" s="52"/>
-      <c r="N47" s="121"/>
-      <c r="O47" s="47"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="46"/>
-      <c r="T47" s="50">
+      <c r="C47" s="181">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
+      <c r="D47" s="181"/>
+      <c r="E47" s="181"/>
+      <c r="F47" s="181"/>
+      <c r="G47" s="181"/>
+      <c r="H47" s="181"/>
+      <c r="I47" s="181"/>
+      <c r="J47" s="182"/>
+      <c r="K47" s="183">
+        <v>6</v>
+      </c>
+      <c r="L47" s="166"/>
+      <c r="M47" s="184">
+        <v>10</v>
+      </c>
+      <c r="N47" s="185"/>
+      <c r="O47" s="181">
+        <v>5</v>
+      </c>
+      <c r="P47" s="182">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="182">
+        <v>10</v>
+      </c>
+      <c r="R47" s="183"/>
+      <c r="S47" s="166"/>
+      <c r="T47" s="186">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U47" s="50">
+        <v>11</v>
+      </c>
+      <c r="U47" s="186">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="50">
+        <v>14177</v>
+      </c>
+      <c r="V47" s="186">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2362.8333333333335</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -29585,30 +29943,32 @@
       <c r="B48" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="47"/>
-      <c r="I48" s="47"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="46"/>
-      <c r="M48" s="52"/>
-      <c r="N48" s="121"/>
-      <c r="O48" s="47"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="46"/>
-      <c r="T48" s="50">
+      <c r="C48" s="181"/>
+      <c r="D48" s="181"/>
+      <c r="E48" s="181"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="181"/>
+      <c r="H48" s="181"/>
+      <c r="I48" s="181"/>
+      <c r="J48" s="182"/>
+      <c r="K48" s="183"/>
+      <c r="L48" s="166"/>
+      <c r="M48" s="184"/>
+      <c r="N48" s="185"/>
+      <c r="O48" s="181"/>
+      <c r="P48" s="182"/>
+      <c r="Q48" s="182"/>
+      <c r="R48" s="183"/>
+      <c r="S48" s="166"/>
+      <c r="T48" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U48" s="50">
+      <c r="U48" s="186">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V48" s="50">
+      <c r="V48" s="186">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -29621,30 +29981,32 @@
       <c r="B49" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="111"/>
-      <c r="K49" s="46"/>
-      <c r="M49" s="52"/>
-      <c r="N49" s="121"/>
-      <c r="O49" s="47"/>
-      <c r="P49" s="111"/>
-      <c r="Q49" s="111"/>
-      <c r="R49" s="46"/>
-      <c r="T49" s="50">
+      <c r="C49" s="181"/>
+      <c r="D49" s="181"/>
+      <c r="E49" s="181"/>
+      <c r="F49" s="181"/>
+      <c r="G49" s="181"/>
+      <c r="H49" s="181"/>
+      <c r="I49" s="181"/>
+      <c r="J49" s="182"/>
+      <c r="K49" s="183"/>
+      <c r="L49" s="166"/>
+      <c r="M49" s="184"/>
+      <c r="N49" s="185"/>
+      <c r="O49" s="181"/>
+      <c r="P49" s="182"/>
+      <c r="Q49" s="182"/>
+      <c r="R49" s="183"/>
+      <c r="S49" s="166"/>
+      <c r="T49" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U49" s="50">
+      <c r="U49" s="186">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V49" s="50">
+      <c r="V49" s="186">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -29657,30 +30019,32 @@
       <c r="B50" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="46"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="121"/>
-      <c r="O50" s="47"/>
-      <c r="P50" s="111"/>
-      <c r="Q50" s="111"/>
-      <c r="R50" s="46"/>
-      <c r="T50" s="50">
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
+      <c r="F50" s="181"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="182"/>
+      <c r="K50" s="183"/>
+      <c r="L50" s="166"/>
+      <c r="M50" s="184"/>
+      <c r="N50" s="185"/>
+      <c r="O50" s="181"/>
+      <c r="P50" s="182"/>
+      <c r="Q50" s="182"/>
+      <c r="R50" s="183"/>
+      <c r="S50" s="166"/>
+      <c r="T50" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U50" s="50">
+      <c r="U50" s="186">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V50" s="50">
+      <c r="V50" s="186">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -29693,32 +30057,36 @@
       <c r="B51" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="111"/>
-      <c r="K51" s="46"/>
-      <c r="M51" s="52"/>
-      <c r="N51" s="121"/>
-      <c r="O51" s="47"/>
-      <c r="P51" s="111"/>
-      <c r="Q51" s="111"/>
-      <c r="R51" s="46"/>
-      <c r="T51" s="50">
+      <c r="C51" s="181">
+        <v>34</v>
+      </c>
+      <c r="D51" s="181"/>
+      <c r="E51" s="181"/>
+      <c r="F51" s="181"/>
+      <c r="G51" s="181"/>
+      <c r="H51" s="181"/>
+      <c r="I51" s="181"/>
+      <c r="J51" s="182"/>
+      <c r="K51" s="183"/>
+      <c r="L51" s="166"/>
+      <c r="M51" s="184"/>
+      <c r="N51" s="185"/>
+      <c r="O51" s="181"/>
+      <c r="P51" s="182"/>
+      <c r="Q51" s="182"/>
+      <c r="R51" s="183"/>
+      <c r="S51" s="166"/>
+      <c r="T51" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U51" s="50">
+      <c r="U51" s="186">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="50">
+        <v>204</v>
+      </c>
+      <c r="V51" s="186">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -29729,30 +30097,32 @@
       <c r="B52" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="47"/>
-      <c r="I52" s="47"/>
-      <c r="J52" s="111"/>
-      <c r="K52" s="46"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="121"/>
-      <c r="O52" s="47"/>
-      <c r="P52" s="111"/>
-      <c r="Q52" s="111"/>
-      <c r="R52" s="46"/>
-      <c r="T52" s="50">
+      <c r="C52" s="181"/>
+      <c r="D52" s="181"/>
+      <c r="E52" s="181"/>
+      <c r="F52" s="181"/>
+      <c r="G52" s="181"/>
+      <c r="H52" s="181"/>
+      <c r="I52" s="181"/>
+      <c r="J52" s="182"/>
+      <c r="K52" s="183"/>
+      <c r="L52" s="166"/>
+      <c r="M52" s="184"/>
+      <c r="N52" s="185"/>
+      <c r="O52" s="181"/>
+      <c r="P52" s="182"/>
+      <c r="Q52" s="182"/>
+      <c r="R52" s="183"/>
+      <c r="S52" s="166"/>
+      <c r="T52" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U52" s="50">
+      <c r="U52" s="186">
         <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
         <v>0</v>
       </c>
-      <c r="V52" s="50">
+      <c r="V52" s="186">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -29765,32 +30135,36 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="47"/>
-      <c r="D53" s="47"/>
-      <c r="E53" s="47"/>
-      <c r="F53" s="47"/>
-      <c r="G53" s="47"/>
-      <c r="H53" s="47"/>
-      <c r="I53" s="47"/>
-      <c r="J53" s="111"/>
-      <c r="K53" s="46"/>
-      <c r="M53" s="52"/>
-      <c r="N53" s="121"/>
-      <c r="O53" s="47"/>
-      <c r="P53" s="111"/>
-      <c r="Q53" s="111"/>
-      <c r="R53" s="46"/>
-      <c r="T53" s="50">
+      <c r="C53" s="181">
+        <v>2</v>
+      </c>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="181"/>
+      <c r="G53" s="181"/>
+      <c r="H53" s="181"/>
+      <c r="I53" s="181"/>
+      <c r="J53" s="182"/>
+      <c r="K53" s="183"/>
+      <c r="L53" s="166"/>
+      <c r="M53" s="184"/>
+      <c r="N53" s="185"/>
+      <c r="O53" s="181"/>
+      <c r="P53" s="182"/>
+      <c r="Q53" s="182"/>
+      <c r="R53" s="183"/>
+      <c r="S53" s="166"/>
+      <c r="T53" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U53" s="50">
+      <c r="U53" s="186">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="V53" s="50">
+        <v>48</v>
+      </c>
+      <c r="V53" s="186">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -29799,30 +30173,32 @@
         <v>51</v>
       </c>
       <c r="B54" s="74"/>
-      <c r="C54" s="47"/>
-      <c r="D54" s="47"/>
-      <c r="E54" s="47"/>
-      <c r="F54" s="47"/>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
-      <c r="I54" s="47"/>
-      <c r="J54" s="111"/>
-      <c r="K54" s="46"/>
-      <c r="M54" s="52"/>
-      <c r="N54" s="121"/>
-      <c r="O54" s="47"/>
-      <c r="P54" s="111"/>
-      <c r="Q54" s="111"/>
-      <c r="R54" s="46"/>
-      <c r="T54" s="50">
+      <c r="C54" s="181"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="181"/>
+      <c r="G54" s="181"/>
+      <c r="H54" s="181"/>
+      <c r="I54" s="181"/>
+      <c r="J54" s="182"/>
+      <c r="K54" s="183"/>
+      <c r="L54" s="166"/>
+      <c r="M54" s="184"/>
+      <c r="N54" s="185"/>
+      <c r="O54" s="181"/>
+      <c r="P54" s="182"/>
+      <c r="Q54" s="182"/>
+      <c r="R54" s="183"/>
+      <c r="S54" s="166"/>
+      <c r="T54" s="186">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="U54" s="50">
+      <c r="U54" s="186">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="V54" s="50">
+      <c r="V54" s="186">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -29833,24 +30209,26 @@
         <v>52</v>
       </c>
       <c r="B55" s="74"/>
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="47"/>
-      <c r="J55" s="111"/>
-      <c r="K55" s="46"/>
-      <c r="M55" s="52"/>
-      <c r="N55" s="121"/>
-      <c r="O55" s="47"/>
-      <c r="P55" s="111"/>
-      <c r="Q55" s="111"/>
-      <c r="R55" s="46"/>
-      <c r="T55" s="50"/>
-      <c r="U55" s="50"/>
-      <c r="V55" s="50"/>
+      <c r="C55" s="181"/>
+      <c r="D55" s="181"/>
+      <c r="E55" s="181"/>
+      <c r="F55" s="181"/>
+      <c r="G55" s="181"/>
+      <c r="H55" s="181"/>
+      <c r="I55" s="181"/>
+      <c r="J55" s="182"/>
+      <c r="K55" s="183"/>
+      <c r="L55" s="166"/>
+      <c r="M55" s="184"/>
+      <c r="N55" s="185"/>
+      <c r="O55" s="181"/>
+      <c r="P55" s="182"/>
+      <c r="Q55" s="182"/>
+      <c r="R55" s="183"/>
+      <c r="S55" s="166"/>
+      <c r="T55" s="186"/>
+      <c r="U55" s="186"/>
+      <c r="V55" s="186"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="75">
@@ -29858,24 +30236,26 @@
         <v>53</v>
       </c>
       <c r="B56" s="74"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="47"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="47"/>
-      <c r="G56" s="47"/>
-      <c r="H56" s="47"/>
-      <c r="I56" s="47"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="46"/>
-      <c r="M56" s="52"/>
-      <c r="N56" s="121"/>
-      <c r="O56" s="47"/>
-      <c r="P56" s="111"/>
-      <c r="Q56" s="111"/>
-      <c r="R56" s="46"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="50"/>
-      <c r="V56" s="50"/>
+      <c r="C56" s="181"/>
+      <c r="D56" s="181"/>
+      <c r="E56" s="181"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="182"/>
+      <c r="K56" s="183"/>
+      <c r="L56" s="166"/>
+      <c r="M56" s="184"/>
+      <c r="N56" s="185"/>
+      <c r="O56" s="181"/>
+      <c r="P56" s="182"/>
+      <c r="Q56" s="182"/>
+      <c r="R56" s="183"/>
+      <c r="S56" s="166"/>
+      <c r="T56" s="186"/>
+      <c r="U56" s="186"/>
+      <c r="V56" s="186"/>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="75">
@@ -29883,24 +30263,26 @@
         <v>54</v>
       </c>
       <c r="B57" s="74"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="47"/>
-      <c r="H57" s="47"/>
-      <c r="I57" s="47"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="46"/>
-      <c r="M57" s="52"/>
-      <c r="N57" s="121"/>
-      <c r="O57" s="47"/>
-      <c r="P57" s="111"/>
-      <c r="Q57" s="111"/>
-      <c r="R57" s="46"/>
-      <c r="T57" s="50"/>
-      <c r="U57" s="50"/>
-      <c r="V57" s="50"/>
+      <c r="C57" s="181"/>
+      <c r="D57" s="181"/>
+      <c r="E57" s="181"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="182"/>
+      <c r="K57" s="183"/>
+      <c r="L57" s="166"/>
+      <c r="M57" s="184"/>
+      <c r="N57" s="185"/>
+      <c r="O57" s="181"/>
+      <c r="P57" s="182"/>
+      <c r="Q57" s="182"/>
+      <c r="R57" s="183"/>
+      <c r="S57" s="166"/>
+      <c r="T57" s="186"/>
+      <c r="U57" s="186"/>
+      <c r="V57" s="186"/>
     </row>
     <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="77" t="s">
@@ -29908,7 +30290,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>41336</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -29922,56 +30304,56 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="57"/>
+        <v>8</v>
+      </c>
+      <c r="S58" s="166"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="U58" s="51">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>350831</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>42636.583333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -29979,17 +30361,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="149" t="s">
+      <c r="C60" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="150"/>
-      <c r="E60" s="150"/>
-      <c r="F60" s="150"/>
-      <c r="G60" s="150"/>
-      <c r="H60" s="150"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="150"/>
-      <c r="K60" s="151"/>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -30248,6 +30630,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F5F771-BE68-4A3A-A924-82C895121F0F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="153" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="159" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="161" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="154" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="156" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="157"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="142"/>
+      <c r="Q5" s="142"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="165"/>
+      <c r="L7" s="166"/>
+      <c r="M7" s="167"/>
+      <c r="N7" s="168"/>
+      <c r="O7" s="163"/>
+      <c r="P7" s="164"/>
+      <c r="Q7" s="164"/>
+      <c r="R7" s="165"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="169">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="169">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="169">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="170"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="171"/>
+      <c r="K8" s="172"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="174"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="176"/>
+      <c r="P8" s="177"/>
+      <c r="Q8" s="177"/>
+      <c r="R8" s="178"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="179">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="180">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="180">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="181"/>
+      <c r="D9" s="181"/>
+      <c r="E9" s="181"/>
+      <c r="F9" s="181"/>
+      <c r="G9" s="181"/>
+      <c r="H9" s="181"/>
+      <c r="I9" s="181"/>
+      <c r="J9" s="182"/>
+      <c r="K9" s="183"/>
+      <c r="L9" s="166"/>
+      <c r="M9" s="184"/>
+      <c r="N9" s="185"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="182"/>
+      <c r="Q9" s="182"/>
+      <c r="R9" s="183"/>
+      <c r="S9" s="166"/>
+      <c r="T9" s="186">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="187">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="187">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="181"/>
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="181"/>
+      <c r="I10" s="181"/>
+      <c r="J10" s="182"/>
+      <c r="K10" s="183"/>
+      <c r="L10" s="166"/>
+      <c r="M10" s="184"/>
+      <c r="N10" s="185"/>
+      <c r="O10" s="181"/>
+      <c r="P10" s="182"/>
+      <c r="Q10" s="182"/>
+      <c r="R10" s="183"/>
+      <c r="S10" s="166"/>
+      <c r="T10" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="169">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="181"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="181"/>
+      <c r="F11" s="181"/>
+      <c r="G11" s="181"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
+      <c r="K11" s="183"/>
+      <c r="L11" s="166"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="185"/>
+      <c r="O11" s="181"/>
+      <c r="P11" s="182"/>
+      <c r="Q11" s="182"/>
+      <c r="R11" s="183"/>
+      <c r="S11" s="166"/>
+      <c r="T11" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="169">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="169">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="170"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="173"/>
+      <c r="M12" s="174"/>
+      <c r="N12" s="175"/>
+      <c r="O12" s="176"/>
+      <c r="P12" s="177"/>
+      <c r="Q12" s="177"/>
+      <c r="R12" s="178"/>
+      <c r="S12" s="173"/>
+      <c r="T12" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="180">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="180">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="181"/>
+      <c r="D13" s="181"/>
+      <c r="E13" s="181"/>
+      <c r="F13" s="181"/>
+      <c r="G13" s="181"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="182"/>
+      <c r="K13" s="183"/>
+      <c r="L13" s="166"/>
+      <c r="M13" s="184"/>
+      <c r="N13" s="185"/>
+      <c r="O13" s="181"/>
+      <c r="P13" s="182"/>
+      <c r="Q13" s="182"/>
+      <c r="R13" s="183"/>
+      <c r="S13" s="166"/>
+      <c r="T13" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="187">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="187">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="181"/>
+      <c r="D14" s="181"/>
+      <c r="E14" s="181"/>
+      <c r="F14" s="181"/>
+      <c r="G14" s="181"/>
+      <c r="H14" s="181"/>
+      <c r="I14" s="181"/>
+      <c r="J14" s="182"/>
+      <c r="K14" s="183"/>
+      <c r="L14" s="166"/>
+      <c r="M14" s="184"/>
+      <c r="N14" s="185"/>
+      <c r="O14" s="181"/>
+      <c r="P14" s="182"/>
+      <c r="Q14" s="182"/>
+      <c r="R14" s="183"/>
+      <c r="S14" s="166"/>
+      <c r="T14" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="186">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="186">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="181"/>
+      <c r="D15" s="181"/>
+      <c r="E15" s="181"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="181"/>
+      <c r="H15" s="181"/>
+      <c r="I15" s="181"/>
+      <c r="J15" s="182"/>
+      <c r="K15" s="183"/>
+      <c r="L15" s="166"/>
+      <c r="M15" s="184"/>
+      <c r="N15" s="185"/>
+      <c r="O15" s="181"/>
+      <c r="P15" s="182"/>
+      <c r="Q15" s="182"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="166"/>
+      <c r="T15" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="181"/>
+      <c r="H16" s="181"/>
+      <c r="I16" s="181"/>
+      <c r="J16" s="182"/>
+      <c r="K16" s="183"/>
+      <c r="L16" s="166"/>
+      <c r="M16" s="184"/>
+      <c r="N16" s="185"/>
+      <c r="O16" s="181"/>
+      <c r="P16" s="182"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="183"/>
+      <c r="S16" s="166"/>
+      <c r="T16" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="181"/>
+      <c r="D17" s="181"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="181"/>
+      <c r="H17" s="181"/>
+      <c r="I17" s="181"/>
+      <c r="J17" s="182"/>
+      <c r="K17" s="183"/>
+      <c r="L17" s="166"/>
+      <c r="M17" s="184"/>
+      <c r="N17" s="185"/>
+      <c r="O17" s="181"/>
+      <c r="P17" s="182"/>
+      <c r="Q17" s="182"/>
+      <c r="R17" s="183"/>
+      <c r="S17" s="166"/>
+      <c r="T17" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="181"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="181"/>
+      <c r="F18" s="181"/>
+      <c r="G18" s="181"/>
+      <c r="H18" s="181"/>
+      <c r="I18" s="181"/>
+      <c r="J18" s="182"/>
+      <c r="K18" s="183"/>
+      <c r="L18" s="166"/>
+      <c r="M18" s="184"/>
+      <c r="N18" s="185"/>
+      <c r="O18" s="181"/>
+      <c r="P18" s="182"/>
+      <c r="Q18" s="182"/>
+      <c r="R18" s="183"/>
+      <c r="S18" s="166"/>
+      <c r="T18" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="181"/>
+      <c r="D19" s="181"/>
+      <c r="E19" s="181"/>
+      <c r="F19" s="181"/>
+      <c r="G19" s="181"/>
+      <c r="H19" s="181"/>
+      <c r="I19" s="181"/>
+      <c r="J19" s="182"/>
+      <c r="K19" s="183"/>
+      <c r="L19" s="166"/>
+      <c r="M19" s="184"/>
+      <c r="N19" s="185"/>
+      <c r="O19" s="181"/>
+      <c r="P19" s="182"/>
+      <c r="Q19" s="182"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="166"/>
+      <c r="T19" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="181"/>
+      <c r="D20" s="181"/>
+      <c r="E20" s="181"/>
+      <c r="F20" s="181"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="181"/>
+      <c r="I20" s="181"/>
+      <c r="J20" s="182"/>
+      <c r="K20" s="183"/>
+      <c r="L20" s="166"/>
+      <c r="M20" s="184"/>
+      <c r="N20" s="185"/>
+      <c r="O20" s="181"/>
+      <c r="P20" s="182"/>
+      <c r="Q20" s="182"/>
+      <c r="R20" s="183"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="181"/>
+      <c r="D21" s="181"/>
+      <c r="E21" s="181"/>
+      <c r="F21" s="181"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="182"/>
+      <c r="K21" s="183"/>
+      <c r="L21" s="166"/>
+      <c r="M21" s="184"/>
+      <c r="N21" s="185"/>
+      <c r="O21" s="181"/>
+      <c r="P21" s="182"/>
+      <c r="Q21" s="182"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="166"/>
+      <c r="T21" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="181"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="181"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="181"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="182"/>
+      <c r="K22" s="183"/>
+      <c r="L22" s="166"/>
+      <c r="M22" s="184"/>
+      <c r="N22" s="185"/>
+      <c r="O22" s="181"/>
+      <c r="P22" s="182"/>
+      <c r="Q22" s="182"/>
+      <c r="R22" s="183"/>
+      <c r="S22" s="166"/>
+      <c r="T22" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="181"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="181"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="181"/>
+      <c r="I23" s="181"/>
+      <c r="J23" s="182"/>
+      <c r="K23" s="183"/>
+      <c r="L23" s="166"/>
+      <c r="M23" s="184"/>
+      <c r="N23" s="185"/>
+      <c r="O23" s="181"/>
+      <c r="P23" s="182"/>
+      <c r="Q23" s="182"/>
+      <c r="R23" s="183"/>
+      <c r="S23" s="166"/>
+      <c r="T23" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="181"/>
+      <c r="D24" s="181"/>
+      <c r="E24" s="181"/>
+      <c r="F24" s="181"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="181"/>
+      <c r="I24" s="181"/>
+      <c r="J24" s="182"/>
+      <c r="K24" s="183"/>
+      <c r="L24" s="166"/>
+      <c r="M24" s="184"/>
+      <c r="N24" s="185"/>
+      <c r="O24" s="181"/>
+      <c r="P24" s="182"/>
+      <c r="Q24" s="182"/>
+      <c r="R24" s="183"/>
+      <c r="S24" s="166"/>
+      <c r="T24" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="181"/>
+      <c r="D25" s="181"/>
+      <c r="E25" s="181"/>
+      <c r="F25" s="181"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="181"/>
+      <c r="I25" s="181"/>
+      <c r="J25" s="182"/>
+      <c r="K25" s="183"/>
+      <c r="L25" s="166"/>
+      <c r="M25" s="184"/>
+      <c r="N25" s="185"/>
+      <c r="O25" s="181"/>
+      <c r="P25" s="182"/>
+      <c r="Q25" s="182"/>
+      <c r="R25" s="183"/>
+      <c r="S25" s="166"/>
+      <c r="T25" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="181"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="181"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="181"/>
+      <c r="I26" s="181"/>
+      <c r="J26" s="182"/>
+      <c r="K26" s="183"/>
+      <c r="L26" s="166"/>
+      <c r="M26" s="184"/>
+      <c r="N26" s="185"/>
+      <c r="O26" s="181"/>
+      <c r="P26" s="182"/>
+      <c r="Q26" s="182"/>
+      <c r="R26" s="183"/>
+      <c r="S26" s="166"/>
+      <c r="T26" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="181"/>
+      <c r="D27" s="181"/>
+      <c r="E27" s="181"/>
+      <c r="F27" s="181"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="181"/>
+      <c r="I27" s="181"/>
+      <c r="J27" s="182"/>
+      <c r="K27" s="183"/>
+      <c r="L27" s="166"/>
+      <c r="M27" s="184"/>
+      <c r="N27" s="185"/>
+      <c r="O27" s="181"/>
+      <c r="P27" s="182"/>
+      <c r="Q27" s="182"/>
+      <c r="R27" s="183"/>
+      <c r="S27" s="166"/>
+      <c r="T27" s="169"/>
+      <c r="U27" s="186"/>
+      <c r="V27" s="186"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="181"/>
+      <c r="D28" s="181"/>
+      <c r="E28" s="181"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="181"/>
+      <c r="I28" s="181"/>
+      <c r="J28" s="182"/>
+      <c r="K28" s="183"/>
+      <c r="L28" s="166"/>
+      <c r="M28" s="184"/>
+      <c r="N28" s="185"/>
+      <c r="O28" s="181"/>
+      <c r="P28" s="182"/>
+      <c r="Q28" s="182"/>
+      <c r="R28" s="183"/>
+      <c r="S28" s="166"/>
+      <c r="T28" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="181"/>
+      <c r="D29" s="181"/>
+      <c r="E29" s="181"/>
+      <c r="F29" s="181"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="181"/>
+      <c r="I29" s="181"/>
+      <c r="J29" s="182"/>
+      <c r="K29" s="183"/>
+      <c r="L29" s="166"/>
+      <c r="M29" s="184"/>
+      <c r="N29" s="185"/>
+      <c r="O29" s="181"/>
+      <c r="P29" s="182"/>
+      <c r="Q29" s="182"/>
+      <c r="R29" s="183"/>
+      <c r="S29" s="166"/>
+      <c r="T29" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="181"/>
+      <c r="D30" s="181"/>
+      <c r="E30" s="181"/>
+      <c r="F30" s="181"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="181"/>
+      <c r="I30" s="181"/>
+      <c r="J30" s="182"/>
+      <c r="K30" s="183"/>
+      <c r="L30" s="166"/>
+      <c r="M30" s="184"/>
+      <c r="N30" s="185"/>
+      <c r="O30" s="181"/>
+      <c r="P30" s="182"/>
+      <c r="Q30" s="182"/>
+      <c r="R30" s="183"/>
+      <c r="S30" s="166"/>
+      <c r="T30" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="181"/>
+      <c r="D31" s="181"/>
+      <c r="E31" s="181"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="181"/>
+      <c r="H31" s="181"/>
+      <c r="I31" s="181"/>
+      <c r="J31" s="182"/>
+      <c r="K31" s="183"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="184"/>
+      <c r="N31" s="185"/>
+      <c r="O31" s="181"/>
+      <c r="P31" s="182"/>
+      <c r="Q31" s="182"/>
+      <c r="R31" s="183"/>
+      <c r="S31" s="166"/>
+      <c r="T31" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="181"/>
+      <c r="D32" s="181"/>
+      <c r="E32" s="181"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="181"/>
+      <c r="H32" s="181"/>
+      <c r="I32" s="181"/>
+      <c r="J32" s="182"/>
+      <c r="K32" s="183"/>
+      <c r="L32" s="166"/>
+      <c r="M32" s="184"/>
+      <c r="N32" s="185"/>
+      <c r="O32" s="181"/>
+      <c r="P32" s="182"/>
+      <c r="Q32" s="182"/>
+      <c r="R32" s="183"/>
+      <c r="S32" s="166"/>
+      <c r="T32" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="182"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="166"/>
+      <c r="M33" s="184"/>
+      <c r="N33" s="185"/>
+      <c r="O33" s="181"/>
+      <c r="P33" s="182"/>
+      <c r="Q33" s="182"/>
+      <c r="R33" s="183"/>
+      <c r="S33" s="166"/>
+      <c r="T33" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="181"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="182"/>
+      <c r="K34" s="183"/>
+      <c r="L34" s="166"/>
+      <c r="M34" s="184"/>
+      <c r="N34" s="185"/>
+      <c r="O34" s="181"/>
+      <c r="P34" s="182"/>
+      <c r="Q34" s="182"/>
+      <c r="R34" s="183"/>
+      <c r="S34" s="166"/>
+      <c r="T34" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="181"/>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="181"/>
+      <c r="H35" s="181"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="182"/>
+      <c r="K35" s="183"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="184"/>
+      <c r="N35" s="185"/>
+      <c r="O35" s="181"/>
+      <c r="P35" s="182"/>
+      <c r="Q35" s="182"/>
+      <c r="R35" s="183"/>
+      <c r="S35" s="166"/>
+      <c r="T35" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="181"/>
+      <c r="D36" s="181"/>
+      <c r="E36" s="181"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="181"/>
+      <c r="H36" s="181"/>
+      <c r="I36" s="181"/>
+      <c r="J36" s="182"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="166"/>
+      <c r="M36" s="184"/>
+      <c r="N36" s="185"/>
+      <c r="O36" s="181"/>
+      <c r="P36" s="182"/>
+      <c r="Q36" s="182"/>
+      <c r="R36" s="183"/>
+      <c r="S36" s="166"/>
+      <c r="T36" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="186">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="186">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="170"/>
+      <c r="D37" s="170"/>
+      <c r="E37" s="170"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="170"/>
+      <c r="I37" s="170"/>
+      <c r="J37" s="171"/>
+      <c r="K37" s="172"/>
+      <c r="L37" s="173"/>
+      <c r="M37" s="174"/>
+      <c r="N37" s="175"/>
+      <c r="O37" s="176"/>
+      <c r="P37" s="177"/>
+      <c r="Q37" s="177"/>
+      <c r="R37" s="178"/>
+      <c r="S37" s="173"/>
+      <c r="T37" s="188">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="188">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="188">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="181"/>
+      <c r="D38" s="181"/>
+      <c r="E38" s="181"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="181"/>
+      <c r="H38" s="181"/>
+      <c r="I38" s="181"/>
+      <c r="J38" s="182"/>
+      <c r="K38" s="183"/>
+      <c r="L38" s="166"/>
+      <c r="M38" s="184"/>
+      <c r="N38" s="185"/>
+      <c r="O38" s="181"/>
+      <c r="P38" s="182"/>
+      <c r="Q38" s="182"/>
+      <c r="R38" s="183"/>
+      <c r="S38" s="166"/>
+      <c r="T38" s="186">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="186">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="186">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="189"/>
+      <c r="D39" s="189"/>
+      <c r="E39" s="189"/>
+      <c r="F39" s="189"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="189"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="166"/>
+      <c r="M39" s="192"/>
+      <c r="N39" s="193"/>
+      <c r="O39" s="189"/>
+      <c r="P39" s="190"/>
+      <c r="Q39" s="190"/>
+      <c r="R39" s="191"/>
+      <c r="S39" s="166"/>
+      <c r="T39" s="194"/>
+      <c r="U39" s="194"/>
+      <c r="V39" s="194"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="170"/>
+      <c r="D40" s="170"/>
+      <c r="E40" s="170"/>
+      <c r="F40" s="170"/>
+      <c r="G40" s="170"/>
+      <c r="H40" s="170"/>
+      <c r="I40" s="170"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="172"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="174"/>
+      <c r="N40" s="175"/>
+      <c r="O40" s="176"/>
+      <c r="P40" s="177"/>
+      <c r="Q40" s="177"/>
+      <c r="R40" s="178"/>
+      <c r="S40" s="173"/>
+      <c r="T40" s="188">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="188">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="188">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="195"/>
+      <c r="D41" s="195"/>
+      <c r="E41" s="195"/>
+      <c r="F41" s="195"/>
+      <c r="G41" s="195"/>
+      <c r="H41" s="195"/>
+      <c r="I41" s="195"/>
+      <c r="J41" s="196"/>
+      <c r="K41" s="197"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="199"/>
+      <c r="N41" s="200"/>
+      <c r="O41" s="195"/>
+      <c r="P41" s="196"/>
+      <c r="Q41" s="196"/>
+      <c r="R41" s="197"/>
+      <c r="S41" s="198"/>
+      <c r="T41" s="201">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="201">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="201">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="181"/>
+      <c r="D42" s="181"/>
+      <c r="E42" s="181"/>
+      <c r="F42" s="181"/>
+      <c r="G42" s="181"/>
+      <c r="H42" s="181"/>
+      <c r="I42" s="181"/>
+      <c r="J42" s="182"/>
+      <c r="K42" s="183"/>
+      <c r="L42" s="166"/>
+      <c r="M42" s="184"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="181"/>
+      <c r="P42" s="182"/>
+      <c r="Q42" s="182"/>
+      <c r="R42" s="183"/>
+      <c r="S42" s="166"/>
+      <c r="T42" s="186"/>
+      <c r="U42" s="186"/>
+      <c r="V42" s="186"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="176"/>
+      <c r="D43" s="176"/>
+      <c r="E43" s="176"/>
+      <c r="F43" s="176"/>
+      <c r="G43" s="176"/>
+      <c r="H43" s="176"/>
+      <c r="I43" s="176"/>
+      <c r="J43" s="177"/>
+      <c r="K43" s="178"/>
+      <c r="L43" s="173"/>
+      <c r="M43" s="174"/>
+      <c r="N43" s="175"/>
+      <c r="O43" s="176"/>
+      <c r="P43" s="177"/>
+      <c r="Q43" s="177"/>
+      <c r="R43" s="178"/>
+      <c r="S43" s="173"/>
+      <c r="T43" s="188">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="188">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="188">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="181"/>
+      <c r="F44" s="181"/>
+      <c r="G44" s="181"/>
+      <c r="H44" s="181"/>
+      <c r="I44" s="181"/>
+      <c r="J44" s="182"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="166"/>
+      <c r="M44" s="184"/>
+      <c r="N44" s="185"/>
+      <c r="O44" s="181"/>
+      <c r="P44" s="182"/>
+      <c r="Q44" s="182"/>
+      <c r="R44" s="183"/>
+      <c r="S44" s="166"/>
+      <c r="T44" s="186"/>
+      <c r="U44" s="186"/>
+      <c r="V44" s="186"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="181"/>
+      <c r="F45" s="181"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="182"/>
+      <c r="K45" s="183"/>
+      <c r="L45" s="166"/>
+      <c r="M45" s="184"/>
+      <c r="N45" s="185"/>
+      <c r="O45" s="181"/>
+      <c r="P45" s="182"/>
+      <c r="Q45" s="182"/>
+      <c r="R45" s="183"/>
+      <c r="S45" s="166"/>
+      <c r="T45" s="186">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="186">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="186">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="181"/>
+      <c r="D46" s="181"/>
+      <c r="E46" s="181"/>
+      <c r="F46" s="181"/>
+      <c r="G46" s="181"/>
+      <c r="H46" s="181"/>
+      <c r="I46" s="181"/>
+      <c r="J46" s="182"/>
+      <c r="K46" s="183"/>
+      <c r="L46" s="166"/>
+      <c r="M46" s="184"/>
+      <c r="N46" s="185"/>
+      <c r="O46" s="181"/>
+      <c r="P46" s="182"/>
+      <c r="Q46" s="182"/>
+      <c r="R46" s="183"/>
+      <c r="S46" s="166"/>
+      <c r="T46" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="186">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="186">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="176"/>
+      <c r="D47" s="176"/>
+      <c r="E47" s="176"/>
+      <c r="F47" s="176"/>
+      <c r="G47" s="176"/>
+      <c r="H47" s="176"/>
+      <c r="I47" s="176"/>
+      <c r="J47" s="177"/>
+      <c r="K47" s="178"/>
+      <c r="L47" s="173"/>
+      <c r="M47" s="174"/>
+      <c r="N47" s="175"/>
+      <c r="O47" s="176"/>
+      <c r="P47" s="177"/>
+      <c r="Q47" s="177"/>
+      <c r="R47" s="178"/>
+      <c r="S47" s="173"/>
+      <c r="T47" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="188">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="188">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="181"/>
+      <c r="D48" s="181"/>
+      <c r="E48" s="181"/>
+      <c r="F48" s="181"/>
+      <c r="G48" s="181"/>
+      <c r="H48" s="181"/>
+      <c r="I48" s="181"/>
+      <c r="J48" s="182"/>
+      <c r="K48" s="183"/>
+      <c r="L48" s="166"/>
+      <c r="M48" s="184"/>
+      <c r="N48" s="185"/>
+      <c r="O48" s="181"/>
+      <c r="P48" s="182"/>
+      <c r="Q48" s="182"/>
+      <c r="R48" s="183"/>
+      <c r="S48" s="166"/>
+      <c r="T48" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="186">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="181"/>
+      <c r="D49" s="181"/>
+      <c r="E49" s="181"/>
+      <c r="F49" s="181"/>
+      <c r="G49" s="181"/>
+      <c r="H49" s="181"/>
+      <c r="I49" s="181"/>
+      <c r="J49" s="182"/>
+      <c r="K49" s="183"/>
+      <c r="L49" s="166"/>
+      <c r="M49" s="184"/>
+      <c r="N49" s="185"/>
+      <c r="O49" s="181"/>
+      <c r="P49" s="182"/>
+      <c r="Q49" s="182"/>
+      <c r="R49" s="183"/>
+      <c r="S49" s="166"/>
+      <c r="T49" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="186">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="181"/>
+      <c r="F50" s="181"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="182"/>
+      <c r="K50" s="183"/>
+      <c r="L50" s="166"/>
+      <c r="M50" s="184"/>
+      <c r="N50" s="185"/>
+      <c r="O50" s="181"/>
+      <c r="P50" s="182"/>
+      <c r="Q50" s="182"/>
+      <c r="R50" s="183"/>
+      <c r="S50" s="166"/>
+      <c r="T50" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="186">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="176"/>
+      <c r="D51" s="176"/>
+      <c r="E51" s="176"/>
+      <c r="F51" s="176"/>
+      <c r="G51" s="176"/>
+      <c r="H51" s="176"/>
+      <c r="I51" s="176"/>
+      <c r="J51" s="177"/>
+      <c r="K51" s="178"/>
+      <c r="L51" s="173"/>
+      <c r="M51" s="174"/>
+      <c r="N51" s="175"/>
+      <c r="O51" s="176"/>
+      <c r="P51" s="177"/>
+      <c r="Q51" s="177"/>
+      <c r="R51" s="178"/>
+      <c r="S51" s="173"/>
+      <c r="T51" s="188">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="188">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="188">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="181"/>
+      <c r="D52" s="181"/>
+      <c r="E52" s="181"/>
+      <c r="F52" s="181"/>
+      <c r="G52" s="181"/>
+      <c r="H52" s="181"/>
+      <c r="I52" s="181"/>
+      <c r="J52" s="182"/>
+      <c r="K52" s="183"/>
+      <c r="L52" s="166"/>
+      <c r="M52" s="184"/>
+      <c r="N52" s="185"/>
+      <c r="O52" s="181"/>
+      <c r="P52" s="182"/>
+      <c r="Q52" s="182"/>
+      <c r="R52" s="183"/>
+      <c r="S52" s="166"/>
+      <c r="T52" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="186">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="181"/>
+      <c r="D53" s="181"/>
+      <c r="E53" s="181"/>
+      <c r="F53" s="181"/>
+      <c r="G53" s="181"/>
+      <c r="H53" s="181"/>
+      <c r="I53" s="181"/>
+      <c r="J53" s="182"/>
+      <c r="K53" s="183"/>
+      <c r="L53" s="166"/>
+      <c r="M53" s="184"/>
+      <c r="N53" s="185"/>
+      <c r="O53" s="181"/>
+      <c r="P53" s="182"/>
+      <c r="Q53" s="182"/>
+      <c r="R53" s="183"/>
+      <c r="S53" s="166"/>
+      <c r="T53" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="186">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="181"/>
+      <c r="D54" s="181"/>
+      <c r="E54" s="181"/>
+      <c r="F54" s="181"/>
+      <c r="G54" s="181"/>
+      <c r="H54" s="181"/>
+      <c r="I54" s="181"/>
+      <c r="J54" s="182"/>
+      <c r="K54" s="183"/>
+      <c r="L54" s="166"/>
+      <c r="M54" s="184"/>
+      <c r="N54" s="185"/>
+      <c r="O54" s="181"/>
+      <c r="P54" s="182"/>
+      <c r="Q54" s="182"/>
+      <c r="R54" s="183"/>
+      <c r="S54" s="166"/>
+      <c r="T54" s="186">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="186">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="186">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="181"/>
+      <c r="D55" s="181"/>
+      <c r="E55" s="181"/>
+      <c r="F55" s="181"/>
+      <c r="G55" s="181"/>
+      <c r="H55" s="181"/>
+      <c r="I55" s="181"/>
+      <c r="J55" s="182"/>
+      <c r="K55" s="183"/>
+      <c r="L55" s="166"/>
+      <c r="M55" s="184"/>
+      <c r="N55" s="185"/>
+      <c r="O55" s="181"/>
+      <c r="P55" s="182"/>
+      <c r="Q55" s="182"/>
+      <c r="R55" s="183"/>
+      <c r="S55" s="166"/>
+      <c r="T55" s="186"/>
+      <c r="U55" s="186"/>
+      <c r="V55" s="186"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="181"/>
+      <c r="D56" s="181"/>
+      <c r="E56" s="181"/>
+      <c r="F56" s="181"/>
+      <c r="G56" s="181"/>
+      <c r="H56" s="181"/>
+      <c r="I56" s="181"/>
+      <c r="J56" s="182"/>
+      <c r="K56" s="183"/>
+      <c r="L56" s="166"/>
+      <c r="M56" s="184"/>
+      <c r="N56" s="185"/>
+      <c r="O56" s="181"/>
+      <c r="P56" s="182"/>
+      <c r="Q56" s="182"/>
+      <c r="R56" s="183"/>
+      <c r="S56" s="166"/>
+      <c r="T56" s="186"/>
+      <c r="U56" s="186"/>
+      <c r="V56" s="186"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="181"/>
+      <c r="D57" s="181"/>
+      <c r="E57" s="181"/>
+      <c r="F57" s="181"/>
+      <c r="G57" s="181"/>
+      <c r="H57" s="181"/>
+      <c r="I57" s="181"/>
+      <c r="J57" s="182"/>
+      <c r="K57" s="183"/>
+      <c r="L57" s="166"/>
+      <c r="M57" s="184"/>
+      <c r="N57" s="185"/>
+      <c r="O57" s="181"/>
+      <c r="P57" s="182"/>
+      <c r="Q57" s="182"/>
+      <c r="R57" s="183"/>
+      <c r="S57" s="166"/>
+      <c r="T57" s="186"/>
+      <c r="U57" s="186"/>
+      <c r="V57" s="186"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="166"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="151"/>
+      <c r="E60" s="151"/>
+      <c r="F60" s="151"/>
+      <c r="G60" s="151"/>
+      <c r="H60" s="151"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="152"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -30289,16 +33592,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="152" t="s">
+      <c r="H1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -30310,15 +33613,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="149"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -31967,15 +35270,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="152"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -32248,21 +35551,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -32274,17 +35577,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -32304,13 +35607,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -32350,10 +35653,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -32361,9 +35664,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -34968,17 +38271,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35287,21 +38590,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35313,17 +38616,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35343,13 +38646,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35389,10 +38692,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35400,9 +38703,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38000,17 +41303,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -38319,21 +41622,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38345,17 +41648,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38375,13 +41678,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38421,10 +41724,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38432,9 +41735,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41041,17 +44344,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -41360,21 +44663,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41386,17 +44689,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41416,13 +44719,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41462,10 +44765,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41473,9 +44776,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44075,17 +47378,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -44394,21 +47697,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44420,17 +47723,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44450,13 +47753,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44496,10 +47799,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44507,9 +47810,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47091,17 +50394,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -47410,21 +50713,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47436,17 +50739,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -47466,13 +50769,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -47512,10 +50815,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -47523,9 +50826,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -50105,17 +53408,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -50424,21 +53727,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-      <c r="M1" s="152"/>
-      <c r="N1" s="152"/>
-      <c r="O1" s="152"/>
-      <c r="P1" s="152"/>
-      <c r="Q1" s="152"/>
-      <c r="R1" s="152"/>
-      <c r="S1" s="152"/>
-      <c r="T1" s="152"/>
-      <c r="U1" s="152"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -50450,17 +53753,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="147" t="s">
+      <c r="C4" s="148" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="149"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -50480,13 +53783,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="159" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="160" t="s">
+      <c r="U4" s="161" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="153" t="s">
+      <c r="V4" s="154" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -50526,10 +53829,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="155" t="s">
+      <c r="J5" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="156"/>
+      <c r="K5" s="157"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -50537,9 +53840,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="159"/>
-      <c r="U5" s="161"/>
-      <c r="V5" s="154"/>
+      <c r="T5" s="160"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="155"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -53126,17 +56429,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="149" t="s">
+      <c r="C59" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="150"/>
-      <c r="E59" s="150"/>
-      <c r="F59" s="150"/>
-      <c r="G59" s="150"/>
-      <c r="H59" s="150"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="150"/>
-      <c r="K59" s="151"/>
+      <c r="D59" s="151"/>
+      <c r="E59" s="151"/>
+      <c r="F59" s="151"/>
+      <c r="G59" s="151"/>
+      <c r="H59" s="151"/>
+      <c r="I59" s="151"/>
+      <c r="J59" s="151"/>
+      <c r="K59" s="152"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A844D4-7D29-444E-9416-339E28F3FC05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D8DC9-D792-4BA6-ABA7-FB9B03E1BBB2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="10" activeTab="17" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -31,9 +31,10 @@
     <sheet name="02-17-2026" sheetId="25" r:id="rId16"/>
     <sheet name="02-18-2026" sheetId="24" r:id="rId17"/>
     <sheet name="02-19-2026" sheetId="26" r:id="rId18"/>
-    <sheet name="02-20-2026" sheetId="28" r:id="rId19"/>
+    <sheet name="02-20-2026__" sheetId="28" r:id="rId19"/>
     <sheet name="02-21-2026" sheetId="29" r:id="rId20"/>
     <sheet name="02-23-2026" sheetId="30" r:id="rId21"/>
+    <sheet name="02-25-2026" sheetId="31" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -51,9 +52,10 @@
     <definedName name="_xlnm.Print_Area" localSheetId="15">'02-17-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="16">'02-18-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="17">'02-19-2026'!$A$1:$W$59</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'02-20-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'02-20-2026__'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'02-21-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'02-23-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'02-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -74,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="102">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -378,6 +380,9 @@
   </si>
   <si>
     <t>DATE: 02/23/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/25/2026</t>
   </si>
 </sst>
 </file>
@@ -1511,7 +1516,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2072,6 +2077,9 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3387,34 +3395,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="186" t="s">
+      <c r="A21" s="187" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="183" t="s">
+      <c r="B21" s="184" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="184"/>
-      <c r="D21" s="185"/>
-      <c r="E21" s="183" t="s">
+      <c r="C21" s="185"/>
+      <c r="D21" s="186"/>
+      <c r="E21" s="184" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="184"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="183" t="s">
+      <c r="F21" s="185"/>
+      <c r="G21" s="186"/>
+      <c r="H21" s="184" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="184"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="183" t="s">
+      <c r="I21" s="185"/>
+      <c r="J21" s="186"/>
+      <c r="K21" s="184" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="184"/>
-      <c r="M21" s="185"/>
-      <c r="N21" s="183" t="s">
+      <c r="L21" s="185"/>
+      <c r="M21" s="186"/>
+      <c r="N21" s="184" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="184"/>
-      <c r="P21" s="185"/>
+      <c r="O21" s="185"/>
+      <c r="P21" s="186"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3437,7 +3445,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="187"/>
+      <c r="A22" s="188"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3661,21 +3669,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3687,17 +3695,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3717,13 +3725,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3763,10 +3771,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3774,9 +3782,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6359,17 +6367,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6678,21 +6686,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6704,17 +6712,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6734,13 +6742,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6780,10 +6788,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6791,9 +6799,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9372,17 +9380,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9691,21 +9699,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9717,17 +9725,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9747,13 +9755,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9793,10 +9801,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9804,9 +9812,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12376,17 +12384,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12695,21 +12703,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12721,17 +12729,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12751,13 +12759,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12797,10 +12805,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12808,9 +12816,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15394,17 +15402,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15713,21 +15721,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15739,17 +15747,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15769,13 +15777,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15815,10 +15823,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15826,9 +15834,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18402,17 +18410,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18721,21 +18729,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18747,17 +18755,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18777,13 +18785,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18823,10 +18831,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18834,9 +18842,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21243,17 +21251,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21562,21 +21570,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21588,17 +21596,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21618,13 +21626,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21664,10 +21672,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21675,9 +21683,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24263,17 +24271,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24582,21 +24590,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24608,17 +24616,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24638,13 +24646,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24684,10 +24692,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24695,9 +24703,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27282,17 +27290,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27601,21 +27609,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27627,17 +27635,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -27657,13 +27665,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -27703,10 +27711,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -27714,9 +27722,9 @@
       <c r="Q5" s="141"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -30374,17 +30382,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -30693,21 +30701,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -30719,17 +30727,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -30749,13 +30757,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -30795,10 +30803,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -30806,9 +30814,9 @@
       <c r="Q5" s="142"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -33295,17 +33303,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -33605,16 +33613,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="193" t="s">
+      <c r="H1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -33626,15 +33634,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="190"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35283,15 +35291,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="193"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35564,21 +35572,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35590,17 +35598,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35620,13 +35628,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35666,10 +35674,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35677,9 +35685,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -35756,34 +35764,48 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>25</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
-      <c r="M7" s="148"/>
-      <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
+      <c r="M7" s="148">
+        <v>1</v>
+      </c>
+      <c r="N7" s="149">
+        <v>12</v>
+      </c>
+      <c r="O7" s="144">
+        <v>3</v>
+      </c>
       <c r="P7" s="145"/>
       <c r="Q7" s="145"/>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -35818,7 +35840,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+28</f>
+        <v>91</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -35832,7 +35857,9 @@
       <c r="N8" s="156"/>
       <c r="O8" s="157"/>
       <c r="P8" s="158"/>
-      <c r="Q8" s="158"/>
+      <c r="Q8" s="158">
+        <v>2</v>
+      </c>
       <c r="R8" s="159"/>
       <c r="S8" s="154"/>
       <c r="T8" s="160">
@@ -35841,11 +35868,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -35942,7 +35969,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <v>55</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -35954,7 +35983,9 @@
       <c r="L10" s="147"/>
       <c r="M10" s="165"/>
       <c r="N10" s="166"/>
-      <c r="O10" s="162"/>
+      <c r="O10" s="162">
+        <v>2</v>
+      </c>
       <c r="P10" s="163"/>
       <c r="Q10" s="163"/>
       <c r="R10" s="164"/>
@@ -35965,11 +35996,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1368</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -36009,10 +36040,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -36023,15 +36058,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -36064,7 +36099,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1224+51+1440+576</f>
+        <v>3363</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -36074,24 +36112,34 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
+      <c r="M12" s="155">
+        <v>8</v>
+      </c>
+      <c r="N12" s="156">
+        <v>18</v>
+      </c>
+      <c r="O12" s="157">
+        <v>12</v>
+      </c>
       <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="159"/>
+      <c r="Q12" s="158">
+        <v>20</v>
+      </c>
+      <c r="R12" s="159">
+        <v>4</v>
+      </c>
       <c r="S12" s="154"/>
       <c r="T12" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>81694</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3403.9166666666665</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -36133,7 +36181,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -36156,11 +36206,11 @@
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -36377,7 +36427,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -36400,11 +36452,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -36498,7 +36550,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -36521,11 +36575,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -36559,7 +36613,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -36582,11 +36638,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -36620,7 +36676,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -36643,11 +36701,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -36681,7 +36739,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -36704,11 +36764,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -36751,7 +36811,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>48</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -36774,11 +36836,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -36821,7 +36883,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -36844,11 +36908,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -36882,34 +36946,45 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <f>63+19</f>
+        <v>82</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
       <c r="M25" s="165"/>
-      <c r="N25" s="166"/>
-      <c r="O25" s="162"/>
+      <c r="N25" s="166">
+        <v>12</v>
+      </c>
+      <c r="O25" s="162">
+        <v>1</v>
+      </c>
       <c r="P25" s="163"/>
       <c r="Q25" s="163"/>
       <c r="R25" s="164"/>
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2015</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>83.958333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -37009,7 +37084,9 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <v>17</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
@@ -37021,9 +37098,13 @@
       <c r="L28" s="147"/>
       <c r="M28" s="165"/>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>1</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>5</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
@@ -37032,11 +37113,11 @@
       </c>
       <c r="U28" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -37094,7 +37175,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <v>62</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -37108,7 +37191,9 @@
       <c r="N30" s="166"/>
       <c r="O30" s="162"/>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -37117,11 +37202,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -37246,34 +37331,51 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>20+70</f>
+        <v>90</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="M34" s="165">
+        <v>2</v>
+      </c>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2357</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -37360,34 +37462,45 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>2376+1404+25</f>
+        <v>3805</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37" s="156"/>
-      <c r="O37" s="157"/>
+      <c r="O37" s="157">
+        <v>33</v>
+      </c>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>108</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>23684</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3947.3333333333335</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -37399,7 +37512,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <f>1+3</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -37422,11 +37538,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -37466,34 +37582,47 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>630+61</f>
+        <v>691</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>9</v>
+      </c>
       <c r="I40" s="151"/>
       <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="K40" s="153">
+        <v>15</v>
+      </c>
       <c r="L40" s="154"/>
       <c r="M40" s="155"/>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>16692</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>695.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -37504,7 +37633,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1536+28</f>
+        <v>1564</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -37516,9 +37648,13 @@
       <c r="L41" s="179"/>
       <c r="M41" s="180"/>
       <c r="N41" s="181"/>
-      <c r="O41" s="176"/>
+      <c r="O41" s="176">
+        <v>10</v>
+      </c>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>15</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -37527,11 +37663,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>19068</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -37571,34 +37707,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>6048+1728+6372+5400+7128+1836</f>
+        <v>28512</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>1</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>3*6+4</f>
+        <v>22</v>
+      </c>
+      <c r="K43" s="159">
+        <f>87*6</f>
+        <v>522</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>245</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>379</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>432</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>177960</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>29660</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -37714,7 +37869,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -37722,26 +37880,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>9</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14158</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2359.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -37866,7 +38034,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -37889,11 +38059,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -37942,7 +38112,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -37965,11 +38137,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -38095,7 +38267,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>40813</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -38109,56 +38281,56 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>447</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="U58" s="51">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>346304</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>42224.583333333336</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -38166,17 +38338,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -38485,21 +38657,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38511,17 +38683,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38541,13 +38713,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38587,10 +38759,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38598,9 +38770,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38677,34 +38849,46 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>25</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
-      <c r="M7" s="148"/>
+      <c r="M7" s="148">
+        <v>1</v>
+      </c>
       <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
+      <c r="O7" s="144">
+        <v>3</v>
+      </c>
       <c r="P7" s="145"/>
       <c r="Q7" s="145"/>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>29.5</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -38739,7 +38923,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+28</f>
+        <v>91</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -38762,11 +38949,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -38863,7 +39050,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <v>54</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -38877,7 +39066,9 @@
       <c r="N10" s="166"/>
       <c r="O10" s="162"/>
       <c r="P10" s="163"/>
-      <c r="Q10" s="163"/>
+      <c r="Q10" s="163">
+        <v>2</v>
+      </c>
       <c r="R10" s="164"/>
       <c r="S10" s="147"/>
       <c r="T10" s="150">
@@ -38886,11 +39077,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -38930,10 +39121,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -38944,15 +39139,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -38985,7 +39180,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1224+26+1440+576</f>
+        <v>3338</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -38995,24 +39193,34 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
+      <c r="M12" s="155">
+        <v>4</v>
+      </c>
+      <c r="N12" s="156">
+        <v>4</v>
+      </c>
+      <c r="O12" s="157">
+        <v>2</v>
+      </c>
       <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="159"/>
+      <c r="Q12" s="158">
+        <v>24</v>
+      </c>
+      <c r="R12" s="159">
+        <v>13</v>
+      </c>
       <c r="S12" s="154"/>
-      <c r="T12" s="150">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="T12" s="160">
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>80849</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3368.7083333333335</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -39054,7 +39262,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -39071,17 +39281,17 @@
       <c r="Q13" s="163"/>
       <c r="R13" s="164"/>
       <c r="S13" s="147"/>
-      <c r="T13" s="150">
+      <c r="T13" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -39298,7 +39508,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -39321,11 +39533,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -39419,7 +39631,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -39442,11 +39656,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -39480,7 +39694,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -39503,11 +39719,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -39541,7 +39757,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -39564,11 +39782,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -39602,7 +39820,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -39625,11 +39845,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -39672,7 +39892,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>46</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -39686,7 +39908,9 @@
       <c r="N23" s="166"/>
       <c r="O23" s="162"/>
       <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
+      <c r="Q23" s="163">
+        <v>2</v>
+      </c>
       <c r="R23" s="164"/>
       <c r="S23" s="147"/>
       <c r="T23" s="150">
@@ -39695,11 +39919,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -39742,7 +39966,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -39765,11 +39991,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -39803,13 +40029,20 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <f>63+15</f>
+        <v>78</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
@@ -39822,15 +40055,15 @@
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1883</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>78.458333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -39930,7 +40163,10 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <f>12+1</f>
+        <v>13</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
@@ -39942,9 +40178,13 @@
       <c r="L28" s="147"/>
       <c r="M28" s="165"/>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>1</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>3</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
@@ -39953,11 +40193,11 @@
       </c>
       <c r="U28" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -40015,7 +40255,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <v>60</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -40029,7 +40271,9 @@
       <c r="N30" s="166"/>
       <c r="O30" s="162"/>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -40038,11 +40282,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -40167,34 +40411,51 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>72+12</f>
+        <v>84</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="M34" s="165">
+        <v>2</v>
+      </c>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2213</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>92.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40281,34 +40542,43 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>2376+1404+6</f>
+        <v>3786</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37" s="156"/>
       <c r="O37" s="157"/>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>100</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>23324</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3887.3333333333335</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -40320,7 +40590,9 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <v>3</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -40334,7 +40606,9 @@
       <c r="N38" s="166"/>
       <c r="O38" s="162"/>
       <c r="P38" s="163"/>
-      <c r="Q38" s="163"/>
+      <c r="Q38" s="163">
+        <v>1</v>
+      </c>
       <c r="R38" s="164"/>
       <c r="S38" s="147"/>
       <c r="T38" s="167">
@@ -40343,11 +40617,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -40387,34 +40661,49 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>567+53</f>
+        <v>620</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>9</v>
+      </c>
       <c r="I40" s="151"/>
       <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="K40" s="153">
+        <v>15</v>
+      </c>
       <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="M40" s="155">
+        <v>1</v>
+      </c>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>15012</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -40425,7 +40714,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1536+17</f>
+        <v>1553</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -40435,11 +40727,17 @@
       <c r="J41" s="177"/>
       <c r="K41" s="178"/>
       <c r="L41" s="179"/>
-      <c r="M41" s="180"/>
+      <c r="M41" s="180">
+        <v>1</v>
+      </c>
       <c r="N41" s="181"/>
-      <c r="O41" s="176"/>
+      <c r="O41" s="176">
+        <v>9</v>
+      </c>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>15</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -40448,11 +40746,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>18936</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40492,34 +40790,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>6048+1080+8208+5400+7128+108+45</f>
+        <v>28017</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>4</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>6*4</f>
+        <v>24</v>
+      </c>
+      <c r="K43" s="159">
+        <f>87*6</f>
+        <v>522</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>4</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>57</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>487</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>171947</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>28657.833333333332</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -40635,7 +40952,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -40643,26 +40963,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>8</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14152</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2358.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -40787,7 +41117,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -40810,11 +41142,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -40863,7 +41195,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -40886,11 +41220,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -41016,7 +41350,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>40172</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -41030,56 +41364,56 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="U58" s="51">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>336716</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>41022.208333333328</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -41087,17 +41421,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="190" t="s">
+      <c r="C60" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="191"/>
-      <c r="E60" s="191"/>
-      <c r="F60" s="191"/>
-      <c r="G60" s="191"/>
-      <c r="H60" s="191"/>
-      <c r="I60" s="191"/>
-      <c r="J60" s="191"/>
-      <c r="K60" s="192"/>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -41356,6 +41690,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A2F5F4-C5DF-4049-87CE-B29D5D492895}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="194" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="189" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="200" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="202" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="195" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="197" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="198"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="183"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="183"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="183"/>
+      <c r="Q6" s="183"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="150">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="150">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="150">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="155"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="158"/>
+      <c r="Q8" s="158"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="160">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="161">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="161">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="163"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="168">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="168">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="163"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="166"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="163"/>
+      <c r="Q10" s="163"/>
+      <c r="R10" s="164"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="162"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="163"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="165"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="163"/>
+      <c r="Q11" s="163"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="158"/>
+      <c r="R12" s="159"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="161">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="161">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="162"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="163"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="164"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="168">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="168">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="162"/>
+      <c r="H14" s="162"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="163"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="165"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="163"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="167">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="167">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="162"/>
+      <c r="D15" s="162"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="163"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="164"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="164"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="165"/>
+      <c r="N17" s="166"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="163"/>
+      <c r="R17" s="164"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="164"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="162"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="166"/>
+      <c r="O19" s="162"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="164"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="162"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="164"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="162"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="163"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="164"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="166"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="162"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="164"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="166"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="163"/>
+      <c r="Q23" s="163"/>
+      <c r="R23" s="164"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="162"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="165"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="164"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="166"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="164"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="162"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="163"/>
+      <c r="Q26" s="163"/>
+      <c r="R26" s="164"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="162"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="166"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="163"/>
+      <c r="Q27" s="163"/>
+      <c r="R27" s="164"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="150"/>
+      <c r="U27" s="167"/>
+      <c r="V27" s="167"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="163"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="166"/>
+      <c r="O28" s="162"/>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="163"/>
+      <c r="R28" s="164"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="162"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="166"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="163"/>
+      <c r="Q29" s="163"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="162"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="166"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="163"/>
+      <c r="Q30" s="163"/>
+      <c r="R30" s="164"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="162"/>
+      <c r="D31" s="162"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="162"/>
+      <c r="H31" s="162"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="164"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="162"/>
+      <c r="D32" s="162"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="164"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="162"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="163"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="166"/>
+      <c r="O33" s="162"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="164"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="164"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="162"/>
+      <c r="D35" s="162"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="166"/>
+      <c r="O35" s="162"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="162"/>
+      <c r="D36" s="162"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="163"/>
+      <c r="K36" s="164"/>
+      <c r="L36" s="147"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="166"/>
+      <c r="O36" s="162"/>
+      <c r="P36" s="163"/>
+      <c r="Q36" s="163"/>
+      <c r="R36" s="164"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="151"/>
+      <c r="H37" s="151"/>
+      <c r="I37" s="151"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="157"/>
+      <c r="P37" s="158"/>
+      <c r="Q37" s="158"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="154"/>
+      <c r="T37" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="169">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="169">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="162"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="162"/>
+      <c r="P38" s="163"/>
+      <c r="Q38" s="163"/>
+      <c r="R38" s="164"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="167">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="167">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="170"/>
+      <c r="D39" s="170"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="170"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="170"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="171"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="175"/>
+      <c r="U39" s="175"/>
+      <c r="V39" s="175"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="151"/>
+      <c r="I40" s="151"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="157"/>
+      <c r="P40" s="158"/>
+      <c r="Q40" s="158"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="169">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="169">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="180"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="176"/>
+      <c r="P41" s="177"/>
+      <c r="Q41" s="177"/>
+      <c r="R41" s="178"/>
+      <c r="S41" s="179"/>
+      <c r="T41" s="182">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="182">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="182">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="162"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="163"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="162"/>
+      <c r="P42" s="163"/>
+      <c r="Q42" s="163"/>
+      <c r="R42" s="164"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="157"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="158"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="156"/>
+      <c r="O43" s="157"/>
+      <c r="P43" s="158"/>
+      <c r="Q43" s="158"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="154"/>
+      <c r="T43" s="169">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="169">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="169">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="162"/>
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="147"/>
+      <c r="M44" s="165"/>
+      <c r="N44" s="166"/>
+      <c r="O44" s="162"/>
+      <c r="P44" s="163"/>
+      <c r="Q44" s="163"/>
+      <c r="R44" s="164"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="167"/>
+      <c r="U44" s="167"/>
+      <c r="V44" s="167"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="162"/>
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="165"/>
+      <c r="N45" s="166"/>
+      <c r="O45" s="162"/>
+      <c r="P45" s="163"/>
+      <c r="Q45" s="163"/>
+      <c r="R45" s="164"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="167">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="167">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="167">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="162"/>
+      <c r="D46" s="162"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="162"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="147"/>
+      <c r="M46" s="165"/>
+      <c r="N46" s="166"/>
+      <c r="O46" s="162"/>
+      <c r="P46" s="163"/>
+      <c r="Q46" s="163"/>
+      <c r="R46" s="164"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="167">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="167">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="158"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
+      <c r="N47" s="156"/>
+      <c r="O47" s="157"/>
+      <c r="P47" s="158"/>
+      <c r="Q47" s="158"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="169">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="169">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="162"/>
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="165"/>
+      <c r="N48" s="166"/>
+      <c r="O48" s="162"/>
+      <c r="P48" s="163"/>
+      <c r="Q48" s="163"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="147"/>
+      <c r="T48" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="162"/>
+      <c r="D49" s="162"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="147"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="163"/>
+      <c r="Q49" s="163"/>
+      <c r="R49" s="164"/>
+      <c r="S49" s="147"/>
+      <c r="T49" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="162"/>
+      <c r="D50" s="162"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="162"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="165"/>
+      <c r="N50" s="166"/>
+      <c r="O50" s="162"/>
+      <c r="P50" s="163"/>
+      <c r="Q50" s="163"/>
+      <c r="R50" s="164"/>
+      <c r="S50" s="147"/>
+      <c r="T50" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="159"/>
+      <c r="L51" s="154"/>
+      <c r="M51" s="155"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="157"/>
+      <c r="P51" s="158"/>
+      <c r="Q51" s="158"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="154"/>
+      <c r="T51" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="169">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="169">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="162"/>
+      <c r="D52" s="162"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="163"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="166"/>
+      <c r="O52" s="162"/>
+      <c r="P52" s="163"/>
+      <c r="Q52" s="163"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="167">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="162"/>
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="163"/>
+      <c r="K53" s="164"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="165"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="162"/>
+      <c r="P53" s="163"/>
+      <c r="Q53" s="163"/>
+      <c r="R53" s="164"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="162"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="164"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="165"/>
+      <c r="N54" s="166"/>
+      <c r="O54" s="162"/>
+      <c r="P54" s="163"/>
+      <c r="Q54" s="163"/>
+      <c r="R54" s="164"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="162"/>
+      <c r="D55" s="162"/>
+      <c r="E55" s="162"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="164"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="165"/>
+      <c r="N55" s="166"/>
+      <c r="O55" s="162"/>
+      <c r="P55" s="163"/>
+      <c r="Q55" s="163"/>
+      <c r="R55" s="164"/>
+      <c r="S55" s="147"/>
+      <c r="T55" s="167"/>
+      <c r="U55" s="167"/>
+      <c r="V55" s="167"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="164"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="165"/>
+      <c r="N56" s="166"/>
+      <c r="O56" s="162"/>
+      <c r="P56" s="163"/>
+      <c r="Q56" s="163"/>
+      <c r="R56" s="164"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="167"/>
+      <c r="U56" s="167"/>
+      <c r="V56" s="167"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="162"/>
+      <c r="E57" s="162"/>
+      <c r="F57" s="162"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="162"/>
+      <c r="I57" s="162"/>
+      <c r="J57" s="163"/>
+      <c r="K57" s="164"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="165"/>
+      <c r="N57" s="166"/>
+      <c r="O57" s="162"/>
+      <c r="P57" s="163"/>
+      <c r="Q57" s="163"/>
+      <c r="R57" s="164"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="167"/>
+      <c r="U57" s="167"/>
+      <c r="V57" s="167"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="147"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="191" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="192"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="193"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -41406,21 +44661,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41432,17 +44687,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41462,13 +44717,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41508,10 +44763,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41519,9 +44774,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44126,17 +47381,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -44445,21 +47700,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44471,17 +47726,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44501,13 +47756,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44547,10 +47802,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44558,9 +47813,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47158,17 +50413,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -47477,21 +50732,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47503,17 +50758,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -47533,13 +50788,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -47579,10 +50834,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -47590,9 +50845,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -50199,17 +53454,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -50518,21 +53773,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -50544,17 +53799,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -50574,13 +53829,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -50620,10 +53875,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -50631,9 +53886,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -53233,17 +56488,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -53552,21 +56807,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -53578,17 +56833,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -53608,13 +56863,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -53654,10 +56909,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -53665,9 +56920,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -56249,17 +59504,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -56568,21 +59823,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -56594,17 +59849,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -56624,13 +59879,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -56670,10 +59925,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -56681,9 +59936,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -59263,17 +62518,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -59582,21 +62837,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="193" t="s">
+      <c r="I1" s="194" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="194"/>
+      <c r="N1" s="194"/>
+      <c r="O1" s="194"/>
+      <c r="P1" s="194"/>
+      <c r="Q1" s="194"/>
+      <c r="R1" s="194"/>
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="U1" s="194"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -59608,17 +62863,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="189" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="190"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -59638,13 +62893,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="199" t="s">
+      <c r="T4" s="200" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="201" t="s">
+      <c r="U4" s="202" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="194" t="s">
+      <c r="V4" s="195" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -59684,10 +62939,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="196" t="s">
+      <c r="J5" s="197" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="197"/>
+      <c r="K5" s="198"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -59695,9 +62950,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="202"/>
-      <c r="V5" s="195"/>
+      <c r="T5" s="201"/>
+      <c r="U5" s="203"/>
+      <c r="V5" s="196"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -62284,17 +65539,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="190" t="s">
+      <c r="C59" s="191" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="191"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="191"/>
-      <c r="I59" s="191"/>
-      <c r="J59" s="191"/>
-      <c r="K59" s="192"/>
+      <c r="D59" s="192"/>
+      <c r="E59" s="192"/>
+      <c r="F59" s="192"/>
+      <c r="G59" s="192"/>
+      <c r="H59" s="192"/>
+      <c r="I59" s="192"/>
+      <c r="J59" s="192"/>
+      <c r="K59" s="193"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D8DC9-D792-4BA6-ABA7-FB9B03E1BBB2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4C4C05-3157-4A1B-8164-0311C30B129F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
@@ -44604,13 +44604,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4C4C05-3157-4A1B-8164-0311C30B129F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B16FF9-2624-4318-88C9-E9A20C5AAF84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B16FF9-2624-4318-88C9-E9A20C5AAF84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197EF725-9692-4970-AEEC-9D3A7F68DCD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="12" activeTab="20" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="02-21-2026" sheetId="29" r:id="rId20"/>
     <sheet name="02-23-2026" sheetId="30" r:id="rId21"/>
     <sheet name="02-25-2026" sheetId="31" r:id="rId22"/>
+    <sheet name="02-26-2026" sheetId="32" r:id="rId23"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -56,6 +57,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="19">'02-21-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'02-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'02-25-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'02-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="103">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -384,6 +386,9 @@
   <si>
     <t>DATE: 02/25/2026</t>
   </si>
+  <si>
+    <t>DATE: 02/26/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -532,7 +537,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,6 +547,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1516,7 +1527,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2080,6 +2091,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2139,6 +2153,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3395,34 +3412,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="187" t="s">
+      <c r="A21" s="188" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="184" t="s">
+      <c r="B21" s="185" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="185"/>
-      <c r="D21" s="186"/>
-      <c r="E21" s="184" t="s">
+      <c r="C21" s="186"/>
+      <c r="D21" s="187"/>
+      <c r="E21" s="185" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="185"/>
-      <c r="G21" s="186"/>
-      <c r="H21" s="184" t="s">
+      <c r="F21" s="186"/>
+      <c r="G21" s="187"/>
+      <c r="H21" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="185"/>
-      <c r="J21" s="186"/>
-      <c r="K21" s="184" t="s">
+      <c r="I21" s="186"/>
+      <c r="J21" s="187"/>
+      <c r="K21" s="185" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="185"/>
-      <c r="M21" s="186"/>
-      <c r="N21" s="184" t="s">
+      <c r="L21" s="186"/>
+      <c r="M21" s="187"/>
+      <c r="N21" s="185" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="185"/>
-      <c r="P21" s="186"/>
+      <c r="O21" s="186"/>
+      <c r="P21" s="187"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3445,7 +3462,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="188"/>
+      <c r="A22" s="189"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3669,21 +3686,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3695,17 +3712,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3725,13 +3742,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3771,10 +3788,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3782,9 +3799,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6367,17 +6384,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6686,21 +6703,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6712,17 +6729,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6742,13 +6759,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6788,10 +6805,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6799,9 +6816,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9380,17 +9397,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9699,21 +9716,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9725,17 +9742,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9755,13 +9772,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9801,10 +9818,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9812,9 +9829,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12384,17 +12401,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12703,21 +12720,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12729,17 +12746,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12759,13 +12776,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12805,10 +12822,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12816,9 +12833,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15402,17 +15419,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15721,21 +15738,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15747,17 +15764,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15777,13 +15794,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15823,10 +15840,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15834,9 +15851,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18410,17 +18427,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18729,21 +18746,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18755,17 +18772,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18785,13 +18802,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18831,10 +18848,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18842,9 +18859,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21251,17 +21268,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21570,21 +21587,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21596,17 +21613,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21626,13 +21643,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21672,10 +21689,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21683,9 +21700,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24271,17 +24288,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24590,21 +24607,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24616,17 +24633,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24646,13 +24663,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24692,10 +24709,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24703,9 +24720,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27290,17 +27307,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27609,21 +27626,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27635,17 +27652,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -27665,13 +27682,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -27711,10 +27728,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -27722,9 +27739,9 @@
       <c r="Q5" s="141"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -30382,17 +30399,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -30701,21 +30718,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -30727,17 +30744,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -30757,13 +30774,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -30803,10 +30820,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -30814,9 +30831,9 @@
       <c r="Q5" s="142"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -33303,17 +33320,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -33613,16 +33630,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="194" t="s">
+      <c r="H1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -33634,15 +33651,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="191"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35291,15 +35308,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="194"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35572,21 +35589,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35598,17 +35615,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35628,13 +35645,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35674,10 +35691,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35685,9 +35702,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38338,17 +38355,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -38657,21 +38674,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38683,17 +38700,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38713,13 +38730,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38759,10 +38776,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38770,9 +38787,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41421,17 +41438,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -41740,21 +41757,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41766,17 +41783,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41796,13 +41813,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41842,10 +41859,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41853,9 +41870,9 @@
       <c r="Q5" s="183"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41932,34 +41949,44 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>25</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
       <c r="M7" s="148"/>
       <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
+      <c r="O7" s="144">
+        <v>3</v>
+      </c>
       <c r="P7" s="145"/>
       <c r="Q7" s="145"/>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>28.5</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -41994,7 +42021,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+26</f>
+        <v>89</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -42004,7 +42034,9 @@
       <c r="J8" s="152"/>
       <c r="K8" s="153"/>
       <c r="L8" s="154"/>
-      <c r="M8" s="155"/>
+      <c r="M8" s="155">
+        <v>2</v>
+      </c>
       <c r="N8" s="156"/>
       <c r="O8" s="157"/>
       <c r="P8" s="158"/>
@@ -42017,11 +42049,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2184</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -42056,7 +42088,9 @@
       <c r="B9" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="162"/>
+      <c r="C9" s="162">
+        <v>10</v>
+      </c>
       <c r="D9" s="162"/>
       <c r="E9" s="162"/>
       <c r="F9" s="162"/>
@@ -42074,16 +42108,16 @@
       <c r="R9" s="164"/>
       <c r="S9" s="147"/>
       <c r="T9" s="167">
-        <f t="shared" si="0"/>
+        <f>G9+H9+I9+J9+K9+N9+P9+R9</f>
         <v>0</v>
       </c>
       <c r="U9" s="168">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V9" s="168">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W9" s="123"/>
       <c r="AF9" s="60"/>
@@ -42118,7 +42152,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <v>54</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -42130,9 +42166,13 @@
       <c r="L10" s="147"/>
       <c r="M10" s="165"/>
       <c r="N10" s="166"/>
-      <c r="O10" s="162"/>
+      <c r="O10" s="162">
+        <v>1</v>
+      </c>
       <c r="P10" s="163"/>
-      <c r="Q10" s="163"/>
+      <c r="Q10" s="163">
+        <v>1</v>
+      </c>
       <c r="R10" s="164"/>
       <c r="S10" s="147"/>
       <c r="T10" s="150">
@@ -42141,11 +42181,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1344</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -42185,10 +42225,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -42199,15 +42243,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -42240,7 +42284,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1152+50+1440+576</f>
+        <v>3290</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -42250,24 +42297,34 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
+      <c r="M12" s="155">
+        <v>13</v>
+      </c>
+      <c r="N12" s="156">
+        <v>22</v>
+      </c>
+      <c r="O12" s="157">
+        <v>11</v>
+      </c>
+      <c r="P12" s="158">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="158">
+        <v>14</v>
+      </c>
       <c r="R12" s="159"/>
       <c r="S12" s="154"/>
       <c r="T12" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>79914</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3329.75</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -42309,7 +42366,10 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <f>5</f>
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -42332,11 +42392,11 @@
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -42553,7 +42613,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -42576,11 +42638,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -42674,7 +42736,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -42697,11 +42761,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -42735,7 +42799,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -42758,11 +42824,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -42796,7 +42862,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -42819,11 +42887,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -42857,7 +42925,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -42880,11 +42950,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -42927,7 +42997,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>42</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -42937,11 +43009,17 @@
       <c r="J23" s="163"/>
       <c r="K23" s="164"/>
       <c r="L23" s="147"/>
-      <c r="M23" s="165"/>
+      <c r="M23" s="165">
+        <v>2</v>
+      </c>
       <c r="N23" s="166"/>
-      <c r="O23" s="162"/>
+      <c r="O23" s="162">
+        <v>2</v>
+      </c>
       <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
+      <c r="Q23" s="163">
+        <v>2</v>
+      </c>
       <c r="R23" s="164"/>
       <c r="S23" s="147"/>
       <c r="T23" s="150">
@@ -42950,11 +43028,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -42997,7 +43075,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -43020,11 +43100,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -43058,17 +43138,26 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <f>63+13</f>
+        <v>76</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
-      <c r="M25" s="165"/>
+      <c r="M25" s="165">
+        <v>2</v>
+      </c>
       <c r="N25" s="166"/>
       <c r="O25" s="162"/>
       <c r="P25" s="163"/>
@@ -43077,15 +43166,15 @@
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1883</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>78.458333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -43185,7 +43274,9 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <v>7</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
@@ -43197,9 +43288,13 @@
       <c r="L28" s="147"/>
       <c r="M28" s="165"/>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>2</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>3</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
@@ -43208,11 +43303,11 @@
       </c>
       <c r="U28" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -43270,7 +43365,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <v>58</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -43282,9 +43379,13 @@
       <c r="L30" s="147"/>
       <c r="M30" s="165"/>
       <c r="N30" s="166"/>
-      <c r="O30" s="162"/>
+      <c r="O30" s="162">
+        <v>2</v>
+      </c>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -43293,11 +43394,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -43308,7 +43409,9 @@
       <c r="B31" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="162"/>
+      <c r="C31" s="162">
+        <v>9</v>
+      </c>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
       <c r="F31" s="162"/>
@@ -43322,7 +43425,9 @@
       <c r="N31" s="166"/>
       <c r="O31" s="162"/>
       <c r="P31" s="163"/>
-      <c r="Q31" s="163"/>
+      <c r="Q31" s="163">
+        <v>1</v>
+      </c>
       <c r="R31" s="164"/>
       <c r="S31" s="147"/>
       <c r="T31" s="150">
@@ -43331,11 +43436,11 @@
       </c>
       <c r="U31" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="V31" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -43422,34 +43527,49 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>72+12</f>
+        <v>84</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
       <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2165</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>90.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -43536,34 +43656,45 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>2376+1080+78</f>
+        <v>3534</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
       <c r="M37" s="155"/>
       <c r="N37" s="156"/>
-      <c r="O37" s="157"/>
+      <c r="O37" s="157">
+        <v>30</v>
+      </c>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>97</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>21974</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3662.3333333333335</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -43575,7 +43706,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <f>1+3</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -43598,11 +43732,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -43642,34 +43776,49 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>567+53</f>
+        <v>620</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>9</v>
+      </c>
       <c r="I40" s="151"/>
       <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="K40" s="153">
+        <v>15</v>
+      </c>
       <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="M40" s="155">
+        <v>1</v>
+      </c>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>15012</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -43680,7 +43829,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1536+7</f>
+        <v>1543</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -43690,11 +43842,17 @@
       <c r="J41" s="177"/>
       <c r="K41" s="178"/>
       <c r="L41" s="179"/>
-      <c r="M41" s="180"/>
+      <c r="M41" s="180">
+        <v>4</v>
+      </c>
       <c r="N41" s="181"/>
-      <c r="O41" s="176"/>
+      <c r="O41" s="176">
+        <v>8</v>
+      </c>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>7</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -43703,11 +43861,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>18744</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -43747,34 +43905,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>5400+1836+8208+5400+7128+1836</f>
+        <v>29808</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>5</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>5*6+5</f>
+        <v>35</v>
+      </c>
+      <c r="K43" s="159">
+        <f>87*6</f>
+        <v>522</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>325</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>362</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>515</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>186629</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31104.833333333332</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -43890,7 +44067,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -43898,26 +44078,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>8</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14152</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2358.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -44042,7 +44232,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -44065,11 +44257,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -44118,7 +44310,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -44141,11 +44335,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -44271,7 +44465,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>41657</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -44285,39 +44479,39 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>656</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
@@ -44326,15 +44520,15 @@
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="51">
+        <v>741</v>
+      </c>
+      <c r="U58" s="205">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>349209</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>43201.249999999993</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -44342,17 +44536,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="191" t="s">
+      <c r="C60" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="192"/>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="193"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -44611,6 +44805,2927 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AAB2A8-83DC-46AC-8C64-B26C110E1981}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="195" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="190" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="201" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="203" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="196" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="198" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="199"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="184"/>
+      <c r="Q5" s="184"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="184"/>
+      <c r="Q6" s="184"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="150">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="150">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="150">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="155"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="158"/>
+      <c r="Q8" s="158"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="160">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="161">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="161">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="163"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="168">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="168">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="163"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="166"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="163"/>
+      <c r="Q10" s="163"/>
+      <c r="R10" s="164"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="162"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="163"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="165"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="163"/>
+      <c r="Q11" s="163"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="158"/>
+      <c r="R12" s="159"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="161">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="161">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="162"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="163"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="164"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="168">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="168">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="162"/>
+      <c r="H14" s="162"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="163"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="165"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="163"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="167">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="167">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="162"/>
+      <c r="D15" s="162"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="163"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="164"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="164"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="165"/>
+      <c r="N17" s="166"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="163"/>
+      <c r="R17" s="164"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="164"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="162"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="166"/>
+      <c r="O19" s="162"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="164"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="162"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="164"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="162"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="163"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="164"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="166"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="162"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="164"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="166"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="163"/>
+      <c r="Q23" s="163"/>
+      <c r="R23" s="164"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="162"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="165"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="164"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="166"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="164"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="162"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="163"/>
+      <c r="Q26" s="163"/>
+      <c r="R26" s="164"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="162"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="166"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="163"/>
+      <c r="Q27" s="163"/>
+      <c r="R27" s="164"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="150"/>
+      <c r="U27" s="167"/>
+      <c r="V27" s="167"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="163"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="166"/>
+      <c r="O28" s="162"/>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="163"/>
+      <c r="R28" s="164"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="162"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="166"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="163"/>
+      <c r="Q29" s="163"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="162"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="166"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="163"/>
+      <c r="Q30" s="163"/>
+      <c r="R30" s="164"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="162"/>
+      <c r="D31" s="162"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="162"/>
+      <c r="H31" s="162"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="164"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="162"/>
+      <c r="D32" s="162"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="164"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="162"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="163"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="166"/>
+      <c r="O33" s="162"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="164"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="164"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="162"/>
+      <c r="D35" s="162"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="166"/>
+      <c r="O35" s="162"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="162"/>
+      <c r="D36" s="162"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="163"/>
+      <c r="K36" s="164"/>
+      <c r="L36" s="147"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="166"/>
+      <c r="O36" s="162"/>
+      <c r="P36" s="163"/>
+      <c r="Q36" s="163"/>
+      <c r="R36" s="164"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="151"/>
+      <c r="H37" s="151"/>
+      <c r="I37" s="151"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="157"/>
+      <c r="P37" s="158"/>
+      <c r="Q37" s="158"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="154"/>
+      <c r="T37" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="169">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="169">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="162"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="162"/>
+      <c r="P38" s="163"/>
+      <c r="Q38" s="163"/>
+      <c r="R38" s="164"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="167">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="167">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="170"/>
+      <c r="D39" s="170"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="170"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="170"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="171"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="175"/>
+      <c r="U39" s="175"/>
+      <c r="V39" s="175"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="151"/>
+      <c r="I40" s="151"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="157"/>
+      <c r="P40" s="158"/>
+      <c r="Q40" s="158"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="169">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="169">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="180"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="176"/>
+      <c r="P41" s="177"/>
+      <c r="Q41" s="177"/>
+      <c r="R41" s="178"/>
+      <c r="S41" s="179"/>
+      <c r="T41" s="182">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="182">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="182">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="162"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="163"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="162"/>
+      <c r="P42" s="163"/>
+      <c r="Q42" s="163"/>
+      <c r="R42" s="164"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="157"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="158"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="156"/>
+      <c r="O43" s="157"/>
+      <c r="P43" s="158"/>
+      <c r="Q43" s="158"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="154"/>
+      <c r="T43" s="169">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="169">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="169">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="162"/>
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="147"/>
+      <c r="M44" s="165"/>
+      <c r="N44" s="166"/>
+      <c r="O44" s="162"/>
+      <c r="P44" s="163"/>
+      <c r="Q44" s="163"/>
+      <c r="R44" s="164"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="167"/>
+      <c r="U44" s="167"/>
+      <c r="V44" s="167"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="162"/>
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="165"/>
+      <c r="N45" s="166"/>
+      <c r="O45" s="162"/>
+      <c r="P45" s="163"/>
+      <c r="Q45" s="163"/>
+      <c r="R45" s="164"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="167">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="167">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="167">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="162"/>
+      <c r="D46" s="162"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="162"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="147"/>
+      <c r="M46" s="165"/>
+      <c r="N46" s="166"/>
+      <c r="O46" s="162"/>
+      <c r="P46" s="163"/>
+      <c r="Q46" s="163"/>
+      <c r="R46" s="164"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="167">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="167">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="158"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
+      <c r="N47" s="156"/>
+      <c r="O47" s="157"/>
+      <c r="P47" s="158"/>
+      <c r="Q47" s="158"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="169">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="169">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="162"/>
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="165"/>
+      <c r="N48" s="166"/>
+      <c r="O48" s="162"/>
+      <c r="P48" s="163"/>
+      <c r="Q48" s="163"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="147"/>
+      <c r="T48" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="162"/>
+      <c r="D49" s="162"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="147"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="163"/>
+      <c r="Q49" s="163"/>
+      <c r="R49" s="164"/>
+      <c r="S49" s="147"/>
+      <c r="T49" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="162"/>
+      <c r="D50" s="162"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="162"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="165"/>
+      <c r="N50" s="166"/>
+      <c r="O50" s="162"/>
+      <c r="P50" s="163"/>
+      <c r="Q50" s="163"/>
+      <c r="R50" s="164"/>
+      <c r="S50" s="147"/>
+      <c r="T50" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="159"/>
+      <c r="L51" s="154"/>
+      <c r="M51" s="155"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="157"/>
+      <c r="P51" s="158"/>
+      <c r="Q51" s="158"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="154"/>
+      <c r="T51" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="169">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="169">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="162"/>
+      <c r="D52" s="162"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="163"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="166"/>
+      <c r="O52" s="162"/>
+      <c r="P52" s="163"/>
+      <c r="Q52" s="163"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="167">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="162"/>
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="163"/>
+      <c r="K53" s="164"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="165"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="162"/>
+      <c r="P53" s="163"/>
+      <c r="Q53" s="163"/>
+      <c r="R53" s="164"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="162"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="164"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="165"/>
+      <c r="N54" s="166"/>
+      <c r="O54" s="162"/>
+      <c r="P54" s="163"/>
+      <c r="Q54" s="163"/>
+      <c r="R54" s="164"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="162"/>
+      <c r="D55" s="162"/>
+      <c r="E55" s="162"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="164"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="165"/>
+      <c r="N55" s="166"/>
+      <c r="O55" s="162"/>
+      <c r="P55" s="163"/>
+      <c r="Q55" s="163"/>
+      <c r="R55" s="164"/>
+      <c r="S55" s="147"/>
+      <c r="T55" s="167"/>
+      <c r="U55" s="167"/>
+      <c r="V55" s="167"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="164"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="165"/>
+      <c r="N56" s="166"/>
+      <c r="O56" s="162"/>
+      <c r="P56" s="163"/>
+      <c r="Q56" s="163"/>
+      <c r="R56" s="164"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="167"/>
+      <c r="U56" s="167"/>
+      <c r="V56" s="167"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="162"/>
+      <c r="E57" s="162"/>
+      <c r="F57" s="162"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="162"/>
+      <c r="I57" s="162"/>
+      <c r="J57" s="163"/>
+      <c r="K57" s="164"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="165"/>
+      <c r="N57" s="166"/>
+      <c r="O57" s="162"/>
+      <c r="P57" s="163"/>
+      <c r="Q57" s="163"/>
+      <c r="R57" s="164"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="167"/>
+      <c r="U57" s="167"/>
+      <c r="V57" s="167"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="147"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="193"/>
+      <c r="E60" s="193"/>
+      <c r="F60" s="193"/>
+      <c r="G60" s="193"/>
+      <c r="H60" s="193"/>
+      <c r="I60" s="193"/>
+      <c r="J60" s="193"/>
+      <c r="K60" s="194"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -44661,21 +47776,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44687,17 +47802,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44717,13 +47832,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44763,10 +47878,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44774,9 +47889,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47381,17 +50496,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -47700,21 +50815,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47726,17 +50841,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -47756,13 +50871,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -47802,10 +50917,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -47813,9 +50928,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -50413,17 +53528,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -50732,21 +53847,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -50758,17 +53873,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -50788,13 +53903,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -50834,10 +53949,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -50845,9 +53960,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -53454,17 +56569,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -53773,21 +56888,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -53799,17 +56914,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -53829,13 +56944,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -53875,10 +56990,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -53886,9 +57001,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -56488,17 +59603,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -56807,21 +59922,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -56833,17 +59948,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -56863,13 +59978,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -56909,10 +60024,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -56920,9 +60035,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -59504,17 +62619,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -59823,21 +62938,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -59849,17 +62964,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -59879,13 +62994,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -59925,10 +63040,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -59936,9 +63051,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -62518,17 +65633,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -62837,21 +65952,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
+      <c r="Q1" s="195"/>
+      <c r="R1" s="195"/>
+      <c r="S1" s="195"/>
+      <c r="T1" s="195"/>
+      <c r="U1" s="195"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -62863,17 +65978,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="189" t="s">
+      <c r="C4" s="190" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
+      <c r="I4" s="190"/>
+      <c r="J4" s="200"/>
+      <c r="K4" s="191"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -62893,13 +66008,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="200" t="s">
+      <c r="T4" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="202" t="s">
+      <c r="U4" s="203" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="195" t="s">
+      <c r="V4" s="196" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -62939,10 +66054,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="197" t="s">
+      <c r="J5" s="198" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="198"/>
+      <c r="K5" s="199"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -62950,9 +66065,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="201"/>
-      <c r="U5" s="203"/>
-      <c r="V5" s="196"/>
+      <c r="T5" s="202"/>
+      <c r="U5" s="204"/>
+      <c r="V5" s="197"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -65539,17 +68654,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="191" t="s">
+      <c r="C59" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="192"/>
-      <c r="E59" s="192"/>
-      <c r="F59" s="192"/>
-      <c r="G59" s="192"/>
-      <c r="H59" s="192"/>
-      <c r="I59" s="192"/>
-      <c r="J59" s="192"/>
-      <c r="K59" s="193"/>
+      <c r="D59" s="193"/>
+      <c r="E59" s="193"/>
+      <c r="F59" s="193"/>
+      <c r="G59" s="193"/>
+      <c r="H59" s="193"/>
+      <c r="I59" s="193"/>
+      <c r="J59" s="193"/>
+      <c r="K59" s="194"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197EF725-9692-4970-AEEC-9D3A7F68DCD6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B5305-3C75-4688-876E-B71A34A14B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="13" activeTab="21" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="14" activeTab="22" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="02-23-2026" sheetId="30" r:id="rId21"/>
     <sheet name="02-25-2026" sheetId="31" r:id="rId22"/>
     <sheet name="02-26-2026" sheetId="32" r:id="rId23"/>
+    <sheet name="02-27-2026" sheetId="33" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -58,6 +59,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="20">'02-23-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="21">'02-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'02-26-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'02-27-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -78,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="104">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -388,6 +390,9 @@
   </si>
   <si>
     <t>DATE: 02/26/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/27/2026</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1532,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2094,6 +2099,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2153,9 +2164,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3412,34 +3420,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="188" t="s">
+      <c r="A21" s="190" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="185" t="s">
+      <c r="B21" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="186"/>
-      <c r="D21" s="187"/>
-      <c r="E21" s="185" t="s">
+      <c r="C21" s="188"/>
+      <c r="D21" s="189"/>
+      <c r="E21" s="187" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="186"/>
-      <c r="G21" s="187"/>
-      <c r="H21" s="185" t="s">
+      <c r="F21" s="188"/>
+      <c r="G21" s="189"/>
+      <c r="H21" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="186"/>
-      <c r="J21" s="187"/>
-      <c r="K21" s="185" t="s">
+      <c r="I21" s="188"/>
+      <c r="J21" s="189"/>
+      <c r="K21" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="186"/>
-      <c r="M21" s="187"/>
-      <c r="N21" s="185" t="s">
+      <c r="L21" s="188"/>
+      <c r="M21" s="189"/>
+      <c r="N21" s="187" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="186"/>
-      <c r="P21" s="187"/>
+      <c r="O21" s="188"/>
+      <c r="P21" s="189"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3462,7 +3470,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="189"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3686,21 +3694,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3712,17 +3720,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3742,13 +3750,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3788,10 +3796,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3799,9 +3807,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6384,17 +6392,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6703,21 +6711,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6729,17 +6737,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6759,13 +6767,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6805,10 +6813,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6816,9 +6824,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9397,17 +9405,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9716,21 +9724,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9742,17 +9750,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9772,13 +9780,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9818,10 +9826,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9829,9 +9837,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12401,17 +12409,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12720,21 +12728,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12746,17 +12754,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12776,13 +12784,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12822,10 +12830,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12833,9 +12841,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15419,17 +15427,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15738,21 +15746,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15764,17 +15772,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15794,13 +15802,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15840,10 +15848,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15851,9 +15859,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18427,17 +18435,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18746,21 +18754,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18772,17 +18780,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18802,13 +18810,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18848,10 +18856,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18859,9 +18867,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21268,17 +21276,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21587,21 +21595,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21613,17 +21621,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21643,13 +21651,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21689,10 +21697,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21700,9 +21708,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24288,17 +24296,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24607,21 +24615,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24633,17 +24641,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24663,13 +24671,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24709,10 +24717,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24720,9 +24728,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27307,17 +27315,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27626,21 +27634,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27652,17 +27660,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -27682,13 +27690,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -27728,10 +27736,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -27739,9 +27747,9 @@
       <c r="Q5" s="141"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -30399,17 +30407,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -30718,21 +30726,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -30744,17 +30752,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -30774,13 +30782,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -30820,10 +30828,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -30831,9 +30839,9 @@
       <c r="Q5" s="142"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -33320,17 +33328,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -33630,16 +33638,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="195" t="s">
+      <c r="H1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -33651,15 +33659,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="193"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35308,15 +35316,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="196"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35589,21 +35597,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35615,17 +35623,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35645,13 +35653,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35691,10 +35699,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35702,9 +35710,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38355,17 +38363,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -38674,21 +38682,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38700,17 +38708,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38730,13 +38738,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38776,10 +38784,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38787,9 +38795,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41438,17 +41446,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -41757,21 +41765,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41783,17 +41791,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41813,13 +41821,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41859,10 +41867,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41870,9 +41878,9 @@
       <c r="Q5" s="183"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44522,7 +44530,7 @@
         <f>SUM(T7:T57)</f>
         <v>741</v>
       </c>
-      <c r="U58" s="205">
+      <c r="U58" s="186">
         <f>SUM(U7:U57)</f>
         <v>349209</v>
       </c>
@@ -44536,17 +44544,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -44855,21 +44863,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44881,17 +44889,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44911,13 +44919,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44957,10 +44965,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44968,9 +44976,9 @@
       <c r="Q5" s="184"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -45047,34 +45055,48 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>23</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
       <c r="M7" s="148"/>
       <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
+      <c r="O7" s="144">
+        <v>2</v>
+      </c>
+      <c r="P7" s="145">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="145">
+        <v>2</v>
+      </c>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -45109,7 +45131,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+26</f>
+        <v>89</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -45119,7 +45144,9 @@
       <c r="J8" s="152"/>
       <c r="K8" s="153"/>
       <c r="L8" s="154"/>
-      <c r="M8" s="155"/>
+      <c r="M8" s="155">
+        <v>1</v>
+      </c>
       <c r="N8" s="156"/>
       <c r="O8" s="157"/>
       <c r="P8" s="158"/>
@@ -45132,11 +45159,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -45171,7 +45198,10 @@
       <c r="B9" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="162"/>
+      <c r="C9" s="162">
+        <f>6+1</f>
+        <v>7</v>
+      </c>
       <c r="D9" s="162"/>
       <c r="E9" s="162"/>
       <c r="F9" s="162"/>
@@ -45194,11 +45224,11 @@
       </c>
       <c r="U9" s="168">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V9" s="168">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W9" s="123"/>
       <c r="AF9" s="60"/>
@@ -45233,7 +45263,10 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <f>5+46</f>
+        <v>51</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -45256,11 +45289,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1224</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -45300,10 +45333,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -45314,15 +45351,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -45355,7 +45392,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1152+6+1440+576</f>
+        <v>3246</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -45365,24 +45405,36 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="159"/>
+      <c r="M12" s="155">
+        <v>15</v>
+      </c>
+      <c r="N12" s="156">
+        <v>20</v>
+      </c>
+      <c r="O12" s="157">
+        <v>7</v>
+      </c>
+      <c r="P12" s="158">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="158">
+        <v>18</v>
+      </c>
+      <c r="R12" s="159">
+        <v>15</v>
+      </c>
       <c r="S12" s="154"/>
       <c r="T12" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>78906</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3287.75</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -45424,7 +45476,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -45447,11 +45501,11 @@
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -45668,7 +45722,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -45691,11 +45747,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -45789,7 +45845,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -45812,11 +45870,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -45850,7 +45908,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -45873,11 +45933,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -45911,7 +45971,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -45934,11 +45996,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -45972,7 +46034,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -45995,11 +46059,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -46042,7 +46106,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>42</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -46052,11 +46118,17 @@
       <c r="J23" s="163"/>
       <c r="K23" s="164"/>
       <c r="L23" s="147"/>
-      <c r="M23" s="165"/>
+      <c r="M23" s="165">
+        <v>2</v>
+      </c>
       <c r="N23" s="166"/>
-      <c r="O23" s="162"/>
+      <c r="O23" s="162">
+        <v>2</v>
+      </c>
       <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
+      <c r="Q23" s="163">
+        <v>2</v>
+      </c>
       <c r="R23" s="164"/>
       <c r="S23" s="147"/>
       <c r="T23" s="150">
@@ -46065,11 +46137,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -46112,7 +46184,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -46135,11 +46209,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -46173,17 +46247,26 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <f>63+13</f>
+        <v>76</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
-      <c r="M25" s="165"/>
+      <c r="M25" s="165">
+        <v>1</v>
+      </c>
       <c r="N25" s="166"/>
       <c r="O25" s="162"/>
       <c r="P25" s="163"/>
@@ -46192,15 +46275,15 @@
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>77.458333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -46300,34 +46383,45 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <f>2+2</f>
+        <v>4</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
-      <c r="G28" s="162"/>
+      <c r="G28" s="162">
+        <v>127</v>
+      </c>
       <c r="H28" s="162"/>
       <c r="I28" s="162"/>
       <c r="J28" s="163"/>
       <c r="K28" s="164"/>
       <c r="L28" s="147"/>
-      <c r="M28" s="165"/>
+      <c r="M28" s="165">
+        <v>2</v>
+      </c>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>2</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>3</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
-        <f t="shared" si="0"/>
+        <f>H28+I28+J28+K28+N28+P28+R28</f>
         <v>0</v>
       </c>
       <c r="U28" s="167">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f>C28*24+M28*24+O28*24+Q28*24+T28+G28*24</f>
+        <v>3312</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -46385,7 +46479,10 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <f>58</f>
+        <v>58</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -46397,9 +46494,13 @@
       <c r="L30" s="147"/>
       <c r="M30" s="165"/>
       <c r="N30" s="166"/>
-      <c r="O30" s="162"/>
+      <c r="O30" s="162">
+        <v>2</v>
+      </c>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -46408,11 +46509,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -46423,7 +46524,10 @@
       <c r="B31" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="162"/>
+      <c r="C31" s="162">
+        <f>2+4</f>
+        <v>6</v>
+      </c>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
       <c r="F31" s="162"/>
@@ -46437,7 +46541,9 @@
       <c r="N31" s="166"/>
       <c r="O31" s="162"/>
       <c r="P31" s="163"/>
-      <c r="Q31" s="163"/>
+      <c r="Q31" s="163">
+        <v>1</v>
+      </c>
       <c r="R31" s="164"/>
       <c r="S31" s="147"/>
       <c r="T31" s="150">
@@ -46446,11 +46552,11 @@
       </c>
       <c r="U31" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V31" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -46537,34 +46643,49 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>9+72</f>
+        <v>81</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
       <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2093</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>87.208333333333329</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -46651,34 +46772,47 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>1080+2376</f>
+        <v>3456</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="M37" s="155">
+        <v>12</v>
+      </c>
       <c r="N37" s="156"/>
-      <c r="O37" s="157"/>
+      <c r="O37" s="157">
+        <v>58</v>
+      </c>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>47</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>21446</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>3574.3333333333335</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -46690,7 +46824,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <f>2+2</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -46713,11 +46850,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -46757,34 +46894,49 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>567+53</f>
+        <v>620</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>9</v>
+      </c>
       <c r="I40" s="151"/>
       <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="K40" s="153">
+        <v>15</v>
+      </c>
       <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="M40" s="155">
+        <v>1</v>
+      </c>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>15012</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -46795,7 +46947,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1440+80</f>
+        <v>1520</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -46805,11 +46960,17 @@
       <c r="J41" s="177"/>
       <c r="K41" s="178"/>
       <c r="L41" s="179"/>
-      <c r="M41" s="180"/>
+      <c r="M41" s="180">
+        <v>6</v>
+      </c>
       <c r="N41" s="181"/>
-      <c r="O41" s="176"/>
+      <c r="O41" s="176">
+        <v>11</v>
+      </c>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>15</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -46818,11 +46979,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>18624</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -46862,34 +47023,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>4644+3672+8208+5400+7128+1620</f>
+        <v>30672</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>5</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>6*6+5</f>
+        <v>41</v>
+      </c>
+      <c r="K43" s="159">
+        <f>87*6</f>
+        <v>522</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>325</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>168</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>373</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>189803</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31633.833333333332</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -47005,7 +47185,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -47013,26 +47196,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>5</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14134</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2355.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -47157,7 +47350,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -47180,11 +47375,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -47233,7 +47428,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -47256,11 +47453,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -47386,7 +47583,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>42359</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -47396,60 +47593,60 @@
       </c>
       <c r="G58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>477</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>759</v>
       </c>
       <c r="U58" s="51">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>353337</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>43696.749999999993</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -47457,17 +47654,2938 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="192" t="s">
+      <c r="C60" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="193"/>
-      <c r="E60" s="193"/>
-      <c r="F60" s="193"/>
-      <c r="G60" s="193"/>
-      <c r="H60" s="193"/>
-      <c r="I60" s="193"/>
-      <c r="J60" s="193"/>
-      <c r="K60" s="194"/>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30352C0-F5F8-4596-B7FF-2BAD0B6B36A9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="197" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="192" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="203" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="205" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="198" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="200" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="201"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="185"/>
+      <c r="Q5" s="185"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="185"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="185"/>
+      <c r="Q6" s="185"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="150">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="150">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="150">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="155"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="158"/>
+      <c r="Q8" s="158"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="160">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="161">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="161">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="163"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="168">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="168">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="163"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="166"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="163"/>
+      <c r="Q10" s="163"/>
+      <c r="R10" s="164"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="162"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="163"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="165"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="163"/>
+      <c r="Q11" s="163"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="158"/>
+      <c r="R12" s="159"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="161">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="161">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="162"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="163"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="164"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="168">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="168">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="162"/>
+      <c r="H14" s="162"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="163"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="165"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="163"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="167">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="167">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="162"/>
+      <c r="D15" s="162"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="163"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="164"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="164"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="165"/>
+      <c r="N17" s="166"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="163"/>
+      <c r="R17" s="164"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="164"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="162"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="166"/>
+      <c r="O19" s="162"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="164"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="162"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="164"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="162"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="163"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="164"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="166"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="162"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="164"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="166"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="163"/>
+      <c r="Q23" s="163"/>
+      <c r="R23" s="164"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="162"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="165"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="164"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="166"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="164"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="162"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="163"/>
+      <c r="Q26" s="163"/>
+      <c r="R26" s="164"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="162"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="166"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="163"/>
+      <c r="Q27" s="163"/>
+      <c r="R27" s="164"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="150"/>
+      <c r="U27" s="167"/>
+      <c r="V27" s="167"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="163"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="166"/>
+      <c r="O28" s="162"/>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="163"/>
+      <c r="R28" s="164"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="162"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="166"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="163"/>
+      <c r="Q29" s="163"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="162"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="166"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="163"/>
+      <c r="Q30" s="163"/>
+      <c r="R30" s="164"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="162"/>
+      <c r="D31" s="162"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="162"/>
+      <c r="H31" s="162"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="164"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="162"/>
+      <c r="D32" s="162"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="164"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="162"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="163"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="166"/>
+      <c r="O33" s="162"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="164"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="164"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="162"/>
+      <c r="D35" s="162"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="166"/>
+      <c r="O35" s="162"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="162"/>
+      <c r="D36" s="162"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="163"/>
+      <c r="K36" s="164"/>
+      <c r="L36" s="147"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="166"/>
+      <c r="O36" s="162"/>
+      <c r="P36" s="163"/>
+      <c r="Q36" s="163"/>
+      <c r="R36" s="164"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="151"/>
+      <c r="H37" s="151"/>
+      <c r="I37" s="151"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="157"/>
+      <c r="P37" s="158"/>
+      <c r="Q37" s="158"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="154"/>
+      <c r="T37" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="169">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="169">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="162"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="162"/>
+      <c r="P38" s="163"/>
+      <c r="Q38" s="163"/>
+      <c r="R38" s="164"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="167">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="167">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="170"/>
+      <c r="D39" s="170"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="170"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="170"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="171"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="175"/>
+      <c r="U39" s="175"/>
+      <c r="V39" s="175"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="151"/>
+      <c r="I40" s="151"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="157"/>
+      <c r="P40" s="158"/>
+      <c r="Q40" s="158"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="169">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="169">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="180"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="176"/>
+      <c r="P41" s="177"/>
+      <c r="Q41" s="177"/>
+      <c r="R41" s="178"/>
+      <c r="S41" s="179"/>
+      <c r="T41" s="182">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="182">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="182">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="162"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="163"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="162"/>
+      <c r="P42" s="163"/>
+      <c r="Q42" s="163"/>
+      <c r="R42" s="164"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="157"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="158"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="156"/>
+      <c r="O43" s="157"/>
+      <c r="P43" s="158"/>
+      <c r="Q43" s="158"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="154"/>
+      <c r="T43" s="169">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="169">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="169">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="162"/>
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="147"/>
+      <c r="M44" s="165"/>
+      <c r="N44" s="166"/>
+      <c r="O44" s="162"/>
+      <c r="P44" s="163"/>
+      <c r="Q44" s="163"/>
+      <c r="R44" s="164"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="167"/>
+      <c r="U44" s="167"/>
+      <c r="V44" s="167"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="162"/>
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="165"/>
+      <c r="N45" s="166"/>
+      <c r="O45" s="162"/>
+      <c r="P45" s="163"/>
+      <c r="Q45" s="163"/>
+      <c r="R45" s="164"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="167">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="167">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="167">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="162"/>
+      <c r="D46" s="162"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="162"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="147"/>
+      <c r="M46" s="165"/>
+      <c r="N46" s="166"/>
+      <c r="O46" s="162"/>
+      <c r="P46" s="163"/>
+      <c r="Q46" s="163"/>
+      <c r="R46" s="164"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="167">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="167">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="158"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
+      <c r="N47" s="156"/>
+      <c r="O47" s="157"/>
+      <c r="P47" s="158"/>
+      <c r="Q47" s="158"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="169">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="169">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="162"/>
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="165"/>
+      <c r="N48" s="166"/>
+      <c r="O48" s="162"/>
+      <c r="P48" s="163"/>
+      <c r="Q48" s="163"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="147"/>
+      <c r="T48" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="162"/>
+      <c r="D49" s="162"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="147"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="163"/>
+      <c r="Q49" s="163"/>
+      <c r="R49" s="164"/>
+      <c r="S49" s="147"/>
+      <c r="T49" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="162"/>
+      <c r="D50" s="162"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="162"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="165"/>
+      <c r="N50" s="166"/>
+      <c r="O50" s="162"/>
+      <c r="P50" s="163"/>
+      <c r="Q50" s="163"/>
+      <c r="R50" s="164"/>
+      <c r="S50" s="147"/>
+      <c r="T50" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="159"/>
+      <c r="L51" s="154"/>
+      <c r="M51" s="155"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="157"/>
+      <c r="P51" s="158"/>
+      <c r="Q51" s="158"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="154"/>
+      <c r="T51" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="169">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="169">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="162"/>
+      <c r="D52" s="162"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="163"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="166"/>
+      <c r="O52" s="162"/>
+      <c r="P52" s="163"/>
+      <c r="Q52" s="163"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="167">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="162"/>
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="163"/>
+      <c r="K53" s="164"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="165"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="162"/>
+      <c r="P53" s="163"/>
+      <c r="Q53" s="163"/>
+      <c r="R53" s="164"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="162"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="164"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="165"/>
+      <c r="N54" s="166"/>
+      <c r="O54" s="162"/>
+      <c r="P54" s="163"/>
+      <c r="Q54" s="163"/>
+      <c r="R54" s="164"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="162"/>
+      <c r="D55" s="162"/>
+      <c r="E55" s="162"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="164"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="165"/>
+      <c r="N55" s="166"/>
+      <c r="O55" s="162"/>
+      <c r="P55" s="163"/>
+      <c r="Q55" s="163"/>
+      <c r="R55" s="164"/>
+      <c r="S55" s="147"/>
+      <c r="T55" s="167"/>
+      <c r="U55" s="167"/>
+      <c r="V55" s="167"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="164"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="165"/>
+      <c r="N56" s="166"/>
+      <c r="O56" s="162"/>
+      <c r="P56" s="163"/>
+      <c r="Q56" s="163"/>
+      <c r="R56" s="164"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="167"/>
+      <c r="U56" s="167"/>
+      <c r="V56" s="167"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="162"/>
+      <c r="E57" s="162"/>
+      <c r="F57" s="162"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="162"/>
+      <c r="I57" s="162"/>
+      <c r="J57" s="163"/>
+      <c r="K57" s="164"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="165"/>
+      <c r="N57" s="166"/>
+      <c r="O57" s="162"/>
+      <c r="P57" s="163"/>
+      <c r="Q57" s="163"/>
+      <c r="R57" s="164"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="167"/>
+      <c r="U57" s="167"/>
+      <c r="V57" s="167"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="147"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="194" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="195"/>
+      <c r="E60" s="195"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="195"/>
+      <c r="H60" s="195"/>
+      <c r="I60" s="195"/>
+      <c r="J60" s="195"/>
+      <c r="K60" s="196"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -47776,21 +50894,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47802,17 +50920,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -47832,13 +50950,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -47878,10 +50996,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -47889,9 +51007,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -50496,17 +53614,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -50815,21 +53933,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -50841,17 +53959,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -50871,13 +53989,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -50917,10 +54035,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -50928,9 +54046,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -53528,17 +56646,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -53847,21 +56965,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -53873,17 +56991,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -53903,13 +57021,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -53949,10 +57067,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -53960,9 +57078,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -56569,17 +59687,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -56888,21 +60006,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -56914,17 +60032,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -56944,13 +60062,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -56990,10 +60108,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -57001,9 +60119,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -59603,17 +62721,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -59922,21 +63040,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -59948,17 +63066,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -59978,13 +63096,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -60024,10 +63142,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -60035,9 +63153,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -62619,17 +65737,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -62938,21 +66056,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -62964,17 +66082,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -62994,13 +66112,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -63040,10 +66158,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -63051,9 +66169,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -65633,17 +68751,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -65952,21 +69070,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="197"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -65978,17 +69096,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="192" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="191"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="192"/>
+      <c r="G4" s="192"/>
+      <c r="H4" s="192"/>
+      <c r="I4" s="192"/>
+      <c r="J4" s="202"/>
+      <c r="K4" s="193"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -66008,13 +69126,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="201" t="s">
+      <c r="T4" s="203" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="203" t="s">
+      <c r="U4" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="196" t="s">
+      <c r="V4" s="198" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -66054,10 +69172,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="198" t="s">
+      <c r="J5" s="200" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="199"/>
+      <c r="K5" s="201"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -66065,9 +69183,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="202"/>
-      <c r="U5" s="204"/>
-      <c r="V5" s="197"/>
+      <c r="T5" s="204"/>
+      <c r="U5" s="206"/>
+      <c r="V5" s="199"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -68654,17 +71772,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="192" t="s">
+      <c r="C59" s="194" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
-      <c r="H59" s="193"/>
-      <c r="I59" s="193"/>
-      <c r="J59" s="193"/>
-      <c r="K59" s="194"/>
+      <c r="D59" s="195"/>
+      <c r="E59" s="195"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="195"/>
+      <c r="H59" s="195"/>
+      <c r="I59" s="195"/>
+      <c r="J59" s="195"/>
+      <c r="K59" s="196"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B5305-3C75-4688-876E-B71A34A14B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEAC8A7-9CDA-4CE8-9378-ECCCDBEA4D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="14" activeTab="22" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="15" activeTab="23" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="02-25-2026" sheetId="31" r:id="rId22"/>
     <sheet name="02-26-2026" sheetId="32" r:id="rId23"/>
     <sheet name="02-27-2026" sheetId="33" r:id="rId24"/>
+    <sheet name="02-28-2026" sheetId="34" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'02-03-2026'!$A$1:$W$58</definedName>
@@ -60,6 +61,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="21">'02-25-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="22">'02-26-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="23">'02-27-2026'!$A$1:$W$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'02-28-2026'!$A$1:$W$59</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'COUNT SHEET'!$A$1:$AM$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'COUNT SHEET SAMPLE'!$A$1:$Q$88</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$83</definedName>
@@ -80,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2075" uniqueCount="105">
   <si>
     <t>ROUTE 1</t>
   </si>
@@ -393,6 +395,9 @@
   </si>
   <si>
     <t>DATE: 02/27/2026</t>
+  </si>
+  <si>
+    <t>DATE: 02/28/2026</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1537,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2105,6 +2110,9 @@
     <xf numFmtId="166" fontId="13" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3420,34 +3428,34 @@
       <c r="AP20" s="7"/>
     </row>
     <row r="21" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="190" t="s">
+      <c r="A21" s="191" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="187" t="s">
+      <c r="B21" s="188" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="188"/>
-      <c r="D21" s="189"/>
-      <c r="E21" s="187" t="s">
+      <c r="C21" s="189"/>
+      <c r="D21" s="190"/>
+      <c r="E21" s="188" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="188"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="187" t="s">
+      <c r="F21" s="189"/>
+      <c r="G21" s="190"/>
+      <c r="H21" s="188" t="s">
         <v>41</v>
       </c>
-      <c r="I21" s="188"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="187" t="s">
+      <c r="I21" s="189"/>
+      <c r="J21" s="190"/>
+      <c r="K21" s="188" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="188"/>
-      <c r="M21" s="189"/>
-      <c r="N21" s="187" t="s">
+      <c r="L21" s="189"/>
+      <c r="M21" s="190"/>
+      <c r="N21" s="188" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="188"/>
-      <c r="P21" s="189"/>
+      <c r="O21" s="189"/>
+      <c r="P21" s="190"/>
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
@@ -3470,7 +3478,7 @@
       <c r="AP21" s="7"/>
     </row>
     <row r="22" spans="1:42" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="191"/>
+      <c r="A22" s="192"/>
       <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
@@ -3694,21 +3702,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -3720,17 +3728,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -3750,13 +3758,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -3796,10 +3804,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -3807,9 +3815,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -6392,17 +6400,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -6711,21 +6719,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -6737,17 +6745,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -6767,13 +6775,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -6813,10 +6821,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -6824,9 +6832,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -9405,17 +9413,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -9724,21 +9732,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -9750,17 +9758,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -9780,13 +9788,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -9826,10 +9834,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -9837,9 +9845,9 @@
       <c r="Q5" s="108"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -12409,17 +12417,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -12728,21 +12736,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -12754,17 +12762,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -12784,13 +12792,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -12830,10 +12838,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -12841,9 +12849,9 @@
       <c r="Q5" s="129"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -15427,17 +15435,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -15746,21 +15754,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -15772,17 +15780,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -15802,13 +15810,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -15848,10 +15856,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -15859,9 +15867,9 @@
       <c r="Q5" s="130"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -18435,17 +18443,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -18754,21 +18762,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -18780,17 +18788,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -18810,13 +18818,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -18856,10 +18864,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -18867,9 +18875,9 @@
       <c r="Q5" s="131"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -21276,17 +21284,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -21595,21 +21603,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -21621,17 +21629,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -21651,13 +21659,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -21697,10 +21705,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -21708,9 +21716,9 @@
       <c r="Q5" s="140"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -24296,17 +24304,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -24615,21 +24623,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -24641,17 +24649,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -24671,13 +24679,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -24717,10 +24725,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -24728,9 +24736,9 @@
       <c r="Q5" s="139"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -27315,17 +27323,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -27634,21 +27642,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -27660,17 +27668,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -27690,13 +27698,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -27736,10 +27744,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -27747,9 +27755,9 @@
       <c r="Q5" s="141"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -30407,17 +30415,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -30726,21 +30734,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -30752,17 +30760,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -30782,13 +30790,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -30828,10 +30836,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -30839,9 +30847,9 @@
       <c r="Q5" s="142"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -33328,17 +33336,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -33638,16 +33646,16 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="197" t="s">
+      <c r="H1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
     </row>
     <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -33659,15 +33667,15 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="194"/>
       <c r="K4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35316,15 +35324,15 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="197"/>
       <c r="O59" s="72" t="s">
         <v>62</v>
       </c>
@@ -35597,21 +35605,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -35623,17 +35631,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -35653,13 +35661,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -35699,10 +35707,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -35710,9 +35718,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -38363,17 +38371,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -38682,21 +38690,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -38708,17 +38716,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -38738,13 +38746,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -38784,10 +38792,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -38795,9 +38803,9 @@
       <c r="Q5" s="143"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -41446,17 +41454,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -41765,21 +41773,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -41791,17 +41799,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -41821,13 +41829,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -41867,10 +41875,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -41878,9 +41886,9 @@
       <c r="Q5" s="183"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -44544,17 +44552,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -44863,21 +44871,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -44889,17 +44897,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -44919,13 +44927,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -44965,10 +44973,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -44976,9 +44984,9 @@
       <c r="Q5" s="184"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -47654,17 +47662,17 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -47973,21 +47981,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -47999,17 +48007,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -48029,13 +48037,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -48075,10 +48083,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -48086,9 +48094,9 @@
       <c r="Q5" s="185"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -48165,34 +48173,48 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>23</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
       <c r="M7" s="148"/>
       <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
+      <c r="O7" s="144">
+        <v>2</v>
+      </c>
+      <c r="P7" s="145">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="145">
+        <v>2</v>
+      </c>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -48227,7 +48249,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+26</f>
+        <v>89</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -48237,7 +48262,9 @@
       <c r="J8" s="152"/>
       <c r="K8" s="153"/>
       <c r="L8" s="154"/>
-      <c r="M8" s="155"/>
+      <c r="M8" s="155">
+        <v>1</v>
+      </c>
       <c r="N8" s="156"/>
       <c r="O8" s="157"/>
       <c r="P8" s="158"/>
@@ -48250,11 +48277,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -48301,9 +48328,13 @@
       <c r="L9" s="147"/>
       <c r="M9" s="165"/>
       <c r="N9" s="166"/>
-      <c r="O9" s="162"/>
+      <c r="O9" s="162">
+        <v>1</v>
+      </c>
       <c r="P9" s="163"/>
-      <c r="Q9" s="163"/>
+      <c r="Q9" s="163">
+        <v>1</v>
+      </c>
       <c r="R9" s="164"/>
       <c r="S9" s="147"/>
       <c r="T9" s="167">
@@ -48312,11 +48343,11 @@
       </c>
       <c r="U9" s="168">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V9" s="168">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" s="123"/>
       <c r="AF9" s="60"/>
@@ -48351,7 +48382,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <v>42</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -48365,7 +48398,9 @@
       <c r="N10" s="166"/>
       <c r="O10" s="162"/>
       <c r="P10" s="163"/>
-      <c r="Q10" s="163"/>
+      <c r="Q10" s="163">
+        <v>4</v>
+      </c>
       <c r="R10" s="164"/>
       <c r="S10" s="147"/>
       <c r="T10" s="150">
@@ -48374,11 +48409,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -48418,10 +48453,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -48432,15 +48471,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -48473,7 +48512,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1080+54+1440+576</f>
+        <v>3222</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -48483,24 +48525,36 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="159"/>
+      <c r="M12" s="155">
+        <v>4</v>
+      </c>
+      <c r="N12" s="156">
+        <v>18</v>
+      </c>
+      <c r="O12" s="157">
+        <v>12</v>
+      </c>
+      <c r="P12" s="158">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="158">
+        <v>17</v>
+      </c>
+      <c r="R12" s="159">
+        <v>18</v>
+      </c>
       <c r="S12" s="154"/>
       <c r="T12" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>78167</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3256.9583333333335</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -48542,7 +48596,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -48565,11 +48621,11 @@
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -48786,7 +48842,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -48809,11 +48867,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -48907,7 +48965,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -48930,11 +48990,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -48968,7 +49028,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -48991,11 +49053,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -49029,7 +49091,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -49052,11 +49116,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -49090,7 +49154,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -49113,11 +49179,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -49160,7 +49226,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>42</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -49170,11 +49238,17 @@
       <c r="J23" s="163"/>
       <c r="K23" s="164"/>
       <c r="L23" s="147"/>
-      <c r="M23" s="165"/>
+      <c r="M23" s="165">
+        <v>2</v>
+      </c>
       <c r="N23" s="166"/>
-      <c r="O23" s="162"/>
+      <c r="O23" s="162">
+        <v>1</v>
+      </c>
       <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
+      <c r="Q23" s="163">
+        <v>2</v>
+      </c>
       <c r="R23" s="164"/>
       <c r="S23" s="147"/>
       <c r="T23" s="150">
@@ -49183,11 +49257,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -49230,7 +49304,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -49253,11 +49329,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -49291,13 +49367,20 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <f>63+10</f>
+        <v>73</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
@@ -49310,15 +49393,15 @@
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1763</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>73.458333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -49418,7 +49501,9 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <v>127</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
@@ -49430,9 +49515,13 @@
       <c r="L28" s="147"/>
       <c r="M28" s="165"/>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>2</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>3</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
@@ -49441,11 +49530,11 @@
       </c>
       <c r="U28" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3168</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -49503,7 +49592,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <v>58</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -49515,9 +49606,13 @@
       <c r="L30" s="147"/>
       <c r="M30" s="165"/>
       <c r="N30" s="166"/>
-      <c r="O30" s="162"/>
+      <c r="O30" s="162">
+        <v>2</v>
+      </c>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -49526,11 +49621,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -49541,7 +49636,9 @@
       <c r="B31" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="162"/>
+      <c r="C31" s="162">
+        <v>4</v>
+      </c>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
       <c r="F31" s="162"/>
@@ -49553,7 +49650,9 @@
       <c r="L31" s="147"/>
       <c r="M31" s="165"/>
       <c r="N31" s="166"/>
-      <c r="O31" s="162"/>
+      <c r="O31" s="162">
+        <v>1</v>
+      </c>
       <c r="P31" s="163"/>
       <c r="Q31" s="163"/>
       <c r="R31" s="164"/>
@@ -49564,11 +49663,11 @@
       </c>
       <c r="U31" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V31" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -49655,34 +49754,49 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>9+72+72</f>
+        <v>153</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
       <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3821</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>159.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -49769,34 +49883,47 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>2376+972+72+864</f>
+        <v>4284</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="M37" s="155">
+        <v>9</v>
+      </c>
       <c r="N37" s="156"/>
-      <c r="O37" s="157"/>
+      <c r="O37" s="157">
+        <v>29</v>
+      </c>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>75</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>26390</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4398.333333333333</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -49808,7 +49935,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <f>2+2</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -49831,11 +49961,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -49875,34 +50005,51 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>567+53</f>
+        <v>620</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>4</v>
+      </c>
       <c r="I40" s="151"/>
-      <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="J40" s="152">
+        <v>5</v>
+      </c>
+      <c r="K40" s="153">
+        <v>15</v>
+      </c>
       <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="M40" s="155">
+        <v>1</v>
+      </c>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>15012</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -49913,7 +50060,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1440+70</f>
+        <v>1510</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -49923,11 +50073,17 @@
       <c r="J41" s="177"/>
       <c r="K41" s="178"/>
       <c r="L41" s="179"/>
-      <c r="M41" s="180"/>
+      <c r="M41" s="180">
+        <v>6</v>
+      </c>
       <c r="N41" s="181"/>
-      <c r="O41" s="176"/>
+      <c r="O41" s="176">
+        <v>10</v>
+      </c>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>18</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -49936,11 +50092,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>18528</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -49980,34 +50136,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>3888+5292+8208+5400+7128+864</f>
+        <v>30780</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>2</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>8*6+1</f>
+        <v>49</v>
+      </c>
+      <c r="K43" s="159">
+        <f>87*6</f>
+        <v>522</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>4</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>332</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>406</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>189712</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31618.666666666668</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -50123,7 +50298,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+44+2268</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -50131,26 +50309,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>5</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14134</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2355.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -50275,7 +50463,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -50298,11 +50488,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -50351,7 +50541,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -50374,11 +50566,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -50504,7 +50696,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>43435</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -50518,56 +50710,56 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>558</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="U58" s="51">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
-      </c>
-      <c r="V58" s="51">
+        <v>358531</v>
+      </c>
+      <c r="V58" s="186">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>44515.791666666664</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -50575,17 +50767,2938 @@
       <c r="B60" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="194" t="s">
+      <c r="C60" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="195"/>
-      <c r="E60" s="195"/>
-      <c r="F60" s="195"/>
-      <c r="G60" s="195"/>
-      <c r="H60" s="195"/>
-      <c r="I60" s="195"/>
-      <c r="J60" s="195"/>
-      <c r="K60" s="196"/>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
+      <c r="U60" s="72" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B61" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="114"/>
+      <c r="K61" s="68"/>
+      <c r="U61" s="55"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B62" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="48"/>
+      <c r="D62" s="48"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="109"/>
+      <c r="K62" s="69"/>
+      <c r="U62" s="50"/>
+    </row>
+    <row r="63" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="70"/>
+      <c r="F63" s="70"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="70"/>
+      <c r="I63" s="70"/>
+      <c r="J63" s="115"/>
+      <c r="K63" s="71"/>
+      <c r="U63" s="56"/>
+    </row>
+    <row r="64" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="79" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="F65" s="67"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="67"/>
+      <c r="J65" s="114"/>
+      <c r="K65" s="68"/>
+      <c r="U65" s="55"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" s="48"/>
+      <c r="D66" s="48"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="109"/>
+      <c r="K66" s="69"/>
+      <c r="U66" s="50"/>
+    </row>
+    <row r="67" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="70"/>
+      <c r="D67" s="70"/>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="70"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="115"/>
+      <c r="K67" s="71"/>
+      <c r="U67" s="56"/>
+    </row>
+    <row r="68" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
+      <c r="F69" s="67"/>
+      <c r="G69" s="67"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="114"/>
+      <c r="K69" s="68"/>
+      <c r="U69" s="55"/>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B70" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="48"/>
+      <c r="D70" s="48"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="109"/>
+      <c r="K70" s="69"/>
+      <c r="U70" s="50"/>
+    </row>
+    <row r="71" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C71" s="70"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="70"/>
+      <c r="F71" s="70"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="115"/>
+      <c r="K71" s="71"/>
+      <c r="U71" s="56"/>
+    </row>
+    <row r="72" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B73" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="F73" s="67"/>
+      <c r="G73" s="67"/>
+      <c r="H73" s="67"/>
+      <c r="I73" s="67"/>
+      <c r="J73" s="114"/>
+      <c r="K73" s="68"/>
+      <c r="U73" s="55"/>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B74" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C74" s="48"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="109"/>
+      <c r="K74" s="69"/>
+      <c r="U74" s="50"/>
+    </row>
+    <row r="75" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="115"/>
+      <c r="K75" s="71"/>
+      <c r="U75" s="56"/>
+    </row>
+    <row r="76" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B77" s="79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="F77" s="67"/>
+      <c r="G77" s="67"/>
+      <c r="H77" s="67"/>
+      <c r="I77" s="67"/>
+      <c r="J77" s="114"/>
+      <c r="K77" s="68"/>
+      <c r="U77" s="55"/>
+    </row>
+    <row r="78" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B78" s="80" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="48"/>
+      <c r="D78" s="48"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="109"/>
+      <c r="K78" s="69"/>
+      <c r="U78" s="50"/>
+    </row>
+    <row r="79" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
+      <c r="F79" s="70"/>
+      <c r="G79" s="70"/>
+      <c r="H79" s="70"/>
+      <c r="I79" s="70"/>
+      <c r="J79" s="115"/>
+      <c r="K79" s="71"/>
+      <c r="U79" s="56"/>
+    </row>
+    <row r="80" spans="2:21" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="2:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="116"/>
+      <c r="K81" s="66"/>
+      <c r="U81" s="64"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="I1:U1"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
+  <pageSetup paperSize="14" scale="70" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="24" max="80" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB370E7-AE3E-4115-AA82-9A126A8EA922}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BB81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="76" customWidth="1"/>
+    <col min="3" max="6" width="10" style="57" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="6.7109375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" style="57" customWidth="1"/>
+    <col min="11" max="11" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.42578125" style="57" customWidth="1"/>
+    <col min="13" max="13" width="10" style="57" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="57" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" style="57" customWidth="1"/>
+    <col min="17" max="17" width="10" style="57" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.42578125" style="57" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="57" customWidth="1"/>
+    <col min="22" max="22" width="19.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="49" width="7.28515625" style="57" customWidth="1"/>
+    <col min="50" max="50" width="1.5703125" style="57" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" style="57" customWidth="1"/>
+    <col min="52" max="52" width="1.28515625" style="57" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="10.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9.140625" style="57"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="75" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="198" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="B2" s="76" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
+      <c r="M4" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="N4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="P4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q4" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="117" t="s">
+        <v>72</v>
+      </c>
+      <c r="S4" s="57"/>
+      <c r="T4" s="204" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="206" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="199" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="59"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
+      <c r="AO4" s="59"/>
+      <c r="AP4" s="59"/>
+      <c r="AQ4" s="59"/>
+      <c r="AR4" s="59"/>
+      <c r="AS4" s="59"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+    </row>
+    <row r="5" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="87"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="92" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="201" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" s="202"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="187"/>
+      <c r="Q5" s="187"/>
+      <c r="R5" s="89"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="59"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+    </row>
+    <row r="6" spans="1:54" s="58" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="87"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="187"/>
+      <c r="K6" s="89"/>
+      <c r="M6" s="87"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="92"/>
+      <c r="P6" s="187"/>
+      <c r="Q6" s="187"/>
+      <c r="R6" s="89"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="AF6" s="59"/>
+      <c r="AG6" s="59"/>
+      <c r="AH6" s="59"/>
+      <c r="AI6" s="59"/>
+      <c r="AJ6" s="59"/>
+      <c r="AK6" s="59"/>
+      <c r="AL6" s="59"/>
+      <c r="AM6" s="59"/>
+      <c r="AN6" s="59"/>
+      <c r="AO6" s="59"/>
+      <c r="AP6" s="59"/>
+      <c r="AQ6" s="59"/>
+      <c r="AR6" s="59"/>
+      <c r="AS6" s="59"/>
+      <c r="AT6" s="59"/>
+      <c r="AU6" s="59"/>
+      <c r="AV6" s="59"/>
+      <c r="AW6" s="59"/>
+      <c r="AX6" s="59"/>
+      <c r="AY6" s="59"/>
+      <c r="AZ6" s="59"/>
+      <c r="BA6" s="59"/>
+      <c r="BB6" s="59"/>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A7" s="75">
+        <v>1</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="144"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="144"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="144"/>
+      <c r="J7" s="145"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="148"/>
+      <c r="N7" s="149"/>
+      <c r="O7" s="144"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="150">
+        <f>H7+I7+J7+K7+N7+P7+R7</f>
+        <v>0</v>
+      </c>
+      <c r="U7" s="150">
+        <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="150">
+        <f>U7/24</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="123"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
+      <c r="AK7" s="60"/>
+      <c r="AL7" s="60"/>
+      <c r="AM7" s="60"/>
+      <c r="AN7" s="60"/>
+      <c r="AO7" s="60"/>
+      <c r="AP7" s="60"/>
+      <c r="AQ7" s="60"/>
+      <c r="AR7" s="60"/>
+      <c r="AS7" s="60"/>
+      <c r="AT7" s="60"/>
+      <c r="AU7" s="60"/>
+      <c r="AV7" s="60"/>
+      <c r="AW7" s="60"/>
+      <c r="AX7" s="60"/>
+      <c r="AY7" s="60"/>
+      <c r="AZ7" s="60"/>
+      <c r="BA7" s="60"/>
+      <c r="BB7" s="60"/>
+    </row>
+    <row r="8" spans="1:54" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="75">
+        <f>A7+1</f>
+        <v>2</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="152"/>
+      <c r="K8" s="153"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="155"/>
+      <c r="N8" s="156"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="158"/>
+      <c r="Q8" s="158"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="160">
+        <f t="shared" ref="T8:T41" si="0">H8+I8+J8+K8+N8+P8+R8</f>
+        <v>0</v>
+      </c>
+      <c r="U8" s="161">
+        <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="161">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="123"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
+      <c r="AK8" s="60"/>
+      <c r="AL8" s="60"/>
+      <c r="AM8" s="60"/>
+      <c r="AN8" s="60"/>
+      <c r="AO8" s="60"/>
+      <c r="AP8" s="60"/>
+      <c r="AQ8" s="60"/>
+      <c r="AR8" s="60"/>
+      <c r="AS8" s="60"/>
+      <c r="AT8" s="60"/>
+      <c r="AU8" s="60"/>
+      <c r="AV8" s="60"/>
+      <c r="AW8" s="60"/>
+      <c r="AX8" s="60"/>
+      <c r="AY8" s="60"/>
+      <c r="AZ8" s="60"/>
+      <c r="BA8" s="60"/>
+      <c r="BB8" s="60"/>
+    </row>
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A9" s="75">
+        <f t="shared" ref="A9:A57" si="1">A8+1</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="162"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="162"/>
+      <c r="F9" s="162"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="162"/>
+      <c r="J9" s="163"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="147"/>
+      <c r="M9" s="165"/>
+      <c r="N9" s="166"/>
+      <c r="O9" s="162"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U9" s="168">
+        <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="168">
+        <f t="shared" ref="V9:V11" si="3">U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="123"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
+      <c r="AK9" s="60"/>
+      <c r="AL9" s="60"/>
+      <c r="AM9" s="60"/>
+      <c r="AN9" s="60"/>
+      <c r="AO9" s="60"/>
+      <c r="AP9" s="60"/>
+      <c r="AQ9" s="60"/>
+      <c r="AR9" s="60"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="60"/>
+      <c r="AV9" s="60"/>
+      <c r="AW9" s="60"/>
+      <c r="AX9" s="60"/>
+      <c r="AY9" s="60"/>
+      <c r="AZ9" s="60"/>
+      <c r="BA9" s="60"/>
+      <c r="BB9" s="60"/>
+    </row>
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A10" s="75">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="162"/>
+      <c r="D10" s="162"/>
+      <c r="E10" s="162"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="162"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="162"/>
+      <c r="J10" s="163"/>
+      <c r="K10" s="164"/>
+      <c r="L10" s="147"/>
+      <c r="M10" s="165"/>
+      <c r="N10" s="166"/>
+      <c r="O10" s="162"/>
+      <c r="P10" s="163"/>
+      <c r="Q10" s="163"/>
+      <c r="R10" s="164"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U10" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W10" s="123"/>
+      <c r="AF10" s="60"/>
+      <c r="AG10" s="60"/>
+      <c r="AH10" s="60"/>
+      <c r="AI10" s="60"/>
+      <c r="AJ10" s="60"/>
+      <c r="AK10" s="60"/>
+      <c r="AL10" s="60"/>
+      <c r="AM10" s="60"/>
+      <c r="AN10" s="60"/>
+      <c r="AO10" s="60"/>
+      <c r="AP10" s="60"/>
+      <c r="AQ10" s="60"/>
+      <c r="AR10" s="60"/>
+      <c r="AS10" s="60"/>
+      <c r="AT10" s="60"/>
+      <c r="AU10" s="60"/>
+      <c r="AV10" s="60"/>
+      <c r="AW10" s="60"/>
+      <c r="AX10" s="60"/>
+      <c r="AY10" s="60"/>
+      <c r="AZ10" s="60"/>
+      <c r="BA10" s="60"/>
+      <c r="BB10" s="60"/>
+    </row>
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A11" s="75">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="162"/>
+      <c r="I11" s="162"/>
+      <c r="J11" s="163"/>
+      <c r="K11" s="164"/>
+      <c r="L11" s="147"/>
+      <c r="M11" s="165"/>
+      <c r="N11" s="166"/>
+      <c r="O11" s="162"/>
+      <c r="P11" s="163"/>
+      <c r="Q11" s="163"/>
+      <c r="R11" s="164"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U11" s="150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="150">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="60"/>
+      <c r="AM11" s="60"/>
+      <c r="AN11" s="60"/>
+      <c r="AO11" s="60"/>
+      <c r="AP11" s="60"/>
+      <c r="AQ11" s="60"/>
+      <c r="AR11" s="60"/>
+      <c r="AS11" s="60"/>
+      <c r="AT11" s="60"/>
+      <c r="AU11" s="60"/>
+      <c r="AV11" s="60"/>
+      <c r="AW11" s="60"/>
+      <c r="AX11" s="60"/>
+      <c r="AY11" s="60"/>
+      <c r="AZ11" s="60"/>
+      <c r="BA11" s="60"/>
+      <c r="BB11" s="60"/>
+    </row>
+    <row r="12" spans="1:54" s="61" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="75">
+        <v>7</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="157"/>
+      <c r="P12" s="158"/>
+      <c r="Q12" s="158"/>
+      <c r="R12" s="159"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="161">
+        <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="161">
+        <f>U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="57"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="60"/>
+      <c r="AG12" s="60"/>
+      <c r="AH12" s="60"/>
+      <c r="AI12" s="60"/>
+      <c r="AJ12" s="60"/>
+      <c r="AK12" s="60"/>
+      <c r="AL12" s="60"/>
+      <c r="AM12" s="60"/>
+      <c r="AN12" s="60"/>
+      <c r="AO12" s="60"/>
+      <c r="AP12" s="60"/>
+      <c r="AQ12" s="60"/>
+      <c r="AR12" s="60"/>
+      <c r="AS12" s="60"/>
+      <c r="AT12" s="60"/>
+      <c r="AU12" s="60"/>
+      <c r="AV12" s="60"/>
+      <c r="AW12" s="60"/>
+      <c r="AX12" s="60"/>
+      <c r="AY12" s="60"/>
+      <c r="AZ12" s="60"/>
+      <c r="BA12" s="60"/>
+      <c r="BB12" s="60"/>
+    </row>
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A13" s="75">
+        <v>11</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="162"/>
+      <c r="D13" s="162"/>
+      <c r="E13" s="162"/>
+      <c r="F13" s="162"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="162"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="163"/>
+      <c r="K13" s="164"/>
+      <c r="L13" s="147"/>
+      <c r="M13" s="165"/>
+      <c r="N13" s="166"/>
+      <c r="O13" s="162"/>
+      <c r="P13" s="163"/>
+      <c r="Q13" s="163"/>
+      <c r="R13" s="164"/>
+      <c r="S13" s="147"/>
+      <c r="T13" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U13" s="168">
+        <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="168">
+        <f>U13/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="60"/>
+      <c r="AG13" s="60"/>
+      <c r="AH13" s="60"/>
+      <c r="AI13" s="60"/>
+      <c r="AJ13" s="60"/>
+      <c r="AK13" s="60"/>
+      <c r="AL13" s="60"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="60"/>
+      <c r="AQ13" s="60"/>
+      <c r="AR13" s="60"/>
+      <c r="AS13" s="60"/>
+      <c r="AT13" s="60"/>
+      <c r="AU13" s="60"/>
+      <c r="AV13" s="60"/>
+      <c r="AW13" s="60"/>
+      <c r="AX13" s="60"/>
+      <c r="AY13" s="60"/>
+      <c r="AZ13" s="60"/>
+      <c r="BA13" s="60"/>
+      <c r="BB13" s="60"/>
+    </row>
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A14" s="75">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="74" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
+      <c r="E14" s="162"/>
+      <c r="F14" s="162"/>
+      <c r="G14" s="162"/>
+      <c r="H14" s="162"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="163"/>
+      <c r="K14" s="164"/>
+      <c r="L14" s="147"/>
+      <c r="M14" s="165"/>
+      <c r="N14" s="166"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="163"/>
+      <c r="Q14" s="163"/>
+      <c r="R14" s="164"/>
+      <c r="S14" s="147"/>
+      <c r="T14" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U14" s="167">
+        <f t="shared" ref="U14:U36" si="4">C14*24+M14*24+O14*24+Q14*24+T14</f>
+        <v>0</v>
+      </c>
+      <c r="V14" s="167">
+        <f t="shared" ref="V14:V36" si="5">U14/24</f>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="60"/>
+      <c r="AG14" s="60"/>
+      <c r="AH14" s="60"/>
+      <c r="AI14" s="60"/>
+      <c r="AJ14" s="60"/>
+      <c r="AK14" s="60"/>
+      <c r="AL14" s="60"/>
+      <c r="AM14" s="60"/>
+      <c r="AN14" s="60"/>
+      <c r="AO14" s="60"/>
+      <c r="AP14" s="60"/>
+      <c r="AQ14" s="60"/>
+      <c r="AR14" s="60"/>
+      <c r="AS14" s="60"/>
+      <c r="AT14" s="60"/>
+      <c r="AU14" s="60"/>
+      <c r="AV14" s="60"/>
+      <c r="AW14" s="60"/>
+      <c r="AX14" s="60"/>
+      <c r="AY14" s="60"/>
+      <c r="AZ14" s="60"/>
+      <c r="BA14" s="60"/>
+      <c r="BB14" s="60"/>
+    </row>
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A15" s="75">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="162"/>
+      <c r="D15" s="162"/>
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="162"/>
+      <c r="H15" s="162"/>
+      <c r="I15" s="162"/>
+      <c r="J15" s="163"/>
+      <c r="K15" s="164"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="166"/>
+      <c r="O15" s="162"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="164"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="60"/>
+      <c r="AG15" s="60"/>
+      <c r="AH15" s="60"/>
+      <c r="AI15" s="60"/>
+      <c r="AJ15" s="60"/>
+      <c r="AK15" s="60"/>
+      <c r="AL15" s="60"/>
+      <c r="AM15" s="60"/>
+      <c r="AN15" s="60"/>
+      <c r="AO15" s="60"/>
+      <c r="AP15" s="60"/>
+      <c r="AQ15" s="60"/>
+      <c r="AR15" s="60"/>
+      <c r="AS15" s="60"/>
+      <c r="AT15" s="60"/>
+      <c r="AU15" s="60"/>
+      <c r="AV15" s="60"/>
+      <c r="AW15" s="60"/>
+      <c r="AX15" s="60"/>
+      <c r="AY15" s="60"/>
+      <c r="AZ15" s="60"/>
+      <c r="BA15" s="60"/>
+      <c r="BB15" s="60"/>
+    </row>
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A16" s="75">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+      <c r="E16" s="162"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="162"/>
+      <c r="H16" s="162"/>
+      <c r="I16" s="162"/>
+      <c r="J16" s="163"/>
+      <c r="K16" s="164"/>
+      <c r="L16" s="147"/>
+      <c r="M16" s="165"/>
+      <c r="N16" s="166"/>
+      <c r="O16" s="162"/>
+      <c r="P16" s="163"/>
+      <c r="Q16" s="163"/>
+      <c r="R16" s="164"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="60"/>
+      <c r="AG16" s="60"/>
+      <c r="AH16" s="60"/>
+      <c r="AI16" s="60"/>
+      <c r="AJ16" s="60"/>
+      <c r="AK16" s="60"/>
+      <c r="AL16" s="60"/>
+      <c r="AM16" s="60"/>
+      <c r="AN16" s="60"/>
+      <c r="AO16" s="60"/>
+      <c r="AP16" s="60"/>
+      <c r="AQ16" s="60"/>
+      <c r="AR16" s="60"/>
+      <c r="AS16" s="60"/>
+      <c r="AT16" s="60"/>
+      <c r="AU16" s="60"/>
+      <c r="AV16" s="60"/>
+      <c r="AW16" s="60"/>
+      <c r="AX16" s="60"/>
+      <c r="AY16" s="60"/>
+      <c r="AZ16" s="60"/>
+      <c r="BA16" s="60"/>
+      <c r="BB16" s="60"/>
+    </row>
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A17" s="75">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+      <c r="E17" s="162"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="162"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="162"/>
+      <c r="J17" s="163"/>
+      <c r="K17" s="164"/>
+      <c r="L17" s="147"/>
+      <c r="M17" s="165"/>
+      <c r="N17" s="166"/>
+      <c r="O17" s="162"/>
+      <c r="P17" s="163"/>
+      <c r="Q17" s="163"/>
+      <c r="R17" s="164"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="60"/>
+      <c r="AN17" s="60"/>
+      <c r="AO17" s="60"/>
+      <c r="AP17" s="60"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="60"/>
+      <c r="AS17" s="60"/>
+      <c r="AT17" s="60"/>
+      <c r="AU17" s="60"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="60"/>
+      <c r="AX17" s="60"/>
+      <c r="AY17" s="60"/>
+      <c r="AZ17" s="60"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="60"/>
+    </row>
+    <row r="18" spans="1:54" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="75">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="162"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="166"/>
+      <c r="O18" s="162"/>
+      <c r="P18" s="163"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="164"/>
+      <c r="S18" s="147"/>
+      <c r="T18" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="60"/>
+      <c r="AG18" s="60"/>
+      <c r="AH18" s="60"/>
+      <c r="AI18" s="60"/>
+      <c r="AJ18" s="60"/>
+      <c r="AK18" s="60"/>
+      <c r="AL18" s="60"/>
+      <c r="AM18" s="60"/>
+      <c r="AN18" s="60"/>
+      <c r="AO18" s="60"/>
+      <c r="AP18" s="60"/>
+      <c r="AQ18" s="60"/>
+      <c r="AR18" s="60"/>
+      <c r="AS18" s="60"/>
+      <c r="AT18" s="60"/>
+      <c r="AU18" s="60"/>
+      <c r="AV18" s="60"/>
+      <c r="AW18" s="60"/>
+      <c r="AX18" s="60"/>
+      <c r="AY18" s="60"/>
+      <c r="AZ18" s="60"/>
+      <c r="BA18" s="60"/>
+      <c r="BB18" s="60"/>
+    </row>
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A19" s="75">
+        <v>16</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="162"/>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="162"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="162"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="163"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="147"/>
+      <c r="M19" s="165"/>
+      <c r="N19" s="166"/>
+      <c r="O19" s="162"/>
+      <c r="P19" s="163"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="164"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
+      <c r="AM19" s="60"/>
+      <c r="AN19" s="60"/>
+      <c r="AO19" s="60"/>
+      <c r="AP19" s="60"/>
+      <c r="AQ19" s="60"/>
+      <c r="AR19" s="60"/>
+      <c r="AS19" s="60"/>
+      <c r="AT19" s="60"/>
+      <c r="AU19" s="60"/>
+      <c r="AV19" s="60"/>
+      <c r="AW19" s="60"/>
+      <c r="AX19" s="60"/>
+      <c r="AY19" s="60"/>
+      <c r="AZ19" s="60"/>
+      <c r="BA19" s="60"/>
+      <c r="BB19" s="60"/>
+    </row>
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A20" s="75">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B20" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="162"/>
+      <c r="D20" s="162"/>
+      <c r="E20" s="162"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="162"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="163"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="147"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="166"/>
+      <c r="O20" s="162"/>
+      <c r="P20" s="163"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="164"/>
+      <c r="S20" s="147"/>
+      <c r="T20" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U20" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="60"/>
+      <c r="AG20" s="60"/>
+      <c r="AH20" s="60"/>
+      <c r="AI20" s="60"/>
+      <c r="AJ20" s="60"/>
+      <c r="AK20" s="60"/>
+      <c r="AL20" s="60"/>
+      <c r="AM20" s="60"/>
+      <c r="AN20" s="60"/>
+      <c r="AO20" s="60"/>
+      <c r="AP20" s="60"/>
+      <c r="AQ20" s="60"/>
+      <c r="AR20" s="60"/>
+      <c r="AS20" s="60"/>
+      <c r="AT20" s="60"/>
+      <c r="AU20" s="60"/>
+      <c r="AV20" s="60"/>
+      <c r="AW20" s="60"/>
+      <c r="AX20" s="60"/>
+      <c r="AY20" s="60"/>
+      <c r="AZ20" s="60"/>
+      <c r="BA20" s="60"/>
+      <c r="BB20" s="60"/>
+    </row>
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A21" s="75">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="162"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="162"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="163"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="147"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="162"/>
+      <c r="P21" s="163"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="164"/>
+      <c r="S21" s="147"/>
+      <c r="T21" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="60"/>
+      <c r="AG21" s="60"/>
+      <c r="AH21" s="60"/>
+      <c r="AI21" s="60"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="60"/>
+      <c r="AR21" s="60"/>
+      <c r="AS21" s="60"/>
+      <c r="AT21" s="60"/>
+      <c r="AU21" s="60"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+    </row>
+    <row r="22" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="75">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="162"/>
+      <c r="D22" s="162"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="162"/>
+      <c r="H22" s="162"/>
+      <c r="I22" s="162"/>
+      <c r="J22" s="163"/>
+      <c r="K22" s="164"/>
+      <c r="L22" s="147"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="166"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="164"/>
+      <c r="S22" s="147"/>
+      <c r="T22" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+      <c r="AA22" s="57"/>
+      <c r="AB22" s="57"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="60"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="60"/>
+      <c r="AI22" s="60"/>
+      <c r="AJ22" s="60"/>
+      <c r="AK22" s="60"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="60"/>
+      <c r="AT22" s="60"/>
+      <c r="AU22" s="60"/>
+      <c r="AV22" s="60"/>
+      <c r="AW22" s="60"/>
+      <c r="AX22" s="60"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+    </row>
+    <row r="23" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="75">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B23" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="162"/>
+      <c r="D23" s="162"/>
+      <c r="E23" s="162"/>
+      <c r="F23" s="162"/>
+      <c r="G23" s="162"/>
+      <c r="H23" s="162"/>
+      <c r="I23" s="162"/>
+      <c r="J23" s="163"/>
+      <c r="K23" s="164"/>
+      <c r="L23" s="147"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="166"/>
+      <c r="O23" s="162"/>
+      <c r="P23" s="163"/>
+      <c r="Q23" s="163"/>
+      <c r="R23" s="164"/>
+      <c r="S23" s="147"/>
+      <c r="T23" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="60"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="60"/>
+      <c r="AI23" s="60"/>
+      <c r="AJ23" s="60"/>
+      <c r="AK23" s="60"/>
+      <c r="AL23" s="60"/>
+      <c r="AM23" s="60"/>
+      <c r="AN23" s="60"/>
+      <c r="AO23" s="60"/>
+      <c r="AP23" s="60"/>
+      <c r="AQ23" s="60"/>
+      <c r="AR23" s="60"/>
+      <c r="AS23" s="60"/>
+      <c r="AT23" s="60"/>
+      <c r="AU23" s="60"/>
+      <c r="AV23" s="60"/>
+      <c r="AW23" s="60"/>
+      <c r="AX23" s="60"/>
+      <c r="AY23" s="60"/>
+      <c r="AZ23" s="60"/>
+      <c r="BA23" s="60"/>
+      <c r="BB23" s="60"/>
+    </row>
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A24" s="75">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="162"/>
+      <c r="D24" s="162"/>
+      <c r="E24" s="162"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="162"/>
+      <c r="H24" s="162"/>
+      <c r="I24" s="162"/>
+      <c r="J24" s="163"/>
+      <c r="K24" s="164"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="165"/>
+      <c r="N24" s="166"/>
+      <c r="O24" s="162"/>
+      <c r="P24" s="163"/>
+      <c r="Q24" s="163"/>
+      <c r="R24" s="164"/>
+      <c r="S24" s="147"/>
+      <c r="T24" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="60"/>
+      <c r="AI24" s="60"/>
+      <c r="AJ24" s="60"/>
+      <c r="AK24" s="60"/>
+      <c r="AL24" s="60"/>
+      <c r="AM24" s="60"/>
+      <c r="AN24" s="60"/>
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="60"/>
+      <c r="AS24" s="60"/>
+      <c r="AT24" s="60"/>
+      <c r="AU24" s="60"/>
+      <c r="AV24" s="60"/>
+      <c r="AW24" s="60"/>
+      <c r="AX24" s="60"/>
+      <c r="AY24" s="60"/>
+      <c r="AZ24" s="60"/>
+      <c r="BA24" s="60"/>
+      <c r="BB24" s="60"/>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A25" s="75">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B25" s="74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="162"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="162"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="162"/>
+      <c r="H25" s="162"/>
+      <c r="I25" s="162"/>
+      <c r="J25" s="163"/>
+      <c r="K25" s="164"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="165"/>
+      <c r="N25" s="166"/>
+      <c r="O25" s="162"/>
+      <c r="P25" s="163"/>
+      <c r="Q25" s="163"/>
+      <c r="R25" s="164"/>
+      <c r="S25" s="147"/>
+      <c r="T25" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY25" s="62" t="e">
+        <f>#REF!-AY24</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="75">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B26" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="162"/>
+      <c r="D26" s="162"/>
+      <c r="E26" s="162"/>
+      <c r="F26" s="162"/>
+      <c r="G26" s="162"/>
+      <c r="H26" s="162"/>
+      <c r="I26" s="162"/>
+      <c r="J26" s="163"/>
+      <c r="K26" s="164"/>
+      <c r="L26" s="147"/>
+      <c r="M26" s="165"/>
+      <c r="N26" s="166"/>
+      <c r="O26" s="162"/>
+      <c r="P26" s="163"/>
+      <c r="Q26" s="163"/>
+      <c r="R26" s="164"/>
+      <c r="S26" s="147"/>
+      <c r="T26" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+    </row>
+    <row r="27" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="75">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="162"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="162"/>
+      <c r="G27" s="162"/>
+      <c r="H27" s="162"/>
+      <c r="I27" s="162"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="164"/>
+      <c r="L27" s="147"/>
+      <c r="M27" s="165"/>
+      <c r="N27" s="166"/>
+      <c r="O27" s="162"/>
+      <c r="P27" s="163"/>
+      <c r="Q27" s="163"/>
+      <c r="R27" s="164"/>
+      <c r="S27" s="147"/>
+      <c r="T27" s="150"/>
+      <c r="U27" s="167"/>
+      <c r="V27" s="167"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+    </row>
+    <row r="28" spans="1:54" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="75">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
+      <c r="E28" s="162"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="162"/>
+      <c r="H28" s="162"/>
+      <c r="I28" s="162"/>
+      <c r="J28" s="163"/>
+      <c r="K28" s="164"/>
+      <c r="L28" s="147"/>
+      <c r="M28" s="165"/>
+      <c r="N28" s="166"/>
+      <c r="O28" s="162"/>
+      <c r="P28" s="163"/>
+      <c r="Q28" s="163"/>
+      <c r="R28" s="164"/>
+      <c r="S28" s="147"/>
+      <c r="T28" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U28" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="57"/>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A29" s="75">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="162"/>
+      <c r="D29" s="162"/>
+      <c r="E29" s="162"/>
+      <c r="F29" s="162"/>
+      <c r="G29" s="162"/>
+      <c r="H29" s="162"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="164"/>
+      <c r="L29" s="147"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="166"/>
+      <c r="O29" s="162"/>
+      <c r="P29" s="163"/>
+      <c r="Q29" s="163"/>
+      <c r="R29" s="164"/>
+      <c r="S29" s="147"/>
+      <c r="T29" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V29" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A30" s="75">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B30" s="74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="162"/>
+      <c r="D30" s="162"/>
+      <c r="E30" s="162"/>
+      <c r="F30" s="162"/>
+      <c r="G30" s="162"/>
+      <c r="H30" s="162"/>
+      <c r="I30" s="162"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="165"/>
+      <c r="N30" s="166"/>
+      <c r="O30" s="162"/>
+      <c r="P30" s="163"/>
+      <c r="Q30" s="163"/>
+      <c r="R30" s="164"/>
+      <c r="S30" s="147"/>
+      <c r="T30" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A31" s="75">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B31" s="74" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="162"/>
+      <c r="D31" s="162"/>
+      <c r="E31" s="162"/>
+      <c r="F31" s="162"/>
+      <c r="G31" s="162"/>
+      <c r="H31" s="162"/>
+      <c r="I31" s="162"/>
+      <c r="J31" s="163"/>
+      <c r="K31" s="164"/>
+      <c r="L31" s="147"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="162"/>
+      <c r="P31" s="163"/>
+      <c r="Q31" s="163"/>
+      <c r="R31" s="164"/>
+      <c r="S31" s="147"/>
+      <c r="T31" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A32" s="75">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B32" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="162"/>
+      <c r="D32" s="162"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="163"/>
+      <c r="K32" s="164"/>
+      <c r="L32" s="147"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="163"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="164"/>
+      <c r="S32" s="147"/>
+      <c r="T32" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B33" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="162"/>
+      <c r="D33" s="162"/>
+      <c r="E33" s="162"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="162"/>
+      <c r="J33" s="163"/>
+      <c r="K33" s="164"/>
+      <c r="L33" s="147"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="166"/>
+      <c r="O33" s="162"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="163"/>
+      <c r="R33" s="164"/>
+      <c r="S33" s="147"/>
+      <c r="T33" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U33" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="75">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B34" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="162"/>
+      <c r="D34" s="162"/>
+      <c r="E34" s="162"/>
+      <c r="F34" s="162"/>
+      <c r="G34" s="162"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="162"/>
+      <c r="J34" s="163"/>
+      <c r="K34" s="164"/>
+      <c r="L34" s="147"/>
+      <c r="M34" s="165"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="162"/>
+      <c r="P34" s="163"/>
+      <c r="Q34" s="163"/>
+      <c r="R34" s="164"/>
+      <c r="S34" s="147"/>
+      <c r="T34" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="75">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B35" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="162"/>
+      <c r="D35" s="162"/>
+      <c r="E35" s="162"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="162"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="162"/>
+      <c r="J35" s="163"/>
+      <c r="K35" s="164"/>
+      <c r="L35" s="147"/>
+      <c r="M35" s="165"/>
+      <c r="N35" s="166"/>
+      <c r="O35" s="162"/>
+      <c r="P35" s="163"/>
+      <c r="Q35" s="163"/>
+      <c r="R35" s="164"/>
+      <c r="S35" s="147"/>
+      <c r="T35" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="75">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B36" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="162"/>
+      <c r="D36" s="162"/>
+      <c r="E36" s="162"/>
+      <c r="F36" s="162"/>
+      <c r="G36" s="162"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="162"/>
+      <c r="J36" s="163"/>
+      <c r="K36" s="164"/>
+      <c r="L36" s="147"/>
+      <c r="M36" s="165"/>
+      <c r="N36" s="166"/>
+      <c r="O36" s="162"/>
+      <c r="P36" s="163"/>
+      <c r="Q36" s="163"/>
+      <c r="R36" s="164"/>
+      <c r="S36" s="147"/>
+      <c r="T36" s="150">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="167">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="75">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B37" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="151"/>
+      <c r="D37" s="151"/>
+      <c r="E37" s="151"/>
+      <c r="F37" s="151"/>
+      <c r="G37" s="151"/>
+      <c r="H37" s="151"/>
+      <c r="I37" s="151"/>
+      <c r="J37" s="152"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="157"/>
+      <c r="P37" s="158"/>
+      <c r="Q37" s="158"/>
+      <c r="R37" s="159"/>
+      <c r="S37" s="154"/>
+      <c r="T37" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="169">
+        <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
+        <v>0</v>
+      </c>
+      <c r="V37" s="169">
+        <f>U37/6</f>
+        <v>0</v>
+      </c>
+      <c r="W37" s="123"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="75">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="162"/>
+      <c r="D38" s="162"/>
+      <c r="E38" s="162"/>
+      <c r="F38" s="162"/>
+      <c r="G38" s="162"/>
+      <c r="H38" s="162"/>
+      <c r="I38" s="162"/>
+      <c r="J38" s="163"/>
+      <c r="K38" s="164"/>
+      <c r="L38" s="147"/>
+      <c r="M38" s="165"/>
+      <c r="N38" s="166"/>
+      <c r="O38" s="162"/>
+      <c r="P38" s="163"/>
+      <c r="Q38" s="163"/>
+      <c r="R38" s="164"/>
+      <c r="S38" s="147"/>
+      <c r="T38" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="167">
+        <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
+        <v>0</v>
+      </c>
+      <c r="V38" s="167">
+        <f>U38/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="75">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="170"/>
+      <c r="D39" s="170"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="170"/>
+      <c r="H39" s="170"/>
+      <c r="I39" s="170"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="147"/>
+      <c r="M39" s="173"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="170"/>
+      <c r="P39" s="171"/>
+      <c r="Q39" s="171"/>
+      <c r="R39" s="172"/>
+      <c r="S39" s="147"/>
+      <c r="T39" s="175"/>
+      <c r="U39" s="175"/>
+      <c r="V39" s="175"/>
+    </row>
+    <row r="40" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="75">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B40" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="151"/>
+      <c r="I40" s="151"/>
+      <c r="J40" s="152"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="154"/>
+      <c r="M40" s="155"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="157"/>
+      <c r="P40" s="158"/>
+      <c r="Q40" s="158"/>
+      <c r="R40" s="159"/>
+      <c r="S40" s="154"/>
+      <c r="T40" s="169">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U40" s="169">
+        <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
+        <v>0</v>
+      </c>
+      <c r="V40" s="169">
+        <f>U40/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="75">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B41" s="99" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="176"/>
+      <c r="D41" s="176"/>
+      <c r="E41" s="176"/>
+      <c r="F41" s="176"/>
+      <c r="G41" s="176"/>
+      <c r="H41" s="176"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="177"/>
+      <c r="K41" s="178"/>
+      <c r="L41" s="179"/>
+      <c r="M41" s="180"/>
+      <c r="N41" s="181"/>
+      <c r="O41" s="176"/>
+      <c r="P41" s="177"/>
+      <c r="Q41" s="177"/>
+      <c r="R41" s="178"/>
+      <c r="S41" s="179"/>
+      <c r="T41" s="182">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U41" s="182">
+        <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
+        <v>0</v>
+      </c>
+      <c r="V41" s="182">
+        <f>U41/12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="75">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B42" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="162"/>
+      <c r="D42" s="162"/>
+      <c r="E42" s="162"/>
+      <c r="F42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="162"/>
+      <c r="I42" s="162"/>
+      <c r="J42" s="163"/>
+      <c r="K42" s="164"/>
+      <c r="L42" s="147"/>
+      <c r="M42" s="165"/>
+      <c r="N42" s="166"/>
+      <c r="O42" s="162"/>
+      <c r="P42" s="163"/>
+      <c r="Q42" s="163"/>
+      <c r="R42" s="164"/>
+      <c r="S42" s="147"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+    </row>
+    <row r="43" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="75">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B43" s="94" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="157"/>
+      <c r="D43" s="157"/>
+      <c r="E43" s="157"/>
+      <c r="F43" s="157"/>
+      <c r="G43" s="157"/>
+      <c r="H43" s="157"/>
+      <c r="I43" s="157"/>
+      <c r="J43" s="158"/>
+      <c r="K43" s="159"/>
+      <c r="L43" s="154"/>
+      <c r="M43" s="155"/>
+      <c r="N43" s="156"/>
+      <c r="O43" s="157"/>
+      <c r="P43" s="158"/>
+      <c r="Q43" s="158"/>
+      <c r="R43" s="159"/>
+      <c r="S43" s="154"/>
+      <c r="T43" s="169">
+        <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="169">
+        <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
+        <v>0</v>
+      </c>
+      <c r="V43" s="169">
+        <f>U43/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="75">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B44" s="73" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="162"/>
+      <c r="D44" s="162"/>
+      <c r="E44" s="162"/>
+      <c r="F44" s="162"/>
+      <c r="G44" s="162"/>
+      <c r="H44" s="162"/>
+      <c r="I44" s="162"/>
+      <c r="J44" s="163"/>
+      <c r="K44" s="164"/>
+      <c r="L44" s="147"/>
+      <c r="M44" s="165"/>
+      <c r="N44" s="166"/>
+      <c r="O44" s="162"/>
+      <c r="P44" s="163"/>
+      <c r="Q44" s="163"/>
+      <c r="R44" s="164"/>
+      <c r="S44" s="147"/>
+      <c r="T44" s="167"/>
+      <c r="U44" s="167"/>
+      <c r="V44" s="167"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B45" s="74" t="s">
+        <v>25</v>
+      </c>
+      <c r="C45" s="162"/>
+      <c r="D45" s="162"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="162"/>
+      <c r="G45" s="162"/>
+      <c r="H45" s="162"/>
+      <c r="I45" s="162"/>
+      <c r="J45" s="163"/>
+      <c r="K45" s="164"/>
+      <c r="L45" s="147"/>
+      <c r="M45" s="165"/>
+      <c r="N45" s="166"/>
+      <c r="O45" s="162"/>
+      <c r="P45" s="163"/>
+      <c r="Q45" s="163"/>
+      <c r="R45" s="164"/>
+      <c r="S45" s="147"/>
+      <c r="T45" s="167">
+        <f t="shared" ref="T45:T54" si="7">H45+I45+J45+K45+N45+P45+R45</f>
+        <v>0</v>
+      </c>
+      <c r="U45" s="167">
+        <f>C45*24+M45*24+O45*24+Q45*24+T45</f>
+        <v>0</v>
+      </c>
+      <c r="V45" s="167">
+        <f>U45/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="75">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B46" s="74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="162"/>
+      <c r="D46" s="162"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="162"/>
+      <c r="G46" s="162"/>
+      <c r="H46" s="162"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="163"/>
+      <c r="K46" s="164"/>
+      <c r="L46" s="147"/>
+      <c r="M46" s="165"/>
+      <c r="N46" s="166"/>
+      <c r="O46" s="162"/>
+      <c r="P46" s="163"/>
+      <c r="Q46" s="163"/>
+      <c r="R46" s="164"/>
+      <c r="S46" s="147"/>
+      <c r="T46" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="167">
+        <f t="shared" ref="U46:U50" si="8">C46*24+M46*24+O46*24+Q46*24+T46</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="167">
+        <f t="shared" ref="V46:V54" si="9">U46/24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="75">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B47" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="157"/>
+      <c r="D47" s="157"/>
+      <c r="E47" s="157"/>
+      <c r="F47" s="157"/>
+      <c r="G47" s="157"/>
+      <c r="H47" s="157"/>
+      <c r="I47" s="157"/>
+      <c r="J47" s="158"/>
+      <c r="K47" s="159"/>
+      <c r="L47" s="154"/>
+      <c r="M47" s="155"/>
+      <c r="N47" s="156"/>
+      <c r="O47" s="157"/>
+      <c r="P47" s="158"/>
+      <c r="Q47" s="158"/>
+      <c r="R47" s="159"/>
+      <c r="S47" s="154"/>
+      <c r="T47" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="169">
+        <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
+        <v>0</v>
+      </c>
+      <c r="V47" s="169">
+        <f>U47/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="75">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B48" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="162"/>
+      <c r="D48" s="162"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="162"/>
+      <c r="G48" s="162"/>
+      <c r="H48" s="162"/>
+      <c r="I48" s="162"/>
+      <c r="J48" s="163"/>
+      <c r="K48" s="164"/>
+      <c r="L48" s="147"/>
+      <c r="M48" s="165"/>
+      <c r="N48" s="166"/>
+      <c r="O48" s="162"/>
+      <c r="P48" s="163"/>
+      <c r="Q48" s="163"/>
+      <c r="R48" s="164"/>
+      <c r="S48" s="147"/>
+      <c r="T48" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U48" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="75">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B49" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="162"/>
+      <c r="D49" s="162"/>
+      <c r="E49" s="162"/>
+      <c r="F49" s="162"/>
+      <c r="G49" s="162"/>
+      <c r="H49" s="162"/>
+      <c r="I49" s="162"/>
+      <c r="J49" s="163"/>
+      <c r="K49" s="164"/>
+      <c r="L49" s="147"/>
+      <c r="M49" s="165"/>
+      <c r="N49" s="166"/>
+      <c r="O49" s="162"/>
+      <c r="P49" s="163"/>
+      <c r="Q49" s="163"/>
+      <c r="R49" s="164"/>
+      <c r="S49" s="147"/>
+      <c r="T49" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U49" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="75">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B50" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="162"/>
+      <c r="D50" s="162"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="162"/>
+      <c r="G50" s="162"/>
+      <c r="H50" s="162"/>
+      <c r="I50" s="162"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="164"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="165"/>
+      <c r="N50" s="166"/>
+      <c r="O50" s="162"/>
+      <c r="P50" s="163"/>
+      <c r="Q50" s="163"/>
+      <c r="R50" s="164"/>
+      <c r="S50" s="147"/>
+      <c r="T50" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U50" s="167">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="75">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="B51" s="94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="157"/>
+      <c r="D51" s="157"/>
+      <c r="E51" s="157"/>
+      <c r="F51" s="157"/>
+      <c r="G51" s="157"/>
+      <c r="H51" s="157"/>
+      <c r="I51" s="157"/>
+      <c r="J51" s="158"/>
+      <c r="K51" s="159"/>
+      <c r="L51" s="154"/>
+      <c r="M51" s="155"/>
+      <c r="N51" s="156"/>
+      <c r="O51" s="157"/>
+      <c r="P51" s="158"/>
+      <c r="Q51" s="158"/>
+      <c r="R51" s="159"/>
+      <c r="S51" s="154"/>
+      <c r="T51" s="169">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U51" s="169">
+        <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
+        <v>0</v>
+      </c>
+      <c r="V51" s="169">
+        <f>U51/6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" s="75">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B52" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="162"/>
+      <c r="D52" s="162"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="162"/>
+      <c r="G52" s="162"/>
+      <c r="H52" s="162"/>
+      <c r="I52" s="162"/>
+      <c r="J52" s="163"/>
+      <c r="K52" s="164"/>
+      <c r="L52" s="147"/>
+      <c r="M52" s="165"/>
+      <c r="N52" s="166"/>
+      <c r="O52" s="162"/>
+      <c r="P52" s="163"/>
+      <c r="Q52" s="163"/>
+      <c r="R52" s="164"/>
+      <c r="S52" s="147"/>
+      <c r="T52" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="167">
+        <f t="shared" ref="U52:U54" si="10">C52*24+M52*24+O52*24+Q52*24+T52</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B53" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="162"/>
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="162"/>
+      <c r="H53" s="162"/>
+      <c r="I53" s="162"/>
+      <c r="J53" s="163"/>
+      <c r="K53" s="164"/>
+      <c r="L53" s="147"/>
+      <c r="M53" s="165"/>
+      <c r="N53" s="166"/>
+      <c r="O53" s="162"/>
+      <c r="P53" s="163"/>
+      <c r="Q53" s="163"/>
+      <c r="R53" s="164"/>
+      <c r="S53" s="147"/>
+      <c r="T53" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U53" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V53" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B54" s="74"/>
+      <c r="C54" s="162"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="162"/>
+      <c r="G54" s="162"/>
+      <c r="H54" s="162"/>
+      <c r="I54" s="162"/>
+      <c r="J54" s="163"/>
+      <c r="K54" s="164"/>
+      <c r="L54" s="147"/>
+      <c r="M54" s="165"/>
+      <c r="N54" s="166"/>
+      <c r="O54" s="162"/>
+      <c r="P54" s="163"/>
+      <c r="Q54" s="163"/>
+      <c r="R54" s="164"/>
+      <c r="S54" s="147"/>
+      <c r="T54" s="167">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U54" s="167">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="167">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B55" s="74"/>
+      <c r="C55" s="162"/>
+      <c r="D55" s="162"/>
+      <c r="E55" s="162"/>
+      <c r="F55" s="162"/>
+      <c r="G55" s="162"/>
+      <c r="H55" s="162"/>
+      <c r="I55" s="162"/>
+      <c r="J55" s="163"/>
+      <c r="K55" s="164"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="165"/>
+      <c r="N55" s="166"/>
+      <c r="O55" s="162"/>
+      <c r="P55" s="163"/>
+      <c r="Q55" s="163"/>
+      <c r="R55" s="164"/>
+      <c r="S55" s="147"/>
+      <c r="T55" s="167"/>
+      <c r="U55" s="167"/>
+      <c r="V55" s="167"/>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B56" s="74"/>
+      <c r="C56" s="162"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="162"/>
+      <c r="F56" s="162"/>
+      <c r="G56" s="162"/>
+      <c r="H56" s="162"/>
+      <c r="I56" s="162"/>
+      <c r="J56" s="163"/>
+      <c r="K56" s="164"/>
+      <c r="L56" s="147"/>
+      <c r="M56" s="165"/>
+      <c r="N56" s="166"/>
+      <c r="O56" s="162"/>
+      <c r="P56" s="163"/>
+      <c r="Q56" s="163"/>
+      <c r="R56" s="164"/>
+      <c r="S56" s="147"/>
+      <c r="T56" s="167"/>
+      <c r="U56" s="167"/>
+      <c r="V56" s="167"/>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B57" s="74"/>
+      <c r="C57" s="162"/>
+      <c r="D57" s="162"/>
+      <c r="E57" s="162"/>
+      <c r="F57" s="162"/>
+      <c r="G57" s="162"/>
+      <c r="H57" s="162"/>
+      <c r="I57" s="162"/>
+      <c r="J57" s="163"/>
+      <c r="K57" s="164"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="165"/>
+      <c r="N57" s="166"/>
+      <c r="O57" s="162"/>
+      <c r="P57" s="163"/>
+      <c r="Q57" s="163"/>
+      <c r="R57" s="164"/>
+      <c r="S57" s="147"/>
+      <c r="T57" s="167"/>
+      <c r="U57" s="167"/>
+      <c r="V57" s="167"/>
+    </row>
+    <row r="58" spans="1:22" s="63" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58" s="49">
+        <f>SUM(C7:C57)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49">
+        <f t="shared" ref="F58:K58" si="11">SUM(F7:F57)</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="54">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="53">
+        <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
+        <v>0</v>
+      </c>
+      <c r="N58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="53">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="147"/>
+      <c r="T58" s="51">
+        <f>SUM(T7:T57)</f>
+        <v>0</v>
+      </c>
+      <c r="U58" s="51">
+        <f>SUM(U7:U57)</f>
+        <v>0</v>
+      </c>
+      <c r="V58" s="51">
+        <f>SUM(V7:V57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="C60" s="195" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="196"/>
+      <c r="E60" s="196"/>
+      <c r="F60" s="196"/>
+      <c r="G60" s="196"/>
+      <c r="H60" s="196"/>
+      <c r="I60" s="196"/>
+      <c r="J60" s="196"/>
+      <c r="K60" s="197"/>
       <c r="U60" s="72" t="s">
         <v>62</v>
       </c>
@@ -50894,21 +54007,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -50920,17 +54033,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -50950,13 +54063,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -50996,10 +54109,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -51007,9 +54120,9 @@
       <c r="Q5" s="127"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -53614,17 +56727,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -53933,21 +57046,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -53959,17 +57072,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -53989,13 +57102,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -54035,10 +57148,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -54046,9 +57159,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -56646,17 +59759,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -56965,21 +60078,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -56991,17 +60104,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -57021,13 +60134,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -57067,10 +60180,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -57078,9 +60191,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -59687,17 +62800,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -60006,21 +63119,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -60032,17 +63145,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -60062,13 +63175,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -60108,10 +63221,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -60119,9 +63232,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -62721,17 +65834,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -63040,21 +66153,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -63066,17 +66179,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -63096,13 +66209,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -63142,10 +66255,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -63153,9 +66266,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -65737,17 +68850,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -66056,21 +69169,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -66082,17 +69195,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -66112,13 +69225,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -66158,10 +69271,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -66169,9 +69282,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -68751,17 +71864,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>
@@ -69070,21 +72183,21 @@
       <c r="B1" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="I1" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="197"/>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="197"/>
-      <c r="T1" s="197"/>
-      <c r="U1" s="197"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="198"/>
+      <c r="P1" s="198"/>
+      <c r="Q1" s="198"/>
+      <c r="R1" s="198"/>
+      <c r="S1" s="198"/>
+      <c r="T1" s="198"/>
+      <c r="U1" s="198"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="B2" s="76" t="s">
@@ -69096,17 +72209,17 @@
       <c r="B4" s="93" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="193" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="192"/>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="203"/>
+      <c r="K4" s="194"/>
       <c r="M4" s="82" t="s">
         <v>0</v>
       </c>
@@ -69126,13 +72239,13 @@
         <v>72</v>
       </c>
       <c r="S4" s="57"/>
-      <c r="T4" s="203" t="s">
+      <c r="T4" s="204" t="s">
         <v>80</v>
       </c>
-      <c r="U4" s="205" t="s">
+      <c r="U4" s="206" t="s">
         <v>79</v>
       </c>
-      <c r="V4" s="198" t="s">
+      <c r="V4" s="199" t="s">
         <v>78</v>
       </c>
       <c r="AF4" s="59"/>
@@ -69172,10 +72285,10 @@
       <c r="I5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="J5" s="200" t="s">
+      <c r="J5" s="201" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="201"/>
+      <c r="K5" s="202"/>
       <c r="M5" s="87"/>
       <c r="N5" s="118"/>
       <c r="O5" s="92"/>
@@ -69183,9 +72296,9 @@
       <c r="Q5" s="128"/>
       <c r="R5" s="89"/>
       <c r="S5" s="57"/>
-      <c r="T5" s="204"/>
-      <c r="U5" s="206"/>
-      <c r="V5" s="199"/>
+      <c r="T5" s="205"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="200"/>
       <c r="AF5" s="59"/>
       <c r="AG5" s="59"/>
       <c r="AH5" s="59"/>
@@ -71772,17 +74885,17 @@
       <c r="B59" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="C59" s="194" t="s">
+      <c r="C59" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D59" s="195"/>
-      <c r="E59" s="195"/>
-      <c r="F59" s="195"/>
-      <c r="G59" s="195"/>
-      <c r="H59" s="195"/>
-      <c r="I59" s="195"/>
-      <c r="J59" s="195"/>
-      <c r="K59" s="196"/>
+      <c r="D59" s="196"/>
+      <c r="E59" s="196"/>
+      <c r="F59" s="196"/>
+      <c r="G59" s="196"/>
+      <c r="H59" s="196"/>
+      <c r="I59" s="196"/>
+      <c r="J59" s="196"/>
+      <c r="K59" s="197"/>
       <c r="U59" s="72" t="s">
         <v>62</v>
       </c>

--- a/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/INVENTORY COUNT SHEET - February 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEAC8A7-9CDA-4CE8-9378-ECCCDBEA4D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEB81FC-EE67-4E37-9DFA-342BDC887306}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="15" activeTab="23" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="15" activeTab="24" xr2:uid="{D34C963E-9680-4B45-A4EE-B681FF0CEC08}"/>
   </bookViews>
   <sheets>
     <sheet name="COUNT SHEET" sheetId="9" r:id="rId1"/>
@@ -51278,34 +51278,48 @@
       <c r="B7" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="144"/>
+      <c r="C7" s="144">
+        <v>23</v>
+      </c>
       <c r="D7" s="144"/>
       <c r="E7" s="144"/>
       <c r="F7" s="144"/>
       <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="144"/>
+      <c r="H7" s="144">
+        <v>5</v>
+      </c>
+      <c r="I7" s="144">
+        <v>1</v>
+      </c>
       <c r="J7" s="145"/>
-      <c r="K7" s="146"/>
+      <c r="K7" s="146">
+        <v>6</v>
+      </c>
       <c r="L7" s="147"/>
       <c r="M7" s="148"/>
       <c r="N7" s="149"/>
-      <c r="O7" s="144"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
+      <c r="O7" s="144">
+        <v>2</v>
+      </c>
+      <c r="P7" s="145">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="145">
+        <v>2</v>
+      </c>
       <c r="R7" s="146"/>
       <c r="S7" s="147"/>
       <c r="T7" s="150">
         <f>H7+I7+J7+K7+N7+P7+R7</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U7" s="150">
         <f>C7*24+M7*24+O7*24+Q7*24+T7</f>
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="V7" s="150">
         <f>U7/24</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W7" s="123"/>
       <c r="AF7" s="60"/>
@@ -51340,7 +51354,10 @@
       <c r="B8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="151"/>
+      <c r="C8" s="151">
+        <f>63+26</f>
+        <v>89</v>
+      </c>
       <c r="D8" s="151"/>
       <c r="E8" s="151"/>
       <c r="F8" s="151"/>
@@ -51350,7 +51367,9 @@
       <c r="J8" s="152"/>
       <c r="K8" s="153"/>
       <c r="L8" s="154"/>
-      <c r="M8" s="155"/>
+      <c r="M8" s="155">
+        <v>1</v>
+      </c>
       <c r="N8" s="156"/>
       <c r="O8" s="157"/>
       <c r="P8" s="158"/>
@@ -51363,11 +51382,11 @@
       </c>
       <c r="U8" s="161">
         <f>C8*24+M8*24+O8*24+Q8*24+T8</f>
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="V8" s="161">
         <f>U8/24</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W8" s="123"/>
       <c r="AF8" s="60"/>
@@ -51402,7 +51421,9 @@
       <c r="B9" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="162"/>
+      <c r="C9" s="162">
+        <v>10</v>
+      </c>
       <c r="D9" s="162"/>
       <c r="E9" s="162"/>
       <c r="F9" s="162"/>
@@ -51414,7 +51435,9 @@
       <c r="L9" s="147"/>
       <c r="M9" s="165"/>
       <c r="N9" s="166"/>
-      <c r="O9" s="162"/>
+      <c r="O9" s="162">
+        <v>1</v>
+      </c>
       <c r="P9" s="163"/>
       <c r="Q9" s="163"/>
       <c r="R9" s="164"/>
@@ -51425,11 +51448,11 @@
       </c>
       <c r="U9" s="168">
         <f t="shared" ref="U9:U11" si="2">C9*24+M9*24+O9*24+Q9*24+T9</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="V9" s="168">
         <f t="shared" ref="V9:V11" si="3">U9/24</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" s="123"/>
       <c r="AF9" s="60"/>
@@ -51464,7 +51487,9 @@
       <c r="B10" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="162"/>
+      <c r="C10" s="162">
+        <v>42</v>
+      </c>
       <c r="D10" s="162"/>
       <c r="E10" s="162"/>
       <c r="F10" s="162"/>
@@ -51487,11 +51512,11 @@
       </c>
       <c r="U10" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="V10" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W10" s="123"/>
       <c r="AF10" s="60"/>
@@ -51531,10 +51556,14 @@
       <c r="E11" s="162"/>
       <c r="F11" s="162"/>
       <c r="G11" s="162"/>
-      <c r="H11" s="162"/>
+      <c r="H11" s="162">
+        <v>22</v>
+      </c>
       <c r="I11" s="162"/>
       <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="K11" s="164">
+        <v>2</v>
+      </c>
       <c r="L11" s="147"/>
       <c r="M11" s="165"/>
       <c r="N11" s="166"/>
@@ -51545,15 +51574,15 @@
       <c r="S11" s="147"/>
       <c r="T11" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U11" s="150">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" s="150">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="60"/>
       <c r="AG11" s="60"/>
@@ -51586,7 +51615,10 @@
       <c r="B12" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="151"/>
+      <c r="C12" s="151">
+        <f>72+1080+23+1440+576</f>
+        <v>3191</v>
+      </c>
       <c r="D12" s="151"/>
       <c r="E12" s="151"/>
       <c r="F12" s="151"/>
@@ -51596,24 +51628,36 @@
       <c r="J12" s="152"/>
       <c r="K12" s="153"/>
       <c r="L12" s="154"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="157"/>
-      <c r="P12" s="158"/>
-      <c r="Q12" s="158"/>
-      <c r="R12" s="159"/>
+      <c r="M12" s="155">
+        <v>16</v>
+      </c>
+      <c r="N12" s="156">
+        <v>18</v>
+      </c>
+      <c r="O12" s="157">
+        <v>7</v>
+      </c>
+      <c r="P12" s="158">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="158">
+        <v>15</v>
+      </c>
+      <c r="R12" s="159">
+        <v>4</v>
+      </c>
       <c r="S12" s="154"/>
       <c r="T12" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U12" s="161">
         <f>C12*24+M12*24+O12*24+Q12*24+T12</f>
-        <v>0</v>
+        <v>77521</v>
       </c>
       <c r="V12" s="161">
         <f>U12/24</f>
-        <v>0</v>
+        <v>3230.0416666666665</v>
       </c>
       <c r="W12" s="57"/>
       <c r="X12" s="57"/>
@@ -51655,7 +51699,9 @@
       <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="162"/>
+      <c r="C13" s="162">
+        <v>5</v>
+      </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
       <c r="F13" s="162"/>
@@ -51678,11 +51724,11 @@
       </c>
       <c r="U13" s="168">
         <f>C13*24+M13*24+O13*24+Q13*24+T13</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V13" s="168">
         <f>U13/24</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF13" s="60"/>
       <c r="AG13" s="60"/>
@@ -51899,7 +51945,9 @@
       <c r="B17" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="162"/>
+      <c r="C17" s="162">
+        <v>4</v>
+      </c>
       <c r="D17" s="162"/>
       <c r="E17" s="162"/>
       <c r="F17" s="162"/>
@@ -51922,11 +51970,11 @@
       </c>
       <c r="U17" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V17" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17" s="60"/>
       <c r="AG17" s="60"/>
@@ -52020,7 +52068,9 @@
       <c r="B19" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="162"/>
+      <c r="C19" s="162">
+        <v>4</v>
+      </c>
       <c r="D19" s="162"/>
       <c r="E19" s="162"/>
       <c r="F19" s="162"/>
@@ -52043,11 +52093,11 @@
       </c>
       <c r="U19" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V19" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF19" s="60"/>
       <c r="AG19" s="60"/>
@@ -52081,7 +52131,9 @@
       <c r="B20" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="162"/>
+      <c r="C20" s="162">
+        <v>6</v>
+      </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
       <c r="F20" s="162"/>
@@ -52104,11 +52156,11 @@
       </c>
       <c r="U20" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="V20" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF20" s="60"/>
       <c r="AG20" s="60"/>
@@ -52142,7 +52194,9 @@
       <c r="B21" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="162"/>
+      <c r="C21" s="162">
+        <v>4</v>
+      </c>
       <c r="D21" s="162"/>
       <c r="E21" s="162"/>
       <c r="F21" s="162"/>
@@ -52165,11 +52219,11 @@
       </c>
       <c r="U21" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V21" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF21" s="60"/>
       <c r="AG21" s="60"/>
@@ -52203,7 +52257,9 @@
       <c r="B22" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="162"/>
+      <c r="C22" s="162">
+        <v>2</v>
+      </c>
       <c r="D22" s="162"/>
       <c r="E22" s="162"/>
       <c r="F22" s="162"/>
@@ -52226,11 +52282,11 @@
       </c>
       <c r="U22" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V22" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" s="57"/>
       <c r="X22" s="57"/>
@@ -52273,7 +52329,9 @@
       <c r="B23" s="74" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="162"/>
+      <c r="C23" s="162">
+        <v>42</v>
+      </c>
       <c r="D23" s="162"/>
       <c r="E23" s="162"/>
       <c r="F23" s="162"/>
@@ -52283,11 +52341,17 @@
       <c r="J23" s="163"/>
       <c r="K23" s="164"/>
       <c r="L23" s="147"/>
-      <c r="M23" s="165"/>
+      <c r="M23" s="165">
+        <v>2</v>
+      </c>
       <c r="N23" s="166"/>
-      <c r="O23" s="162"/>
+      <c r="O23" s="162">
+        <v>1</v>
+      </c>
       <c r="P23" s="163"/>
-      <c r="Q23" s="163"/>
+      <c r="Q23" s="163">
+        <v>2</v>
+      </c>
       <c r="R23" s="164"/>
       <c r="S23" s="147"/>
       <c r="T23" s="150">
@@ -52296,11 +52360,11 @@
       </c>
       <c r="U23" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V23" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="W23" s="57"/>
       <c r="X23" s="57"/>
@@ -52343,7 +52407,9 @@
       <c r="B24" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="162"/>
+      <c r="C24" s="162">
+        <v>7</v>
+      </c>
       <c r="D24" s="162"/>
       <c r="E24" s="162"/>
       <c r="F24" s="162"/>
@@ -52366,11 +52432,11 @@
       </c>
       <c r="U24" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="V24" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF24" s="60"/>
       <c r="AG24" s="60"/>
@@ -52404,34 +52470,44 @@
       <c r="B25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="162"/>
+      <c r="C25" s="162">
+        <v>63</v>
+      </c>
       <c r="D25" s="162"/>
       <c r="E25" s="162"/>
       <c r="F25" s="162"/>
       <c r="G25" s="162"/>
-      <c r="H25" s="162"/>
-      <c r="I25" s="162"/>
+      <c r="H25" s="162">
+        <v>10</v>
+      </c>
+      <c r="I25" s="162">
+        <v>1</v>
+      </c>
       <c r="J25" s="163"/>
       <c r="K25" s="164"/>
       <c r="L25" s="147"/>
-      <c r="M25" s="165"/>
+      <c r="M25" s="165">
+        <v>1</v>
+      </c>
       <c r="N25" s="166"/>
       <c r="O25" s="162"/>
       <c r="P25" s="163"/>
-      <c r="Q25" s="163"/>
+      <c r="Q25" s="163">
+        <v>10</v>
+      </c>
       <c r="R25" s="164"/>
       <c r="S25" s="147"/>
       <c r="T25" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U25" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1787</v>
       </c>
       <c r="V25" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>74.458333333333329</v>
       </c>
       <c r="AY25" s="62" t="e">
         <f>#REF!-AY24</f>
@@ -52531,7 +52607,10 @@
       <c r="B28" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="162"/>
+      <c r="C28" s="162">
+        <f>64+43</f>
+        <v>107</v>
+      </c>
       <c r="D28" s="162"/>
       <c r="E28" s="162"/>
       <c r="F28" s="162"/>
@@ -52543,9 +52622,13 @@
       <c r="L28" s="147"/>
       <c r="M28" s="165"/>
       <c r="N28" s="166"/>
-      <c r="O28" s="162"/>
+      <c r="O28" s="162">
+        <v>2</v>
+      </c>
       <c r="P28" s="163"/>
-      <c r="Q28" s="163"/>
+      <c r="Q28" s="163">
+        <v>20</v>
+      </c>
       <c r="R28" s="164"/>
       <c r="S28" s="147"/>
       <c r="T28" s="150">
@@ -52554,11 +52637,11 @@
       </c>
       <c r="U28" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3096</v>
       </c>
       <c r="V28" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="W28" s="57"/>
       <c r="X28" s="57"/>
@@ -52616,7 +52699,9 @@
       <c r="B30" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="162"/>
+      <c r="C30" s="162">
+        <v>58</v>
+      </c>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
       <c r="F30" s="162"/>
@@ -52628,9 +52713,13 @@
       <c r="L30" s="147"/>
       <c r="M30" s="165"/>
       <c r="N30" s="166"/>
-      <c r="O30" s="162"/>
+      <c r="O30" s="162">
+        <v>2</v>
+      </c>
       <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
+      <c r="Q30" s="163">
+        <v>1</v>
+      </c>
       <c r="R30" s="164"/>
       <c r="S30" s="147"/>
       <c r="T30" s="150">
@@ -52639,11 +52728,11 @@
       </c>
       <c r="U30" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="V30" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:54" x14ac:dyDescent="0.25">
@@ -52654,7 +52743,9 @@
       <c r="B31" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="162"/>
+      <c r="C31" s="162">
+        <v>4</v>
+      </c>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
       <c r="F31" s="162"/>
@@ -52666,7 +52757,9 @@
       <c r="L31" s="147"/>
       <c r="M31" s="165"/>
       <c r="N31" s="166"/>
-      <c r="O31" s="162"/>
+      <c r="O31" s="162">
+        <v>1</v>
+      </c>
       <c r="P31" s="163"/>
       <c r="Q31" s="163"/>
       <c r="R31" s="164"/>
@@ -52677,11 +52770,11 @@
       </c>
       <c r="U31" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="V31" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
@@ -52768,34 +52861,49 @@
       <c r="B34" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="162"/>
+      <c r="C34" s="162">
+        <f>9+72+72</f>
+        <v>153</v>
+      </c>
       <c r="D34" s="162"/>
       <c r="E34" s="162"/>
       <c r="F34" s="162"/>
       <c r="G34" s="162"/>
-      <c r="H34" s="162"/>
+      <c r="H34" s="162">
+        <v>4</v>
+      </c>
       <c r="I34" s="162"/>
       <c r="J34" s="163"/>
-      <c r="K34" s="164"/>
+      <c r="K34" s="164">
+        <v>1</v>
+      </c>
       <c r="L34" s="147"/>
       <c r="M34" s="165"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="163"/>
+      <c r="N34" s="166">
+        <v>12</v>
+      </c>
+      <c r="O34" s="162">
+        <v>2</v>
+      </c>
+      <c r="P34" s="163">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="163">
+        <v>3</v>
+      </c>
       <c r="R34" s="164"/>
       <c r="S34" s="147"/>
       <c r="T34" s="150">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="U34" s="167">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3821</v>
       </c>
       <c r="V34" s="167">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>159.20833333333334</v>
       </c>
     </row>
     <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -52882,34 +52990,47 @@
       <c r="B37" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C37" s="151"/>
+      <c r="C37" s="151">
+        <f>698+2376+864+756</f>
+        <v>4694</v>
+      </c>
       <c r="D37" s="151"/>
       <c r="E37" s="151"/>
       <c r="F37" s="151"/>
       <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
+      <c r="H37" s="151">
+        <v>2</v>
+      </c>
       <c r="I37" s="151"/>
       <c r="J37" s="152"/>
-      <c r="K37" s="153"/>
+      <c r="K37" s="153">
+        <v>6</v>
+      </c>
       <c r="L37" s="154"/>
-      <c r="M37" s="155"/>
+      <c r="M37" s="155">
+        <v>110</v>
+      </c>
       <c r="N37" s="156"/>
-      <c r="O37" s="157"/>
+      <c r="O37" s="157">
+        <v>15</v>
+      </c>
       <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
+      <c r="Q37" s="158">
+        <v>109</v>
+      </c>
       <c r="R37" s="159"/>
       <c r="S37" s="154"/>
       <c r="T37" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U37" s="169">
         <f>C37*6+M37*6+O37*6+Q37*6+T37</f>
-        <v>0</v>
+        <v>29576</v>
       </c>
       <c r="V37" s="169">
         <f>U37/6</f>
-        <v>0</v>
+        <v>4929.333333333333</v>
       </c>
       <c r="W37" s="123"/>
     </row>
@@ -52921,7 +53042,10 @@
       <c r="B38" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="162"/>
+      <c r="C38" s="162">
+        <f>2+2</f>
+        <v>4</v>
+      </c>
       <c r="D38" s="162"/>
       <c r="E38" s="162"/>
       <c r="F38" s="162"/>
@@ -52944,11 +53068,11 @@
       </c>
       <c r="U38" s="167">
         <f>C38*24+M38*24+O38*24+Q38*24+T38</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="V38" s="167">
         <f>U38/24</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
@@ -52988,34 +53112,49 @@
       <c r="B40" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="151"/>
+      <c r="C40" s="151">
+        <f>567+53</f>
+        <v>620</v>
+      </c>
       <c r="D40" s="151"/>
       <c r="E40" s="151"/>
       <c r="F40" s="151"/>
       <c r="G40" s="151"/>
-      <c r="H40" s="151"/>
+      <c r="H40" s="151">
+        <v>4</v>
+      </c>
       <c r="I40" s="151"/>
       <c r="J40" s="152"/>
-      <c r="K40" s="153"/>
+      <c r="K40" s="153">
+        <v>20</v>
+      </c>
       <c r="L40" s="154"/>
-      <c r="M40" s="155"/>
+      <c r="M40" s="155">
+        <v>1</v>
+      </c>
       <c r="N40" s="156"/>
-      <c r="O40" s="157"/>
-      <c r="P40" s="158"/>
-      <c r="Q40" s="158"/>
+      <c r="O40" s="157">
+        <v>1</v>
+      </c>
+      <c r="P40" s="158">
+        <v>12</v>
+      </c>
+      <c r="Q40" s="158">
+        <v>2</v>
+      </c>
       <c r="R40" s="159"/>
       <c r="S40" s="154"/>
       <c r="T40" s="169">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="U40" s="169">
         <f>C40*24+M40*24+O40*24+Q40*24+T40</f>
-        <v>0</v>
+        <v>15012</v>
       </c>
       <c r="V40" s="169">
         <f>U40/24</f>
-        <v>0</v>
+        <v>625.5</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -53026,7 +53165,10 @@
       <c r="B41" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="176"/>
+      <c r="C41" s="176">
+        <f>1440+70</f>
+        <v>1510</v>
+      </c>
       <c r="D41" s="176"/>
       <c r="E41" s="176"/>
       <c r="F41" s="176"/>
@@ -53036,11 +53178,15 @@
       <c r="J41" s="177"/>
       <c r="K41" s="178"/>
       <c r="L41" s="179"/>
-      <c r="M41" s="180"/>
+      <c r="M41" s="180">
+        <v>1</v>
+      </c>
       <c r="N41" s="181"/>
       <c r="O41" s="176"/>
       <c r="P41" s="177"/>
-      <c r="Q41" s="177"/>
+      <c r="Q41" s="177">
+        <v>16</v>
+      </c>
       <c r="R41" s="178"/>
       <c r="S41" s="179"/>
       <c r="T41" s="182">
@@ -53049,11 +53195,11 @@
       </c>
       <c r="U41" s="182">
         <f>C41*12+M41*12+O41*12+Q41*12+T41</f>
-        <v>0</v>
+        <v>18324</v>
       </c>
       <c r="V41" s="182">
         <f>U41/12</f>
-        <v>0</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -53093,34 +53239,53 @@
       <c r="B43" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="157"/>
+      <c r="C43" s="157">
+        <f>1028+3024+102+5940+8424+5400+7128</f>
+        <v>31046</v>
+      </c>
       <c r="D43" s="157"/>
       <c r="E43" s="157"/>
       <c r="F43" s="157"/>
       <c r="G43" s="157"/>
-      <c r="H43" s="157"/>
-      <c r="I43" s="157"/>
-      <c r="J43" s="158"/>
-      <c r="K43" s="159"/>
+      <c r="H43" s="157">
+        <v>2</v>
+      </c>
+      <c r="I43" s="157">
+        <v>7</v>
+      </c>
+      <c r="J43" s="158">
+        <f>6+2</f>
+        <v>8</v>
+      </c>
+      <c r="K43" s="159">
+        <f>93*6+5</f>
+        <v>563</v>
+      </c>
       <c r="L43" s="154"/>
-      <c r="M43" s="155"/>
+      <c r="M43" s="155">
+        <v>248</v>
+      </c>
       <c r="N43" s="156"/>
-      <c r="O43" s="157"/>
+      <c r="O43" s="157">
+        <v>68</v>
+      </c>
       <c r="P43" s="158"/>
-      <c r="Q43" s="158"/>
+      <c r="Q43" s="158">
+        <v>372</v>
+      </c>
       <c r="R43" s="159"/>
       <c r="S43" s="154"/>
       <c r="T43" s="169">
         <f t="shared" ref="T43" si="6">H43+I43+J43+K43+N43+P43+R43</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="U43" s="169">
         <f>C43*6+M43*6+O43*6+Q43*6+T43</f>
-        <v>0</v>
+        <v>190984</v>
       </c>
       <c r="V43" s="169">
         <f>U43/6</f>
-        <v>0</v>
+        <v>31830.666666666668</v>
       </c>
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
@@ -53236,7 +53401,10 @@
       <c r="B47" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="157"/>
+      <c r="C47" s="157">
+        <f>24+2268+44</f>
+        <v>2336</v>
+      </c>
       <c r="D47" s="157"/>
       <c r="E47" s="157"/>
       <c r="F47" s="157"/>
@@ -53244,26 +53412,36 @@
       <c r="H47" s="157"/>
       <c r="I47" s="157"/>
       <c r="J47" s="158"/>
-      <c r="K47" s="159"/>
+      <c r="K47" s="159">
+        <v>6</v>
+      </c>
       <c r="L47" s="154"/>
-      <c r="M47" s="155"/>
+      <c r="M47" s="155">
+        <v>5</v>
+      </c>
       <c r="N47" s="156"/>
-      <c r="O47" s="157"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="O47" s="157">
+        <v>3</v>
+      </c>
+      <c r="P47" s="158">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="158">
+        <v>10</v>
+      </c>
       <c r="R47" s="159"/>
       <c r="S47" s="154"/>
       <c r="T47" s="169">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U47" s="169">
         <f>C47*6+M47*6+O47*6+Q47*6+T47</f>
-        <v>0</v>
+        <v>14134</v>
       </c>
       <c r="V47" s="169">
         <f>U47/6</f>
-        <v>0</v>
+        <v>2355.6666666666665</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -53388,7 +53566,9 @@
       <c r="B51" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="C51" s="157"/>
+      <c r="C51" s="157">
+        <v>34</v>
+      </c>
       <c r="D51" s="157"/>
       <c r="E51" s="157"/>
       <c r="F51" s="157"/>
@@ -53411,11 +53591,11 @@
       </c>
       <c r="U51" s="169">
         <f>C51*6+M51*6+O51*6+Q51*6+T51</f>
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="V51" s="169">
         <f>U51/6</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -53464,7 +53644,9 @@
       <c r="B53" s="74" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="162">
+        <v>2</v>
+      </c>
       <c r="D53" s="162"/>
       <c r="E53" s="162"/>
       <c r="F53" s="162"/>
@@ -53487,11 +53669,11 @@
       </c>
       <c r="U53" s="167">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V53" s="167">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -53617,7 +53799,7 @@
       </c>
       <c r="C58" s="49">
         <f>SUM(C7:C57)</f>
-        <v>0</v>
+        <v>44060</v>
       </c>
       <c r="D58" s="49"/>
       <c r="E58" s="49"/>
@@ -53631,56 +53813,56 @@
       </c>
       <c r="H58" s="49">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K58" s="54">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="M58" s="53">
         <f t="shared" ref="M58:R58" si="12">SUM(M7:M57)</f>
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="P58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="R58" s="53">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S58" s="147"/>
       <c r="T58" s="51">
         <f>SUM(T7:T57)</f>
-        <v>0</v>
-      </c>
-      <c r="U58" s="51">
+        <v>747</v>
+      </c>
+      <c r="U58" s="186">
         <f>SUM(U7:U57)</f>
-        <v>0</v>
+        <v>362211</v>
       </c>
       <c r="V58" s="51">
         <f>SUM(V7:V57)</f>
-        <v>0</v>
+        <v>45217.875</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -53950,13 +54132,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="J5:K5"/>
     <mergeCell ref="C60:K60"/>
     <mergeCell ref="I1:U1"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="T4:T5"/>
     <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
